--- a/data_raw/exportacion_leche_polvo_entera.xlsx
+++ b/data_raw/exportacion_leche_polvo_entera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/2- Mercado externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="581" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC074253-6900-41F7-B354-9E2A7A576A1D}"/>
+  <xr:revisionPtr revIDLastSave="594" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C74971C-5845-4459-AEBA-F95B9BA908AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="703" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1559,7 +1559,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1803,18 +1803,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3568,7 +3571,9 @@
       <c r="C35" s="97">
         <v>47085142</v>
       </c>
-      <c r="D35" s="98"/>
+      <c r="D35" s="98">
+        <v>35086872.229999989</v>
+      </c>
       <c r="E35" s="99"/>
       <c r="F35" s="100"/>
       <c r="G35" s="100"/>
@@ -4619,7 +4624,9 @@
       <c r="C59" s="95">
         <v>12985</v>
       </c>
-      <c r="D59" s="91"/>
+      <c r="D59" s="91">
+        <v>9482.8000000000029</v>
+      </c>
       <c r="E59" s="95"/>
       <c r="F59" s="95"/>
       <c r="G59" s="91"/>
@@ -5690,7 +5697,9 @@
         <f>+C35/C59</f>
         <v>3626.1179822872546</v>
       </c>
-      <c r="D83" s="18"/>
+      <c r="D83" s="18">
+        <v>3700.0540167461063</v>
+      </c>
       <c r="E83" s="18"/>
       <c r="F83" s="18"/>
       <c r="G83" s="18"/>
@@ -5863,23 +5872,23 @@
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:13" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="132" t="s">
+      <c r="C13" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="128"/>
-      <c r="E13" s="132" t="s">
+      <c r="E13" s="127" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="128"/>
-      <c r="G13" s="132" t="s">
+      <c r="G13" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="128"/>
-      <c r="I13" s="132" t="s">
+      <c r="I13" s="127" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="128"/>
-      <c r="K13" s="132" t="s">
+      <c r="K13" s="127" t="s">
         <v>32</v>
       </c>
       <c r="L13" s="128"/>
@@ -6666,23 +6675,23 @@
     </row>
     <row r="35" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="132" t="s">
+      <c r="C36" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D36" s="128"/>
-      <c r="E36" s="132" t="s">
+      <c r="E36" s="127" t="s">
         <v>29</v>
       </c>
       <c r="F36" s="128"/>
-      <c r="G36" s="132" t="s">
+      <c r="G36" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H36" s="128"/>
-      <c r="I36" s="132" t="s">
+      <c r="I36" s="127" t="s">
         <v>31</v>
       </c>
       <c r="J36" s="128"/>
-      <c r="K36" s="132" t="s">
+      <c r="K36" s="127" t="s">
         <v>32</v>
       </c>
       <c r="L36" s="128"/>
@@ -7504,23 +7513,23 @@
       <c r="B65" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C65" s="132" t="s">
+      <c r="C65" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="128"/>
-      <c r="E65" s="132" t="s">
+      <c r="E65" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F65" s="127"/>
-      <c r="G65" s="132" t="s">
+      <c r="F65" s="129"/>
+      <c r="G65" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H65" s="128"/>
-      <c r="I65" s="127" t="s">
+      <c r="I65" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J65" s="128"/>
-      <c r="K65" s="127" t="s">
+      <c r="K65" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L65" s="128"/>
@@ -7721,23 +7730,23 @@
       <c r="B73" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C73" s="132" t="s">
+      <c r="C73" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D73" s="128"/>
-      <c r="E73" s="132" t="s">
+      <c r="E73" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F73" s="127"/>
-      <c r="G73" s="132" t="s">
+      <c r="F73" s="129"/>
+      <c r="G73" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H73" s="128"/>
-      <c r="I73" s="127" t="s">
+      <c r="I73" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J73" s="128"/>
-      <c r="K73" s="127" t="s">
+      <c r="K73" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L73" s="128"/>
@@ -7938,23 +7947,23 @@
       <c r="B81" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C81" s="132" t="s">
+      <c r="C81" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="128"/>
-      <c r="E81" s="132" t="s">
+      <c r="E81" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F81" s="127"/>
-      <c r="G81" s="132" t="s">
+      <c r="F81" s="129"/>
+      <c r="G81" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H81" s="128"/>
-      <c r="I81" s="127" t="s">
+      <c r="I81" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J81" s="128"/>
-      <c r="K81" s="127" t="s">
+      <c r="K81" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L81" s="128"/>
@@ -8155,23 +8164,23 @@
       <c r="B89" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C89" s="132" t="s">
+      <c r="C89" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D89" s="128"/>
-      <c r="E89" s="132" t="s">
+      <c r="E89" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F89" s="127"/>
-      <c r="G89" s="132" t="s">
+      <c r="F89" s="129"/>
+      <c r="G89" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H89" s="128"/>
-      <c r="I89" s="127" t="s">
+      <c r="I89" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J89" s="128"/>
-      <c r="K89" s="127" t="s">
+      <c r="K89" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L89" s="128"/>
@@ -8383,23 +8392,23 @@
       <c r="B98" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C98" s="132" t="s">
+      <c r="C98" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="128"/>
-      <c r="E98" s="132" t="s">
+      <c r="E98" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F98" s="127"/>
-      <c r="G98" s="132" t="s">
+      <c r="F98" s="129"/>
+      <c r="G98" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H98" s="128"/>
-      <c r="I98" s="127" t="s">
+      <c r="I98" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J98" s="128"/>
-      <c r="K98" s="127" t="s">
+      <c r="K98" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L98" s="128"/>
@@ -8613,23 +8622,23 @@
       <c r="B107" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C107" s="132" t="s">
+      <c r="C107" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D107" s="128"/>
-      <c r="E107" s="132" t="s">
+      <c r="E107" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F107" s="127"/>
-      <c r="G107" s="132" t="s">
+      <c r="F107" s="129"/>
+      <c r="G107" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H107" s="128"/>
-      <c r="I107" s="127" t="s">
+      <c r="I107" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J107" s="128"/>
-      <c r="K107" s="127" t="s">
+      <c r="K107" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L107" s="128"/>
@@ -8843,23 +8852,23 @@
       <c r="B116" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C116" s="132" t="s">
+      <c r="C116" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D116" s="128"/>
-      <c r="E116" s="132" t="s">
+      <c r="E116" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F116" s="127"/>
-      <c r="G116" s="132" t="s">
+      <c r="F116" s="129"/>
+      <c r="G116" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H116" s="128"/>
-      <c r="I116" s="127" t="s">
+      <c r="I116" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J116" s="128"/>
-      <c r="K116" s="127" t="s">
+      <c r="K116" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L116" s="128"/>
@@ -9073,23 +9082,23 @@
       <c r="B125" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C125" s="132" t="s">
+      <c r="C125" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D125" s="128"/>
-      <c r="E125" s="132" t="s">
+      <c r="E125" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F125" s="127"/>
-      <c r="G125" s="132" t="s">
+      <c r="F125" s="129"/>
+      <c r="G125" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H125" s="128"/>
-      <c r="I125" s="127" t="s">
+      <c r="I125" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J125" s="128"/>
-      <c r="K125" s="127" t="s">
+      <c r="K125" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L125" s="128"/>
@@ -9303,23 +9312,23 @@
       <c r="B135" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C135" s="132" t="s">
+      <c r="C135" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="128"/>
-      <c r="E135" s="132" t="s">
+      <c r="E135" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F135" s="127"/>
-      <c r="G135" s="132" t="s">
+      <c r="F135" s="129"/>
+      <c r="G135" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H135" s="128"/>
-      <c r="I135" s="127" t="s">
+      <c r="I135" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J135" s="128"/>
-      <c r="K135" s="127" t="s">
+      <c r="K135" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L135" s="128"/>
@@ -9533,23 +9542,23 @@
       <c r="B144" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C144" s="132" t="s">
+      <c r="C144" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D144" s="128"/>
-      <c r="E144" s="132" t="s">
+      <c r="E144" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F144" s="127"/>
-      <c r="G144" s="132" t="s">
+      <c r="F144" s="129"/>
+      <c r="G144" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H144" s="128"/>
-      <c r="I144" s="127" t="s">
+      <c r="I144" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J144" s="128"/>
-      <c r="K144" s="127" t="s">
+      <c r="K144" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L144" s="128"/>
@@ -9763,23 +9772,23 @@
       <c r="B153" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C153" s="132" t="s">
+      <c r="C153" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D153" s="128"/>
-      <c r="E153" s="132" t="s">
+      <c r="E153" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F153" s="127"/>
-      <c r="G153" s="132" t="s">
+      <c r="F153" s="129"/>
+      <c r="G153" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H153" s="128"/>
-      <c r="I153" s="127" t="s">
+      <c r="I153" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J153" s="128"/>
-      <c r="K153" s="127" t="s">
+      <c r="K153" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L153" s="128"/>
@@ -9983,23 +9992,23 @@
       <c r="B162" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C162" s="132" t="s">
+      <c r="C162" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D162" s="128"/>
-      <c r="E162" s="132" t="s">
+      <c r="E162" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F162" s="127"/>
-      <c r="G162" s="132" t="s">
+      <c r="F162" s="129"/>
+      <c r="G162" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H162" s="128"/>
-      <c r="I162" s="127" t="s">
+      <c r="I162" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J162" s="128"/>
-      <c r="K162" s="127" t="s">
+      <c r="K162" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L162" s="128"/>
@@ -10203,23 +10212,23 @@
       <c r="B171" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C171" s="132" t="s">
+      <c r="C171" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D171" s="128"/>
-      <c r="E171" s="132" t="s">
+      <c r="E171" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F171" s="127"/>
-      <c r="G171" s="132" t="s">
+      <c r="F171" s="129"/>
+      <c r="G171" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H171" s="128"/>
-      <c r="I171" s="127" t="s">
+      <c r="I171" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J171" s="128"/>
-      <c r="K171" s="127" t="s">
+      <c r="K171" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L171" s="128"/>
@@ -10424,23 +10433,23 @@
       <c r="B180" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C180" s="132" t="s">
+      <c r="C180" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D180" s="128"/>
-      <c r="E180" s="132" t="s">
+      <c r="E180" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F180" s="127"/>
-      <c r="G180" s="132" t="s">
+      <c r="F180" s="129"/>
+      <c r="G180" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H180" s="128"/>
-      <c r="I180" s="127" t="s">
+      <c r="I180" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J180" s="128"/>
-      <c r="K180" s="127" t="s">
+      <c r="K180" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L180" s="128"/>
@@ -10645,23 +10654,23 @@
       <c r="B189" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C189" s="132" t="s">
+      <c r="C189" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D189" s="128"/>
-      <c r="E189" s="132" t="s">
+      <c r="E189" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F189" s="127"/>
-      <c r="G189" s="132" t="s">
+      <c r="F189" s="129"/>
+      <c r="G189" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H189" s="128"/>
-      <c r="I189" s="127" t="s">
+      <c r="I189" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J189" s="128"/>
-      <c r="K189" s="127" t="s">
+      <c r="K189" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L189" s="128"/>
@@ -10866,23 +10875,23 @@
       <c r="B198" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C198" s="132" t="s">
+      <c r="C198" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D198" s="128"/>
-      <c r="E198" s="132" t="s">
+      <c r="E198" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F198" s="127"/>
-      <c r="G198" s="132" t="s">
+      <c r="F198" s="129"/>
+      <c r="G198" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H198" s="128"/>
-      <c r="I198" s="127" t="s">
+      <c r="I198" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J198" s="128"/>
-      <c r="K198" s="127" t="s">
+      <c r="K198" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L198" s="128"/>
@@ -11087,23 +11096,23 @@
       <c r="B207" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C207" s="132" t="s">
+      <c r="C207" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D207" s="128"/>
-      <c r="E207" s="132" t="s">
+      <c r="E207" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F207" s="127"/>
-      <c r="G207" s="132" t="s">
+      <c r="F207" s="129"/>
+      <c r="G207" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H207" s="128"/>
-      <c r="I207" s="127" t="s">
+      <c r="I207" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J207" s="128"/>
-      <c r="K207" s="127" t="s">
+      <c r="K207" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L207" s="128"/>
@@ -11308,23 +11317,23 @@
       <c r="B216" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C216" s="132" t="s">
+      <c r="C216" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D216" s="128"/>
-      <c r="E216" s="132" t="s">
+      <c r="E216" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F216" s="127"/>
-      <c r="G216" s="132" t="s">
+      <c r="F216" s="129"/>
+      <c r="G216" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H216" s="128"/>
-      <c r="I216" s="127" t="s">
+      <c r="I216" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J216" s="128"/>
-      <c r="K216" s="127" t="s">
+      <c r="K216" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L216" s="128"/>
@@ -11512,7 +11521,7 @@
     </row>
     <row r="223" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="224" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C224" s="129" t="s">
+      <c r="C224" s="132" t="s">
         <v>73</v>
       </c>
       <c r="D224" s="130"/>
@@ -11529,23 +11538,23 @@
       <c r="B225" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C225" s="132" t="s">
+      <c r="C225" s="127" t="s">
         <v>28</v>
       </c>
       <c r="D225" s="128"/>
-      <c r="E225" s="132" t="s">
+      <c r="E225" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F225" s="127"/>
-      <c r="G225" s="132" t="s">
+      <c r="F225" s="129"/>
+      <c r="G225" s="127" t="s">
         <v>30</v>
       </c>
       <c r="H225" s="128"/>
-      <c r="I225" s="127" t="s">
+      <c r="I225" s="129" t="s">
         <v>31</v>
       </c>
       <c r="J225" s="128"/>
-      <c r="K225" s="127" t="s">
+      <c r="K225" s="129" t="s">
         <v>17</v>
       </c>
       <c r="L225" s="128"/>
@@ -11733,17 +11742,96 @@
     </row>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="C64:L64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="I198:J198"/>
+    <mergeCell ref="K198:L198"/>
+    <mergeCell ref="C206:L206"/>
+    <mergeCell ref="C224:L224"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="E207:F207"/>
+    <mergeCell ref="G207:H207"/>
+    <mergeCell ref="I207:J207"/>
+    <mergeCell ref="C225:D225"/>
+    <mergeCell ref="E225:F225"/>
+    <mergeCell ref="G225:H225"/>
+    <mergeCell ref="I225:J225"/>
+    <mergeCell ref="K225:L225"/>
+    <mergeCell ref="C216:D216"/>
+    <mergeCell ref="E216:F216"/>
+    <mergeCell ref="G216:H216"/>
+    <mergeCell ref="I216:J216"/>
+    <mergeCell ref="K216:L216"/>
+    <mergeCell ref="C170:L170"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="G171:H171"/>
+    <mergeCell ref="I171:J171"/>
+    <mergeCell ref="K171:L171"/>
+    <mergeCell ref="K207:L207"/>
+    <mergeCell ref="C215:L215"/>
+    <mergeCell ref="C179:L179"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="E180:F180"/>
+    <mergeCell ref="G180:H180"/>
+    <mergeCell ref="I180:J180"/>
+    <mergeCell ref="K180:L180"/>
+    <mergeCell ref="C188:L188"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="E189:F189"/>
+    <mergeCell ref="G189:H189"/>
+    <mergeCell ref="I189:J189"/>
+    <mergeCell ref="K189:L189"/>
+    <mergeCell ref="C197:L197"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="E198:F198"/>
+    <mergeCell ref="G198:H198"/>
+    <mergeCell ref="C152:L152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="I153:J153"/>
+    <mergeCell ref="K153:L153"/>
+    <mergeCell ref="C161:L161"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="I162:J162"/>
+    <mergeCell ref="K162:L162"/>
+    <mergeCell ref="C134:L134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="C143:L143"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="G144:H144"/>
+    <mergeCell ref="I144:J144"/>
+    <mergeCell ref="K144:L144"/>
+    <mergeCell ref="C97:L97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="C124:L124"/>
+    <mergeCell ref="C115:L115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="C106:L106"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="K107:L107"/>
     <mergeCell ref="C88:L88"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="E89:F89"/>
@@ -11768,96 +11856,17 @@
     <mergeCell ref="I73:J73"/>
     <mergeCell ref="K73:L73"/>
     <mergeCell ref="C80:L80"/>
-    <mergeCell ref="C97:L97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="E125:F125"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="C124:L124"/>
-    <mergeCell ref="C115:L115"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="C106:L106"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="I107:J107"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="C134:L134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="C143:L143"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="G144:H144"/>
-    <mergeCell ref="I144:J144"/>
-    <mergeCell ref="K144:L144"/>
-    <mergeCell ref="C152:L152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="E153:F153"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="I153:J153"/>
-    <mergeCell ref="K153:L153"/>
-    <mergeCell ref="C161:L161"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="E162:F162"/>
-    <mergeCell ref="G162:H162"/>
-    <mergeCell ref="I162:J162"/>
-    <mergeCell ref="K162:L162"/>
-    <mergeCell ref="C170:L170"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="E171:F171"/>
-    <mergeCell ref="G171:H171"/>
-    <mergeCell ref="I171:J171"/>
-    <mergeCell ref="K171:L171"/>
-    <mergeCell ref="K207:L207"/>
-    <mergeCell ref="C215:L215"/>
-    <mergeCell ref="C179:L179"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="E180:F180"/>
-    <mergeCell ref="G180:H180"/>
-    <mergeCell ref="I180:J180"/>
-    <mergeCell ref="K180:L180"/>
-    <mergeCell ref="C188:L188"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="E189:F189"/>
-    <mergeCell ref="G189:H189"/>
-    <mergeCell ref="I189:J189"/>
-    <mergeCell ref="K189:L189"/>
-    <mergeCell ref="C197:L197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="E198:F198"/>
-    <mergeCell ref="G198:H198"/>
-    <mergeCell ref="I198:J198"/>
-    <mergeCell ref="K198:L198"/>
-    <mergeCell ref="C206:L206"/>
-    <mergeCell ref="C224:L224"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="E207:F207"/>
-    <mergeCell ref="G207:H207"/>
-    <mergeCell ref="I207:J207"/>
-    <mergeCell ref="C225:D225"/>
-    <mergeCell ref="E225:F225"/>
-    <mergeCell ref="G225:H225"/>
-    <mergeCell ref="I225:J225"/>
-    <mergeCell ref="K225:L225"/>
-    <mergeCell ref="C216:D216"/>
-    <mergeCell ref="E216:F216"/>
-    <mergeCell ref="G216:H216"/>
-    <mergeCell ref="I216:J216"/>
-    <mergeCell ref="K216:L216"/>
+    <mergeCell ref="C64:L64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="K81:L81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11866,7 +11875,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B9:I242"/>
+  <dimension ref="B9:I244"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -15108,7 +15117,7 @@
       </c>
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B241" s="92">
+      <c r="B241" s="32">
         <v>46023</v>
       </c>
       <c r="C241" s="88">
@@ -15122,7 +15131,27 @@
       </c>
     </row>
     <row r="242" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B242" s="55" t="s">
+      <c r="B242" s="33">
+        <v>46054</v>
+      </c>
+      <c r="C242" s="87">
+        <v>35086872.229999989</v>
+      </c>
+      <c r="D242" s="83">
+        <v>9482.8000000000029</v>
+      </c>
+      <c r="E242" s="22">
+        <v>3700.0540167461063</v>
+      </c>
+    </row>
+    <row r="243" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B243" s="135"/>
+      <c r="C243" s="83"/>
+      <c r="D243" s="83"/>
+      <c r="E243" s="83"/>
+    </row>
+    <row r="244" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B244" s="55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -15140,6 +15169,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -15380,19 +15422,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -15405,6 +15434,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC8F936-4AF3-4FF9-8B1E-0736929643E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15423,22 +15468,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
   <ds:schemaRefs>

--- a/data_raw/exportacion_leche_polvo_entera.xlsx
+++ b/data_raw/exportacion_leche_polvo_entera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/2- Mercado externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="594" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C74971C-5845-4459-AEBA-F95B9BA908AB}"/>
+  <xr:revisionPtr revIDLastSave="661" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D12FD62A-1B3C-46EA-933C-39F26657C5A4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="703" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="85">
   <si>
     <t>Estos datos se consideran preliminares a partir del 23/10/2020 e incluyen Admisiones temporales. Estas modificaciones recientes se deben a cambios realizados por la Agencia de Aduanas de Uruguay.</t>
   </si>
@@ -1817,9 +1817,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="153">
     <cellStyle name="20% - Énfasis1" xfId="11" builtinId="30" customBuiltin="1"/>
@@ -2552,7 +2550,7 @@
     <col min="11" max="14" width="11.42578125" customWidth="1"/>
     <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
@@ -3461,7 +3459,7 @@
         <f t="shared" si="2"/>
         <v>2.5649255177751185E-2</v>
       </c>
-      <c r="Q32" s="1"/>
+      <c r="Q32" s="135"/>
       <c r="R32" s="104"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
@@ -3512,7 +3510,7 @@
         <f t="shared" si="2"/>
         <v>-8.6761415610088211E-3</v>
       </c>
-      <c r="Q33" s="116"/>
+      <c r="Q33" s="135"/>
       <c r="R33" s="104"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
@@ -3561,7 +3559,7 @@
       <c r="P34" s="3">
         <v>0.18613443776225669</v>
       </c>
-      <c r="Q34" s="116"/>
+      <c r="Q34" s="135"/>
       <c r="R34" s="104"/>
     </row>
     <row r="35" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3574,8 +3572,12 @@
       <c r="D35" s="98">
         <v>35086872.229999989</v>
       </c>
-      <c r="E35" s="99"/>
-      <c r="F35" s="100"/>
+      <c r="E35" s="99">
+        <v>57450456</v>
+      </c>
+      <c r="F35" s="100">
+        <v>46922560</v>
+      </c>
       <c r="G35" s="100"/>
       <c r="H35" s="99"/>
       <c r="I35" s="100"/>
@@ -3586,7 +3588,7 @@
       <c r="N35" s="99"/>
       <c r="O35" s="16"/>
       <c r="P35" s="17"/>
-      <c r="Q35" s="116"/>
+      <c r="Q35" s="135"/>
       <c r="R35" s="104"/>
     </row>
     <row r="36" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3621,6 +3623,7 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
+      <c r="Q37" s="135"/>
     </row>
     <row r="38" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
@@ -3635,6 +3638,7 @@
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
+      <c r="Q38" s="135"/>
     </row>
     <row r="39" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="36" t="s">
@@ -4614,7 +4618,7 @@
       <c r="P58" s="3">
         <v>5.9639816496076969E-2</v>
       </c>
-      <c r="Q58" s="116"/>
+      <c r="Q58" s="135"/>
       <c r="R58" s="104"/>
     </row>
     <row r="59" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4627,8 +4631,12 @@
       <c r="D59" s="91">
         <v>9482.8000000000029</v>
       </c>
-      <c r="E59" s="95"/>
-      <c r="F59" s="95"/>
+      <c r="E59" s="95">
+        <v>16137</v>
+      </c>
+      <c r="F59" s="95">
+        <v>13081</v>
+      </c>
       <c r="G59" s="91"/>
       <c r="H59" s="91"/>
       <c r="I59" s="91"/>
@@ -4639,7 +4647,7 @@
       <c r="N59" s="95"/>
       <c r="O59" s="16"/>
       <c r="P59" s="17"/>
-      <c r="Q59" s="106"/>
+      <c r="Q59" s="135"/>
       <c r="R59" s="104"/>
     </row>
     <row r="60" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5685,7 +5693,7 @@
         <f t="shared" si="8"/>
         <v>3978.4184285259557</v>
       </c>
-      <c r="Q82" s="116"/>
+      <c r="Q82" s="135"/>
       <c r="R82" s="104"/>
       <c r="XFD82" s="1"/>
     </row>
@@ -5700,8 +5708,12 @@
       <c r="D83" s="18">
         <v>3700.0540167461063</v>
       </c>
-      <c r="E83" s="18"/>
-      <c r="F83" s="18"/>
+      <c r="E83" s="18">
+        <v>3560.1695482431678</v>
+      </c>
+      <c r="F83" s="18">
+        <v>3587.077440562648</v>
+      </c>
       <c r="G83" s="18"/>
       <c r="H83" s="18"/>
       <c r="I83" s="18"/>
@@ -5712,7 +5724,7 @@
       <c r="N83" s="18"/>
       <c r="O83" s="16"/>
       <c r="P83" s="16"/>
-      <c r="Q83" s="116"/>
+      <c r="Q83" s="135"/>
       <c r="R83" s="104"/>
     </row>
     <row r="84" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
@@ -5782,7 +5794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:M231"/>
+  <dimension ref="B1:M241"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
@@ -6458,7 +6470,7 @@
         <v>38551.514999999999</v>
       </c>
       <c r="J28" s="51">
-        <f t="shared" ref="J28:J33" si="4">I28/I27-1</f>
+        <f t="shared" ref="J28:J32" si="4">I28/I27-1</f>
         <v>0.10381509416927193</v>
       </c>
       <c r="K28" s="1">
@@ -6505,7 +6517,7 @@
         <v>141176.46099999989</v>
       </c>
       <c r="L29" s="51">
-        <f t="shared" ref="L29:L33" si="5">K29/K28-1</f>
+        <f t="shared" ref="L29:L32" si="5">K29/K28-1</f>
         <v>-3.7532092267166028E-2</v>
       </c>
     </row>
@@ -6623,2680 +6635,2619 @@
         <v>-5.7779305539336079E-3</v>
       </c>
     </row>
-    <row r="33" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="67">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="62">
         <v>2025</v>
       </c>
-      <c r="C33" s="53">
+      <c r="C33" s="7">
         <v>37496.223830000024</v>
       </c>
-      <c r="D33" s="54">
-        <f>+C33/C32-1</f>
+      <c r="D33" s="51">
         <v>7.6924972568189087E-2</v>
       </c>
-      <c r="E33" s="53">
+      <c r="E33" s="7">
         <v>33894.893869999993</v>
       </c>
-      <c r="F33" s="54">
+      <c r="F33" s="51">
         <v>-3.5523681518421446E-2</v>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="1">
         <v>45007.448920000032</v>
       </c>
-      <c r="H33" s="54">
-        <f>+G33/G32-1</f>
+      <c r="H33" s="51">
         <v>5.5764122164989605E-2</v>
       </c>
-      <c r="I33" s="53">
+      <c r="I33" s="7">
         <v>51678.194350000071</v>
       </c>
-      <c r="J33" s="54">
-        <f t="shared" si="4"/>
+      <c r="J33" s="51">
         <v>0.12408289573149411</v>
       </c>
-      <c r="K33" s="18">
-        <f>+I33+G33+E33+C33</f>
+      <c r="K33" s="1">
         <v>168076.76097000012</v>
       </c>
-      <c r="L33" s="54">
-        <f t="shared" si="5"/>
+      <c r="L33" s="51">
         <v>5.963981649607808E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C34" s="55" t="s">
+    <row r="34" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="67">
+        <v>2026</v>
+      </c>
+      <c r="C34" s="53">
+        <v>38606</v>
+      </c>
+      <c r="D34" s="54">
+        <f>+C34/C33-1</f>
+        <v>2.9597011555922759E-2</v>
+      </c>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="54"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C35" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-    </row>
-    <row r="35" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="127" t="s">
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+    </row>
+    <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="128"/>
-      <c r="E36" s="127" t="s">
+      <c r="D37" s="128"/>
+      <c r="E37" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="128"/>
-      <c r="G36" s="127" t="s">
+      <c r="F37" s="128"/>
+      <c r="G37" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H36" s="128"/>
-      <c r="I36" s="127" t="s">
+      <c r="H37" s="128"/>
+      <c r="I37" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="J36" s="128"/>
-      <c r="K36" s="127" t="s">
+      <c r="J37" s="128"/>
+      <c r="K37" s="127" t="s">
         <v>32</v>
       </c>
-      <c r="L36" s="128"/>
-    </row>
-    <row r="37" spans="2:12" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="44" t="s">
+      <c r="L37" s="128"/>
+    </row>
+    <row r="38" spans="2:12" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="45" t="s">
+      <c r="C38" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="46" t="s">
+      <c r="D38" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="45" t="s">
+      <c r="E38" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="F37" s="46" t="s">
+      <c r="F38" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="G37" s="45" t="s">
+      <c r="G38" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="46" t="s">
+      <c r="H38" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="45" t="s">
+      <c r="I38" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="J37" s="46" t="s">
+      <c r="J38" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="K37" s="45" t="s">
+      <c r="K38" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="L37" s="46" t="s">
+      <c r="L38" s="46" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" s="47">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" s="47">
         <v>2007</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C39" s="6">
         <v>2316.0981952482853</v>
       </c>
-      <c r="D38" s="48"/>
-      <c r="E38" s="7">
+      <c r="D39" s="48"/>
+      <c r="E39" s="7">
         <v>2672.3871637478087</v>
       </c>
-      <c r="F38" s="56"/>
-      <c r="G38" s="7">
+      <c r="F39" s="56"/>
+      <c r="G39" s="7">
         <v>2969.9711141749349</v>
       </c>
-      <c r="H38" s="56"/>
-      <c r="I38" s="7">
+      <c r="H39" s="56"/>
+      <c r="I39" s="7">
         <v>3464.06221700582</v>
       </c>
-      <c r="J38" s="56"/>
-      <c r="K38" s="6">
+      <c r="J39" s="56"/>
+      <c r="K39" s="6">
         <v>2921.9656414486972</v>
       </c>
-      <c r="L38" s="48"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39" s="49">
-        <v>2008</v>
-      </c>
-      <c r="C39" s="7">
-        <v>4281.4242766745419</v>
-      </c>
-      <c r="D39" s="50">
-        <f t="shared" ref="D39:D52" si="6">C39/C38-1</f>
-        <v>0.84855041356118943</v>
-      </c>
-      <c r="E39" s="7">
-        <v>4521.3450128188788</v>
-      </c>
-      <c r="F39" s="50">
-        <f t="shared" ref="F39:F50" si="7">E39/E38-1</f>
-        <v>0.69187499257332719</v>
-      </c>
-      <c r="G39" s="7">
-        <v>4403.1737637725882</v>
-      </c>
-      <c r="H39" s="50">
-        <f t="shared" ref="H39:H48" si="8">G39/G38-1</f>
-        <v>0.48256450803758089</v>
-      </c>
-      <c r="I39" s="7">
-        <v>3198.0316681223435</v>
-      </c>
-      <c r="J39" s="50">
-        <f t="shared" ref="J39:J56" si="9">I39/I38-1</f>
-        <v>-7.6797277940758635E-2</v>
-      </c>
-      <c r="K39" s="7">
-        <v>4078.3684896736486</v>
-      </c>
-      <c r="L39" s="50">
-        <f t="shared" ref="L39:L56" si="10">K39/K38-1</f>
-        <v>0.39576195962783878</v>
-      </c>
+      <c r="L39" s="48"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="49">
+        <v>2008</v>
+      </c>
+      <c r="C40" s="7">
+        <v>4281.4242766745419</v>
+      </c>
+      <c r="D40" s="50">
+        <f t="shared" ref="D40:D53" si="6">C40/C39-1</f>
+        <v>0.84855041356118943</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4521.3450128188788</v>
+      </c>
+      <c r="F40" s="50">
+        <f t="shared" ref="F40:F51" si="7">E40/E39-1</f>
+        <v>0.69187499257332719</v>
+      </c>
+      <c r="G40" s="7">
+        <v>4403.1737637725882</v>
+      </c>
+      <c r="H40" s="50">
+        <f t="shared" ref="H40:H49" si="8">G40/G39-1</f>
+        <v>0.48256450803758089</v>
+      </c>
+      <c r="I40" s="7">
+        <v>3198.0316681223435</v>
+      </c>
+      <c r="J40" s="50">
+        <f t="shared" ref="J40:J56" si="9">I40/I39-1</f>
+        <v>-7.6797277940758635E-2</v>
+      </c>
+      <c r="K40" s="7">
+        <v>4078.3684896736486</v>
+      </c>
+      <c r="L40" s="50">
+        <f t="shared" ref="L40:L56" si="10">K40/K39-1</f>
+        <v>0.39576195962783878</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" s="49">
         <v>2009</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C41" s="7">
         <v>1824.811792095996</v>
       </c>
-      <c r="D40" s="50">
+      <c r="D41" s="50">
         <f t="shared" si="6"/>
         <v>-0.57378393866786781</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E41" s="7">
         <v>2156.6975638776694</v>
       </c>
-      <c r="F40" s="50">
+      <c r="F41" s="50">
         <f t="shared" si="7"/>
         <v>-0.52299646283063583</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G41" s="7">
         <v>2253.0352269814616</v>
       </c>
-      <c r="H40" s="50">
+      <c r="H41" s="50">
         <f t="shared" si="8"/>
         <v>-0.48831562235438852</v>
       </c>
-      <c r="I40" s="7">
+      <c r="I41" s="7">
         <v>2523.6324429060996</v>
       </c>
-      <c r="J40" s="50">
+      <c r="J41" s="50">
         <f t="shared" si="9"/>
         <v>-0.21087947062519341</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K41" s="7">
         <v>2257.5454063687112</v>
       </c>
-      <c r="L40" s="50">
+      <c r="L41" s="50">
         <f t="shared" si="10"/>
         <v>-0.44645869737254662</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B41" s="49">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="49">
         <v>2010</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C42" s="7">
         <v>2895.9811210541056</v>
       </c>
-      <c r="D41" s="50">
+      <c r="D42" s="50">
         <f t="shared" si="6"/>
         <v>0.58700263424303856</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E42" s="7">
         <v>3289.9073846842039</v>
       </c>
-      <c r="F41" s="50">
+      <c r="F42" s="50">
         <f t="shared" si="7"/>
         <v>0.52543752067353444</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G42" s="7">
         <v>3545.4568090652383</v>
       </c>
-      <c r="H41" s="50">
+      <c r="H42" s="50">
         <f t="shared" si="8"/>
         <v>0.57363576326115329</v>
       </c>
-      <c r="I41" s="7">
+      <c r="I42" s="7">
         <v>3581.7244891354485</v>
       </c>
-      <c r="J41" s="50">
+      <c r="J42" s="50">
         <f t="shared" si="9"/>
         <v>0.4192734362738253</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K42" s="7">
         <v>3352.8629248323873</v>
       </c>
-      <c r="L41" s="50">
+      <c r="L42" s="50">
         <f t="shared" si="10"/>
         <v>0.48518072565614867</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="49">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="49">
         <v>2011</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C43" s="7">
         <v>3835.8830823505277</v>
       </c>
-      <c r="D42" s="51">
+      <c r="D43" s="51">
         <f t="shared" si="6"/>
         <v>0.32455389797372303</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E43" s="7">
         <v>4738.7894964645729</v>
       </c>
-      <c r="F42" s="51">
+      <c r="F43" s="51">
         <f t="shared" si="7"/>
         <v>0.44040209719139134</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G43" s="7">
         <v>4450.6283956737261</v>
       </c>
-      <c r="H42" s="51">
+      <c r="H43" s="51">
         <f t="shared" si="8"/>
         <v>0.25530464347897008</v>
       </c>
-      <c r="I42" s="7">
+      <c r="I43" s="7">
         <v>4134.1995587376068</v>
       </c>
-      <c r="J42" s="51">
+      <c r="J43" s="51">
         <f t="shared" si="9"/>
         <v>0.15424834357807171</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K43" s="7">
         <v>4297.383210370067</v>
       </c>
-      <c r="L42" s="51">
+      <c r="L43" s="51">
         <f t="shared" si="10"/>
         <v>0.28170560703280079</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B43" s="49">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" s="49">
         <v>2012</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C44" s="7">
         <v>3957.101022558687</v>
       </c>
-      <c r="D43" s="51">
+      <c r="D44" s="51">
         <f t="shared" si="6"/>
         <v>3.1601051858410667E-2</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E44" s="7">
         <v>4032.2832725450903</v>
       </c>
-      <c r="F43" s="51">
+      <c r="F44" s="51">
         <f t="shared" si="7"/>
         <v>-0.14909002065750743</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G44" s="7">
         <v>3576.3278236444426</v>
       </c>
-      <c r="H43" s="51">
+      <c r="H44" s="51">
         <f t="shared" si="8"/>
         <v>-0.19644429826564613</v>
       </c>
-      <c r="I43" s="7">
+      <c r="I44" s="7">
         <v>3444.3851166516447</v>
       </c>
-      <c r="J43" s="51">
+      <c r="J44" s="51">
         <f t="shared" si="9"/>
         <v>-0.16685562278386956</v>
       </c>
-      <c r="K43" s="7">
+      <c r="K44" s="7">
         <v>3725.1978364854504</v>
       </c>
-      <c r="L43" s="51">
+      <c r="L44" s="51">
         <f t="shared" si="10"/>
         <v>-0.13314739362872485</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B44" s="49">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B45" s="49">
         <v>2013</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C45" s="7">
         <v>3858.7469943949272</v>
       </c>
-      <c r="D44" s="51">
+      <c r="D45" s="51">
         <f t="shared" si="6"/>
         <v>-2.4855071326979505E-2</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E45" s="7">
         <v>4190.9959214620685</v>
       </c>
-      <c r="F44" s="51">
+      <c r="F45" s="51">
         <f t="shared" si="7"/>
         <v>3.9360490865713027E-2</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G45" s="7">
         <v>4754.147857864863</v>
       </c>
-      <c r="H44" s="51">
+      <c r="H45" s="51">
         <f t="shared" si="8"/>
         <v>0.32933782703962744</v>
       </c>
-      <c r="I44" s="7">
+      <c r="I45" s="7">
         <v>4984.6860939625894</v>
       </c>
-      <c r="J44" s="51">
+      <c r="J45" s="51">
         <f t="shared" si="9"/>
         <v>0.44719185722422994</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K45" s="7">
         <v>4539.2744852213418</v>
       </c>
-      <c r="L44" s="51">
+      <c r="L45" s="51">
         <f t="shared" si="10"/>
         <v>0.21853246041395069</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B45" s="49">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" s="49">
         <v>2014</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C46" s="7">
         <v>5040.9242292535691</v>
       </c>
-      <c r="D45" s="51">
+      <c r="D46" s="51">
         <f t="shared" si="6"/>
         <v>0.30636298170774823</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E46" s="7">
         <v>5144.219232161875</v>
       </c>
-      <c r="F45" s="51">
+      <c r="F46" s="51">
         <f t="shared" si="7"/>
         <v>0.22744553527679545</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G46" s="7">
         <v>4737.1885266533545</v>
       </c>
-      <c r="H45" s="51">
+      <c r="H46" s="51">
         <f t="shared" si="8"/>
         <v>-3.5672704590902216E-3</v>
       </c>
-      <c r="I45" s="7">
+      <c r="I46" s="7">
         <v>4050.7901758453304</v>
       </c>
-      <c r="J45" s="51">
+      <c r="J46" s="51">
         <f t="shared" si="9"/>
         <v>-0.18735300488598194</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K46" s="7">
         <v>4867.3576837397432</v>
       </c>
-      <c r="L45" s="51">
+      <c r="L46" s="51">
         <f t="shared" si="10"/>
         <v>7.2276571858906458E-2</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B46" s="49">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" s="49">
         <v>2015</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C47" s="7">
         <v>2827.8605664970801</v>
       </c>
-      <c r="D46" s="51">
+      <c r="D47" s="51">
         <f t="shared" si="6"/>
         <v>-0.43901942622220025</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E47" s="7">
         <v>2817.6265190826502</v>
       </c>
-      <c r="F46" s="51">
+      <c r="F47" s="51">
         <f t="shared" si="7"/>
         <v>-0.45227324265911317</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G47" s="7">
         <v>3016.091048332798</v>
       </c>
-      <c r="H46" s="51">
+      <c r="H47" s="51">
         <f t="shared" si="8"/>
         <v>-0.36331623042590777</v>
       </c>
-      <c r="I46" s="7">
+      <c r="I47" s="7">
         <v>3155.9058681462147</v>
       </c>
-      <c r="J46" s="51">
+      <c r="J47" s="51">
         <f t="shared" si="9"/>
         <v>-0.22091598647475452</v>
       </c>
-      <c r="K46" s="7">
+      <c r="K47" s="7">
         <v>2968.9448377870258</v>
       </c>
-      <c r="L46" s="51">
+      <c r="L47" s="51">
         <f t="shared" si="10"/>
         <v>-0.39002945115266474</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B47" s="49">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B48" s="49">
         <v>2016</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C48" s="7">
         <v>2380.0605990871172</v>
       </c>
-      <c r="D47" s="51">
+      <c r="D48" s="51">
         <f t="shared" si="6"/>
         <v>-0.15835291623471393</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E48" s="7">
         <v>2368.6334069944724</v>
       </c>
-      <c r="F47" s="51">
+      <c r="F48" s="51">
         <f t="shared" si="7"/>
         <v>-0.15935153543144498</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G48" s="7">
         <v>2587.1485529948905</v>
       </c>
-      <c r="H47" s="51">
+      <c r="H48" s="51">
         <f t="shared" si="8"/>
         <v>-0.14221801943777979</v>
       </c>
-      <c r="I47" s="7">
+      <c r="I48" s="7">
         <v>2833.3991176737331</v>
       </c>
-      <c r="J47" s="51">
+      <c r="J48" s="51">
         <f t="shared" si="9"/>
         <v>-0.10219149871600031</v>
       </c>
-      <c r="K47" s="7">
+      <c r="K48" s="7">
         <v>2509.6306131686624</v>
       </c>
-      <c r="L47" s="51">
+      <c r="L48" s="51">
         <f t="shared" si="10"/>
         <v>-0.15470621709520349</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B48" s="49">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" s="49">
         <v>2017</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C49" s="7">
         <v>3286.7952666345332</v>
       </c>
-      <c r="D48" s="51">
+      <c r="D49" s="51">
         <f t="shared" si="6"/>
         <v>0.38097125253667818</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E49" s="7">
         <v>3403.3950399280184</v>
       </c>
-      <c r="F48" s="51">
+      <c r="F49" s="51">
         <f t="shared" si="7"/>
         <v>0.43686018692379314</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G49" s="7">
         <v>3133.8206802167783</v>
       </c>
-      <c r="H48" s="51">
+      <c r="H49" s="51">
         <f t="shared" si="8"/>
         <v>0.21130295227502827</v>
       </c>
-      <c r="I48" s="7">
+      <c r="I49" s="7">
         <v>3047.4874064124324</v>
       </c>
-      <c r="J48" s="51">
+      <c r="J49" s="51">
         <f t="shared" si="9"/>
         <v>7.5558818171182818E-2</v>
       </c>
-      <c r="K48" s="7">
+      <c r="K49" s="7">
         <v>3190.3522505405317</v>
       </c>
-      <c r="L48" s="51">
+      <c r="L49" s="51">
         <f t="shared" si="10"/>
         <v>0.27124375746771334</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B49" s="49">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B50" s="49">
         <v>2018</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C50" s="7">
         <v>3038.9966755135433</v>
       </c>
-      <c r="D49" s="51">
+      <c r="D50" s="51">
         <f t="shared" si="6"/>
         <v>-7.5392158932588327E-2</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E50" s="7">
         <v>3097.826480080575</v>
       </c>
-      <c r="F49" s="51">
+      <c r="F50" s="51">
         <f t="shared" si="7"/>
         <v>-8.9783453364234211E-2</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G50" s="7">
         <v>3103.4033939281435</v>
       </c>
-      <c r="H49" s="51">
-        <f>G49/G48-1</f>
+      <c r="H50" s="51">
+        <f>G50/G49-1</f>
         <v>-9.7061349044804679E-3</v>
       </c>
-      <c r="I49" s="7">
+      <c r="I50" s="7">
         <v>2758.5934377305066</v>
       </c>
-      <c r="J49" s="51">
+      <c r="J50" s="51">
         <f t="shared" si="9"/>
         <v>-9.4797428226953029E-2</v>
       </c>
-      <c r="K49" s="7">
+      <c r="K50" s="7">
         <v>2971.6834233768363</v>
       </c>
-      <c r="L49" s="51">
+      <c r="L50" s="51">
         <f t="shared" si="10"/>
         <v>-6.8540653191711653E-2</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B50" s="49">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="49">
         <v>2019</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C51" s="7">
         <v>2841.3510481471912</v>
       </c>
-      <c r="D50" s="51">
+      <c r="D51" s="51">
         <f t="shared" si="6"/>
         <v>-6.5036473701621578E-2</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E51" s="7">
         <v>3023.0265612645017</v>
       </c>
-      <c r="F50" s="51">
+      <c r="F51" s="51">
         <f t="shared" si="7"/>
         <v>-2.414593564134293E-2</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G51" s="7">
         <v>3252.5151433781903</v>
       </c>
-      <c r="H50" s="51">
-        <f>G50/G49-1</f>
+      <c r="H51" s="51">
+        <f>G51/G50-1</f>
         <v>4.8047814132634592E-2</v>
       </c>
-      <c r="I50" s="7">
+      <c r="I51" s="7">
         <v>3102.3998117329097</v>
       </c>
-      <c r="J50" s="51">
+      <c r="J51" s="51">
         <f t="shared" si="9"/>
         <v>0.12463104178383477</v>
       </c>
-      <c r="K50" s="7">
+      <c r="K51" s="7">
         <v>3067.9733448340639</v>
       </c>
-      <c r="L50" s="51">
+      <c r="L51" s="51">
         <f t="shared" si="10"/>
         <v>3.2402482949482447E-2</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B51" s="49">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="49">
         <v>2020</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C52" s="7">
         <v>3234.8600184864331</v>
       </c>
-      <c r="D51" s="51">
+      <c r="D52" s="51">
         <f t="shared" si="6"/>
         <v>0.13849361225387624</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E52" s="7">
         <v>3054.3011680353575</v>
       </c>
-      <c r="F51" s="51">
-        <f>E51/E50-1</f>
+      <c r="F52" s="51">
+        <f>E52/E51-1</f>
         <v>1.0345462117863136E-2</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G52" s="7">
         <v>2948.0524163405867</v>
       </c>
-      <c r="H51" s="51">
-        <f>G51/G50-1</f>
+      <c r="H52" s="51">
+        <f>G52/G51-1</f>
         <v>-9.3608396461261845E-2</v>
       </c>
-      <c r="I51" s="7">
+      <c r="I52" s="7">
         <v>3049.0464740490715</v>
       </c>
-      <c r="J51" s="51">
+      <c r="J52" s="51">
         <f t="shared" si="9"/>
         <v>-1.7197440988122259E-2</v>
       </c>
-      <c r="K51" s="7">
+      <c r="K52" s="7">
         <v>3055.2952327107132</v>
       </c>
-      <c r="L51" s="51">
+      <c r="L52" s="51">
         <f t="shared" si="10"/>
         <v>-4.1324062168592857E-3</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B52" s="49">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="49">
         <v>2021</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C53" s="7">
         <v>3136.0775770516107</v>
       </c>
-      <c r="D52" s="51">
+      <c r="D53" s="51">
         <f t="shared" si="6"/>
         <v>-3.0536851941136534E-2</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E53" s="7">
         <v>3534.1207184238669</v>
       </c>
-      <c r="F52" s="51">
-        <f>E52/E51-1</f>
+      <c r="F53" s="51">
+        <f>E53/E52-1</f>
         <v>0.15709634511816906</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G53" s="7">
         <v>3778.8153650089921</v>
       </c>
-      <c r="H52" s="51">
-        <f>G52/G51-1</f>
+      <c r="H53" s="51">
+        <f>G53/G52-1</f>
         <v>0.2818006030230733</v>
       </c>
-      <c r="I52" s="7">
+      <c r="I53" s="7">
         <v>3474.450637724156</v>
       </c>
-      <c r="J52" s="51">
+      <c r="J53" s="51">
         <f t="shared" si="9"/>
         <v>0.13952039343964362</v>
       </c>
-      <c r="K52" s="7">
+      <c r="K53" s="7">
         <v>3479.3424705553466</v>
       </c>
-      <c r="L52" s="51">
+      <c r="L53" s="51">
         <f t="shared" si="10"/>
         <v>0.13879092053189601</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B53" s="49">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="49">
         <v>2022</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C54" s="7">
         <v>3750.3705695165791</v>
       </c>
-      <c r="D53" s="51">
+      <c r="D54" s="51">
         <v>0.19587939946386701</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E54" s="7">
         <v>4248.5048122900907</v>
       </c>
-      <c r="F53" s="51">
+      <c r="F54" s="51">
         <v>0.20213913184743215</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G54" s="7">
         <v>4164.9651589494906</v>
       </c>
-      <c r="H53" s="51">
+      <c r="H54" s="51">
         <v>0.10218805541973852</v>
       </c>
-      <c r="I53" s="7">
+      <c r="I54" s="7">
         <v>3842.6362679890763</v>
       </c>
-      <c r="J53" s="51">
+      <c r="J54" s="51">
         <f t="shared" si="9"/>
         <v>0.10596945205302744</v>
       </c>
-      <c r="K53" s="7">
+      <c r="K54" s="7">
         <v>3993.0058664974749</v>
       </c>
-      <c r="L53" s="51">
+      <c r="L54" s="51">
         <f t="shared" si="10"/>
         <v>0.14763231854556169</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B54" s="49">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="49">
         <v>2023</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C55" s="7">
         <v>3719.3333714125952</v>
       </c>
-      <c r="D54" s="51">
+      <c r="D55" s="51">
         <v>-8.2757683617340483E-3</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E55" s="7">
         <v>3835.6119024412283</v>
       </c>
-      <c r="F54" s="51">
+      <c r="F55" s="51">
         <v>-9.7185463614032908E-2</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G55" s="7">
         <v>3493.3487378734922</v>
       </c>
-      <c r="H54" s="51">
+      <c r="H55" s="51">
         <v>-0.16125379095497572</v>
       </c>
-      <c r="I54" s="7">
+      <c r="I55" s="7">
         <v>3244.9284011941795</v>
       </c>
-      <c r="J54" s="51">
+      <c r="J55" s="51">
         <f t="shared" si="9"/>
         <v>-0.15554630339958986</v>
       </c>
-      <c r="K54" s="7">
+      <c r="K55" s="7">
         <v>3564.5331020541021</v>
       </c>
-      <c r="L54" s="51">
+      <c r="L55" s="51">
         <f t="shared" si="10"/>
         <v>-0.10730581891661839</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B55" s="49">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B56" s="49">
         <v>2024</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C56" s="7">
         <v>3363.8833444771735</v>
       </c>
-      <c r="D55" s="51">
-        <f>+C55/C53-1</f>
+      <c r="D56" s="51">
+        <f>+C56/C54-1</f>
         <v>-0.10305307645618167</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E56" s="7">
         <v>3560.0227093300723</v>
       </c>
-      <c r="F55" s="51">
-        <f>+E55/E53-1</f>
+      <c r="F56" s="51">
+        <f>+E56/E54-1</f>
         <v>-0.16205280054488225</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G56" s="7">
         <v>3598.9310570770144</v>
       </c>
-      <c r="H55" s="51">
-        <f>+G55/G53-1</f>
+      <c r="H56" s="51">
+        <f>+G56/G54-1</f>
         <v>-0.13590368232882033</v>
       </c>
-      <c r="I55" s="7">
+      <c r="I56" s="7">
         <v>3652.2004904128717</v>
       </c>
-      <c r="J55" s="51">
+      <c r="J56" s="51">
         <f t="shared" si="9"/>
         <v>0.12551034687508378</v>
       </c>
-      <c r="K55" s="7">
+      <c r="K56" s="7">
         <v>3554.1422956246934</v>
       </c>
-      <c r="L55" s="51">
+      <c r="L56" s="51">
         <f t="shared" si="10"/>
         <v>-2.9150539865714364E-3</v>
       </c>
     </row>
-    <row r="56" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="52">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B57" s="49">
         <v>2025</v>
       </c>
-      <c r="C56" s="53">
+      <c r="C57" s="7">
         <v>3903.4342963063086</v>
       </c>
-      <c r="D56" s="54">
+      <c r="D57" s="51">
         <v>0.15500639618082168</v>
       </c>
-      <c r="E56" s="53">
+      <c r="E57" s="7">
         <v>4053.6116654316579</v>
       </c>
-      <c r="F56" s="54">
+      <c r="F57" s="51">
         <v>0.14671723434653061</v>
       </c>
-      <c r="G56" s="53">
+      <c r="G57" s="7">
         <v>4089.4408764903569</v>
       </c>
-      <c r="H56" s="54">
-        <f>+G56/G55-1</f>
+      <c r="H57" s="51">
         <v>0.13629319696157927</v>
       </c>
-      <c r="I56" s="53">
+      <c r="I57" s="7">
         <v>3886.8153414884118</v>
       </c>
-      <c r="J56" s="54">
-        <f t="shared" si="9"/>
+      <c r="J57" s="51">
         <v>6.4239313173362289E-2</v>
       </c>
-      <c r="K56" s="53">
+      <c r="K57" s="7">
         <v>3978.4184285259516</v>
       </c>
-      <c r="L56" s="54">
-        <f t="shared" si="10"/>
+      <c r="L57" s="51">
         <v>0.11937511152087543</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C57" s="55" t="s">
+    <row r="58" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="52">
+        <v>2026</v>
+      </c>
+      <c r="C58" s="53">
+        <v>3616.7126945353939</v>
+      </c>
+      <c r="D58" s="54">
+        <f>+C58/C57-1</f>
+        <v>-7.3453676943462276E-2</v>
+      </c>
+      <c r="E58" s="53"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="54"/>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="55" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
-      <c r="H58" s="86"/>
-      <c r="I58" s="86"/>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
-      <c r="H59" s="86"/>
-      <c r="I59" s="86"/>
-    </row>
-    <row r="62" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="57" t="s">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E60" s="86"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="86"/>
+      <c r="H60" s="86"/>
+      <c r="I60" s="86"/>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
+      <c r="H61" s="86"/>
+      <c r="I61" s="86"/>
+    </row>
+    <row r="64" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="57" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="57"/>
-    </row>
-    <row r="64" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="121">
-        <v>2025</v>
-      </c>
-      <c r="D64" s="122"/>
-      <c r="E64" s="122"/>
-      <c r="F64" s="122"/>
-      <c r="G64" s="122"/>
-      <c r="H64" s="122"/>
-      <c r="I64" s="122"/>
-      <c r="J64" s="122"/>
-      <c r="K64" s="122"/>
-      <c r="L64" s="123"/>
-    </row>
-    <row r="65" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="58" t="s">
+    <row r="65" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="57"/>
+    </row>
+    <row r="66" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="121">
+        <v>2026</v>
+      </c>
+      <c r="D66" s="122"/>
+      <c r="E66" s="122"/>
+      <c r="F66" s="122"/>
+      <c r="G66" s="122"/>
+      <c r="H66" s="122"/>
+      <c r="I66" s="122"/>
+      <c r="J66" s="122"/>
+      <c r="K66" s="122"/>
+      <c r="L66" s="123"/>
+    </row>
+    <row r="67" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C65" s="127" t="s">
+      <c r="C67" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D65" s="128"/>
-      <c r="E65" s="127" t="s">
+      <c r="D67" s="128"/>
+      <c r="E67" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F65" s="129"/>
-      <c r="G65" s="127" t="s">
+      <c r="F67" s="129"/>
+      <c r="G67" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H65" s="128"/>
-      <c r="I65" s="129" t="s">
+      <c r="H67" s="128"/>
+      <c r="I67" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J65" s="128"/>
-      <c r="K65" s="129" t="s">
+      <c r="J67" s="128"/>
+      <c r="K67" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L65" s="128"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B66" s="59">
+      <c r="L67" s="128"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B68" s="59">
         <v>1</v>
       </c>
-      <c r="C66" s="60" t="s">
+      <c r="C68" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D66" s="61">
-        <v>0.44059640344190504</v>
-      </c>
-      <c r="E66" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="61">
-        <v>0.50080837170666626</v>
-      </c>
-      <c r="G66" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="H66" s="61">
-        <v>0.52251749239823853</v>
-      </c>
-      <c r="I66" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="J66" s="61">
-        <v>0.52</v>
-      </c>
-      <c r="K66" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="L66" s="61">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B67" s="62">
-        <v>2</v>
-      </c>
-      <c r="C67" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D67" s="64">
-        <v>0.31652504155270544</v>
-      </c>
-      <c r="E67" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="F67" s="64">
-        <v>0.18419696969590921</v>
-      </c>
-      <c r="G67" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="H67" s="64">
-        <v>0.2151208314273656</v>
-      </c>
-      <c r="I67" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="J67" s="64">
-        <v>0.22</v>
-      </c>
-      <c r="K67" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="L67" s="64">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B68" s="62">
-        <v>3</v>
-      </c>
-      <c r="C68" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="D68" s="64">
-        <v>5.488593345465434E-2</v>
-      </c>
-      <c r="E68" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="F68" s="64">
-        <v>4.4394477423385405E-2</v>
-      </c>
-      <c r="G68" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="H68" s="64">
-        <v>4.5506114778961923E-2</v>
-      </c>
-      <c r="I68" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="J68" s="64">
-        <v>0.05</v>
-      </c>
-      <c r="K68" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="L68" s="64">
-        <v>0.05</v>
-      </c>
+      <c r="D68" s="61">
+        <v>0.42775763889315399</v>
+      </c>
+      <c r="E68" s="60"/>
+      <c r="F68" s="61"/>
+      <c r="G68" s="60"/>
+      <c r="H68" s="61"/>
+      <c r="I68" s="60"/>
+      <c r="J68" s="61"/>
+      <c r="K68" s="60"/>
+      <c r="L68" s="61"/>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B69" s="62">
+        <v>2</v>
+      </c>
+      <c r="C69" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D69" s="64">
+        <v>0.30671046829801124</v>
+      </c>
+      <c r="E69" s="63"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="64"/>
+      <c r="I69" s="63"/>
+      <c r="J69" s="64"/>
+      <c r="K69" s="63"/>
+      <c r="L69" s="64"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B70" s="62">
+        <v>3</v>
+      </c>
+      <c r="C70" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="D70" s="64">
+        <v>4.4019583367787392E-2</v>
+      </c>
+      <c r="E70" s="63"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="63"/>
+      <c r="H70" s="64"/>
+      <c r="I70" s="63"/>
+      <c r="J70" s="64"/>
+      <c r="K70" s="63"/>
+      <c r="L70" s="64"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B71" s="62">
         <v>4</v>
       </c>
-      <c r="C69" s="65" t="s">
-        <v>83</v>
-      </c>
-      <c r="D69" s="66">
-        <v>3.1957790530866857E-2</v>
-      </c>
-      <c r="E69" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="F69" s="64">
-        <v>4.1240370211613933E-2</v>
-      </c>
-      <c r="G69" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="H69" s="64">
-        <v>2.8974491275507028E-2</v>
-      </c>
-      <c r="I69" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="J69" s="64">
-        <v>0.04</v>
-      </c>
-      <c r="K69" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="L69" s="64">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="67">
+      <c r="C71" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="66">
+        <v>2.6975318259112924E-2</v>
+      </c>
+      <c r="E71" s="63"/>
+      <c r="F71" s="64"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="64"/>
+      <c r="I71" s="63"/>
+      <c r="J71" s="64"/>
+      <c r="K71" s="63"/>
+      <c r="L71" s="64"/>
+    </row>
+    <row r="72" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="67">
         <v>5</v>
       </c>
-      <c r="C70" s="68" t="s">
-        <v>44</v>
-      </c>
-      <c r="D70" s="69">
-        <v>2.7953357851860587E-2</v>
-      </c>
-      <c r="E70" s="70" t="s">
-        <v>84</v>
-      </c>
-      <c r="F70" s="71">
-        <v>3.8278014174316498E-2</v>
-      </c>
-      <c r="G70" s="70" t="s">
-        <v>80</v>
-      </c>
-      <c r="H70" s="71">
-        <v>2.0367690389506091E-2</v>
-      </c>
-      <c r="I70" s="70" t="s">
-        <v>80</v>
-      </c>
-      <c r="J70" s="71">
-        <v>0.02</v>
-      </c>
-      <c r="K70" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="L70" s="71">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="71" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="57"/>
-    </row>
-    <row r="72" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="121">
-        <v>2024</v>
-      </c>
-      <c r="D72" s="122"/>
-      <c r="E72" s="122"/>
-      <c r="F72" s="122"/>
-      <c r="G72" s="122"/>
-      <c r="H72" s="122"/>
-      <c r="I72" s="122"/>
-      <c r="J72" s="122"/>
-      <c r="K72" s="122"/>
-      <c r="L72" s="123"/>
-    </row>
-    <row r="73" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="58" t="s">
+      <c r="C72" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" s="69">
+        <v>2.6262356589528607E-2</v>
+      </c>
+      <c r="E72" s="70"/>
+      <c r="F72" s="71"/>
+      <c r="G72" s="70"/>
+      <c r="H72" s="71"/>
+      <c r="I72" s="70"/>
+      <c r="J72" s="71"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="71"/>
+    </row>
+    <row r="73" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="57"/>
+    </row>
+    <row r="74" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="121">
+        <v>2025</v>
+      </c>
+      <c r="D74" s="122"/>
+      <c r="E74" s="122"/>
+      <c r="F74" s="122"/>
+      <c r="G74" s="122"/>
+      <c r="H74" s="122"/>
+      <c r="I74" s="122"/>
+      <c r="J74" s="122"/>
+      <c r="K74" s="122"/>
+      <c r="L74" s="123"/>
+    </row>
+    <row r="75" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C73" s="127" t="s">
+      <c r="C75" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D73" s="128"/>
-      <c r="E73" s="127" t="s">
+      <c r="D75" s="128"/>
+      <c r="E75" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F73" s="129"/>
-      <c r="G73" s="127" t="s">
+      <c r="F75" s="129"/>
+      <c r="G75" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H73" s="128"/>
-      <c r="I73" s="129" t="s">
+      <c r="H75" s="128"/>
+      <c r="I75" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J73" s="128"/>
-      <c r="K73" s="129" t="s">
+      <c r="J75" s="128"/>
+      <c r="K75" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L73" s="128"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B74" s="59">
+      <c r="L75" s="128"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B76" s="59">
         <v>1</v>
       </c>
-      <c r="C74" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="D74" s="61">
-        <v>0.37966273780836834</v>
-      </c>
-      <c r="E74" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="F74" s="61">
-        <v>0.4564067604317007</v>
-      </c>
-      <c r="G74" s="60" t="s">
+      <c r="C76" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="H74" s="61">
-        <v>0.45571508010226686</v>
-      </c>
-      <c r="I74" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="J74" s="61">
-        <v>0.4060592218816978</v>
-      </c>
-      <c r="K74" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="L74" s="61">
-        <v>0.37855793797558207</v>
-      </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B75" s="62">
-        <v>2</v>
-      </c>
-      <c r="C75" s="63" t="s">
+      <c r="D76" s="61">
+        <v>0.44059640344190504</v>
+      </c>
+      <c r="E76" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D75" s="64">
-        <v>0.30764870819298079</v>
-      </c>
-      <c r="E75" s="63" t="s">
+      <c r="F76" s="61">
+        <v>0.50080837170666626</v>
+      </c>
+      <c r="G76" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="F75" s="64">
-        <v>0.31424050786063201</v>
-      </c>
-      <c r="G75" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="H75" s="64">
-        <v>0.27940453054783559</v>
-      </c>
-      <c r="I75" s="63" t="s">
+      <c r="H76" s="61">
+        <v>0.52251749239823853</v>
+      </c>
+      <c r="I76" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="J75" s="64">
-        <v>0.38318905940527059</v>
-      </c>
-      <c r="K75" s="63" t="s">
+      <c r="J76" s="61">
+        <v>0.52</v>
+      </c>
+      <c r="K76" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="L75" s="64">
-        <v>0.36796716764609144</v>
-      </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B76" s="62">
-        <v>3</v>
-      </c>
-      <c r="C76" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="D76" s="64">
-        <v>4.2509686019168359E-2</v>
-      </c>
-      <c r="E76" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="64">
-        <v>4.437795936212878E-2</v>
-      </c>
-      <c r="G76" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="H76" s="64">
-        <v>6.2689604690041451E-2</v>
-      </c>
-      <c r="I76" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="J76" s="64">
-        <v>3.7434485964625057E-2</v>
-      </c>
-      <c r="K76" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="L76" s="64">
-        <v>2.7872190885371319E-2</v>
+      <c r="L76" s="61">
+        <v>0.49</v>
       </c>
     </row>
     <row r="77" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B77" s="62">
+        <v>2</v>
+      </c>
+      <c r="C77" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D77" s="64">
+        <v>0.31652504155270544</v>
+      </c>
+      <c r="E77" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" s="64">
+        <v>0.18419696969590921</v>
+      </c>
+      <c r="G77" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H77" s="64">
+        <v>0.2151208314273656</v>
+      </c>
+      <c r="I77" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="J77" s="64">
+        <v>0.22</v>
+      </c>
+      <c r="K77" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="L77" s="64">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B78" s="62">
+        <v>3</v>
+      </c>
+      <c r="C78" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="D78" s="64">
+        <v>5.488593345465434E-2</v>
+      </c>
+      <c r="E78" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="F78" s="64">
+        <v>4.4394477423385405E-2</v>
+      </c>
+      <c r="G78" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="H78" s="64">
+        <v>4.5506114778961923E-2</v>
+      </c>
+      <c r="I78" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="J78" s="64">
+        <v>0.05</v>
+      </c>
+      <c r="K78" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="L78" s="64">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B79" s="62">
         <v>4</v>
       </c>
-      <c r="C77" s="65" t="s">
+      <c r="C79" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="D79" s="66">
+        <v>3.1957790530866857E-2</v>
+      </c>
+      <c r="E79" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="F79" s="64">
+        <v>4.1240370211613933E-2</v>
+      </c>
+      <c r="G79" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="H79" s="64">
+        <v>2.8974491275507028E-2</v>
+      </c>
+      <c r="I79" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="J79" s="64">
+        <v>0.04</v>
+      </c>
+      <c r="K79" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="L79" s="64">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="67">
+        <v>5</v>
+      </c>
+      <c r="C80" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D77" s="66">
+      <c r="D80" s="69">
+        <v>2.7953357851860587E-2</v>
+      </c>
+      <c r="E80" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="F80" s="71">
+        <v>3.8278014174316498E-2</v>
+      </c>
+      <c r="G80" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="H80" s="71">
+        <v>2.0367690389506091E-2</v>
+      </c>
+      <c r="I80" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="J80" s="71">
+        <v>0.02</v>
+      </c>
+      <c r="K80" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="L80" s="71">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="57"/>
+    </row>
+    <row r="82" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C82" s="121">
+        <v>2024</v>
+      </c>
+      <c r="D82" s="122"/>
+      <c r="E82" s="122"/>
+      <c r="F82" s="122"/>
+      <c r="G82" s="122"/>
+      <c r="H82" s="122"/>
+      <c r="I82" s="122"/>
+      <c r="J82" s="122"/>
+      <c r="K82" s="122"/>
+      <c r="L82" s="123"/>
+    </row>
+    <row r="83" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C83" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" s="128"/>
+      <c r="E83" s="127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F83" s="129"/>
+      <c r="G83" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="H83" s="128"/>
+      <c r="I83" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="J83" s="128"/>
+      <c r="K83" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L83" s="128"/>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B84" s="59">
+        <v>1</v>
+      </c>
+      <c r="C84" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" s="61">
+        <v>0.37966273780836834</v>
+      </c>
+      <c r="E84" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="F84" s="61">
+        <v>0.4564067604317007</v>
+      </c>
+      <c r="G84" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="H84" s="61">
+        <v>0.45571508010226686</v>
+      </c>
+      <c r="I84" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="J84" s="61">
+        <v>0.4060592218816978</v>
+      </c>
+      <c r="K84" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="L84" s="61">
+        <v>0.37855793797558207</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B85" s="62">
+        <v>2</v>
+      </c>
+      <c r="C85" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="D85" s="64">
+        <v>0.30764870819298079</v>
+      </c>
+      <c r="E85" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F85" s="64">
+        <v>0.31424050786063201</v>
+      </c>
+      <c r="G85" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H85" s="64">
+        <v>0.27940453054783559</v>
+      </c>
+      <c r="I85" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="J85" s="64">
+        <v>0.38318905940527059</v>
+      </c>
+      <c r="K85" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L85" s="64">
+        <v>0.36796716764609144</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B86" s="62">
+        <v>3</v>
+      </c>
+      <c r="C86" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="D86" s="64">
+        <v>4.2509686019168359E-2</v>
+      </c>
+      <c r="E86" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="F86" s="64">
+        <v>4.437795936212878E-2</v>
+      </c>
+      <c r="G86" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="H86" s="64">
+        <v>6.2689604690041451E-2</v>
+      </c>
+      <c r="I86" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="J86" s="64">
+        <v>3.7434485964625057E-2</v>
+      </c>
+      <c r="K86" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="L86" s="64">
+        <v>2.7872190885371319E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B87" s="62">
+        <v>4</v>
+      </c>
+      <c r="C87" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" s="66">
         <v>3.8042092058676827E-2</v>
       </c>
-      <c r="E77" s="63" t="s">
+      <c r="E87" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="F77" s="64">
+      <c r="F87" s="64">
         <v>2.5167685772620137E-2</v>
       </c>
-      <c r="G77" s="63" t="s">
+      <c r="G87" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="H77" s="64">
+      <c r="H87" s="64">
         <v>2.4430839929391768E-2</v>
       </c>
-      <c r="I77" s="63" t="s">
+      <c r="I87" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="J77" s="64">
+      <c r="J87" s="64">
         <v>2.2295379755751469E-2</v>
       </c>
-      <c r="K77" s="63" t="s">
+      <c r="K87" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="L77" s="64">
+      <c r="L87" s="64">
         <v>2.427234204081009E-2</v>
       </c>
     </row>
-    <row r="78" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="67">
+    <row r="88" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B88" s="67">
         <v>5</v>
       </c>
-      <c r="C78" s="68" t="s">
+      <c r="C88" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D78" s="69">
+      <c r="D88" s="69">
         <v>3.7008330967095333E-2</v>
       </c>
-      <c r="E78" s="70" t="s">
+      <c r="E88" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="F78" s="71">
+      <c r="F88" s="71">
         <v>1.971436059675221E-2</v>
       </c>
-      <c r="G78" s="70" t="s">
+      <c r="G88" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="H78" s="71">
+      <c r="H88" s="71">
         <v>2.404303501072395E-2</v>
       </c>
-      <c r="I78" s="70" t="s">
+      <c r="I88" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="J78" s="71">
+      <c r="J88" s="71">
         <v>1.8488982014309548E-2</v>
       </c>
-      <c r="K78" s="70" t="s">
+      <c r="K88" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="L78" s="71">
+      <c r="L88" s="71">
         <v>2.3740361016315673E-2</v>
       </c>
     </row>
-    <row r="79" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="57"/>
-    </row>
-    <row r="80" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="121">
+    <row r="89" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="57"/>
+    </row>
+    <row r="90" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C90" s="121">
         <v>2023</v>
       </c>
-      <c r="D80" s="122"/>
-      <c r="E80" s="122"/>
-      <c r="F80" s="122"/>
-      <c r="G80" s="122"/>
-      <c r="H80" s="122"/>
-      <c r="I80" s="122"/>
-      <c r="J80" s="122"/>
-      <c r="K80" s="122"/>
-      <c r="L80" s="123"/>
-    </row>
-    <row r="81" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="58" t="s">
+      <c r="D90" s="122"/>
+      <c r="E90" s="122"/>
+      <c r="F90" s="122"/>
+      <c r="G90" s="122"/>
+      <c r="H90" s="122"/>
+      <c r="I90" s="122"/>
+      <c r="J90" s="122"/>
+      <c r="K90" s="122"/>
+      <c r="L90" s="123"/>
+    </row>
+    <row r="91" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C81" s="127" t="s">
+      <c r="C91" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="128"/>
-      <c r="E81" s="127" t="s">
+      <c r="D91" s="128"/>
+      <c r="E91" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F81" s="129"/>
-      <c r="G81" s="127" t="s">
+      <c r="F91" s="129"/>
+      <c r="G91" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H81" s="128"/>
-      <c r="I81" s="129" t="s">
+      <c r="H91" s="128"/>
+      <c r="I91" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J81" s="128"/>
-      <c r="K81" s="129" t="s">
+      <c r="J91" s="128"/>
+      <c r="K91" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L81" s="128"/>
-    </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B82" s="59">
+      <c r="L91" s="128"/>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B92" s="59">
         <v>1</v>
       </c>
-      <c r="C82" s="60" t="s">
+      <c r="C92" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D82" s="61">
+      <c r="D92" s="61">
         <v>0.43363069735008247</v>
       </c>
-      <c r="E82" s="60" t="s">
+      <c r="E92" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="F82" s="61">
+      <c r="F92" s="61">
         <v>0.78521102499207984</v>
       </c>
-      <c r="G82" s="60" t="s">
+      <c r="G92" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="H82" s="61">
+      <c r="H92" s="61">
         <v>0.41450464785548008</v>
       </c>
-      <c r="I82" s="60" t="s">
+      <c r="I92" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="J82" s="61">
+      <c r="J92" s="61">
         <v>0.54991699101823965</v>
       </c>
-      <c r="K82" s="60" t="s">
+      <c r="K92" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="L82" s="61">
+      <c r="L92" s="61">
         <v>0.55253010394070678</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B83" s="62">
-        <v>2</v>
-      </c>
-      <c r="C83" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="D83" s="64">
-        <v>0.20977031453676229</v>
-      </c>
-      <c r="E83" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" s="64">
-        <v>7.649819877646713E-2</v>
-      </c>
-      <c r="G83" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="64">
-        <v>0.37392357466572446</v>
-      </c>
-      <c r="I83" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="J83" s="64">
-        <v>0.20223569916128004</v>
-      </c>
-      <c r="K83" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="L83" s="64">
-        <v>0.21065494889285058</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B84" s="62">
-        <v>3</v>
-      </c>
-      <c r="C84" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="D84" s="64">
-        <v>0.10116156866440182</v>
-      </c>
-      <c r="E84" s="63" t="s">
-        <v>48</v>
-      </c>
-      <c r="F84" s="64">
-        <v>2.1957390902846829E-2</v>
-      </c>
-      <c r="G84" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="H84" s="64">
-        <v>4.1080037016603559E-2</v>
-      </c>
-      <c r="I84" s="63" t="s">
-        <v>50</v>
-      </c>
-      <c r="J84" s="64">
-        <v>2.452732172969347E-2</v>
-      </c>
-      <c r="K84" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="L84" s="64">
-        <v>3.1604994427047235E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="2:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B85" s="62">
-        <v>4</v>
-      </c>
-      <c r="C85" s="65" t="s">
-        <v>49</v>
-      </c>
-      <c r="D85" s="66">
-        <v>3.4544013937706487E-2</v>
-      </c>
-      <c r="E85" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="F85" s="64">
-        <v>2.0234160671947488E-2</v>
-      </c>
-      <c r="G85" s="63" t="s">
-        <v>51</v>
-      </c>
-      <c r="H85" s="64">
-        <v>2.1902715559207166E-2</v>
-      </c>
-      <c r="I85" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="J85" s="64">
-        <v>2.1462670150117959E-2</v>
-      </c>
-      <c r="K85" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="L85" s="64">
-        <v>2.7287859262044602E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="2:12" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="67">
-        <v>5</v>
-      </c>
-      <c r="C86" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="D86" s="69">
-        <v>3.1606487483643669E-2</v>
-      </c>
-      <c r="E86" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" s="71">
-        <v>1.80553499906233E-2</v>
-      </c>
-      <c r="G86" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="H86" s="71">
-        <v>1.4139897394631179E-2</v>
-      </c>
-      <c r="I86" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="J86" s="71">
-        <v>2.074889713383354E-2</v>
-      </c>
-      <c r="K86" s="70" t="s">
-        <v>51</v>
-      </c>
-      <c r="L86" s="71">
-        <v>1.7108357510828152E-2</v>
-      </c>
-    </row>
-    <row r="87" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="57"/>
-    </row>
-    <row r="88" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C88" s="121">
-        <v>2022</v>
-      </c>
-      <c r="D88" s="122"/>
-      <c r="E88" s="122"/>
-      <c r="F88" s="122"/>
-      <c r="G88" s="122"/>
-      <c r="H88" s="122"/>
-      <c r="I88" s="122"/>
-      <c r="J88" s="122"/>
-      <c r="K88" s="122"/>
-      <c r="L88" s="123"/>
-    </row>
-    <row r="89" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="C89" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="D89" s="128"/>
-      <c r="E89" s="127" t="s">
-        <v>29</v>
-      </c>
-      <c r="F89" s="129"/>
-      <c r="G89" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="H89" s="128"/>
-      <c r="I89" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="J89" s="128"/>
-      <c r="K89" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="L89" s="128"/>
-    </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B90" s="59">
-        <v>1</v>
-      </c>
-      <c r="C90" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="D90" s="61">
-        <v>0.39668740961219884</v>
-      </c>
-      <c r="E90" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" s="61">
-        <v>0.43249919453036445</v>
-      </c>
-      <c r="G90" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="H90" s="61">
-        <v>0.45412802596879892</v>
-      </c>
-      <c r="I90" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="J90" s="61">
-        <v>0.4099786164302508</v>
-      </c>
-      <c r="K90" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="L90" s="61">
-        <v>0.31375585681687096</v>
-      </c>
-    </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B91" s="62">
-        <v>2</v>
-      </c>
-      <c r="C91" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="D91" s="64">
-        <v>0.27098401412823242</v>
-      </c>
-      <c r="E91" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="F91" s="64">
-        <v>0.20417848505646141</v>
-      </c>
-      <c r="G91" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H91" s="64">
-        <v>0.18718578950639403</v>
-      </c>
-      <c r="I91" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="J91" s="64">
-        <v>0.30281280233342495</v>
-      </c>
-      <c r="K91" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="L91" s="64">
-        <v>0.28768494235253456</v>
-      </c>
-    </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B92" s="62">
-        <v>3</v>
-      </c>
-      <c r="C92" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="D92" s="64">
-        <v>6.0381881383097906E-2</v>
-      </c>
-      <c r="E92" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="F92" s="64">
-        <v>0.12661511227542196</v>
-      </c>
-      <c r="G92" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="H92" s="64">
-        <v>0.13301269634756607</v>
-      </c>
-      <c r="I92" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="J92" s="64">
-        <v>3.5777776369151831E-2</v>
-      </c>
-      <c r="K92" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="L92" s="64">
-        <v>0.1514849705154091</v>
       </c>
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B93" s="62">
+        <v>2</v>
+      </c>
+      <c r="C93" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="D93" s="64">
+        <v>0.20977031453676229</v>
+      </c>
+      <c r="E93" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F93" s="64">
+        <v>7.649819877646713E-2</v>
+      </c>
+      <c r="G93" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H93" s="64">
+        <v>0.37392357466572446</v>
+      </c>
+      <c r="I93" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="J93" s="64">
+        <v>0.20223569916128004</v>
+      </c>
+      <c r="K93" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L93" s="64">
+        <v>0.21065494889285058</v>
+      </c>
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B94" s="62">
+        <v>3</v>
+      </c>
+      <c r="C94" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D94" s="64">
+        <v>0.10116156866440182</v>
+      </c>
+      <c r="E94" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" s="64">
+        <v>2.1957390902846829E-2</v>
+      </c>
+      <c r="G94" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="H94" s="64">
+        <v>4.1080037016603559E-2</v>
+      </c>
+      <c r="I94" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="J94" s="64">
+        <v>2.452732172969347E-2</v>
+      </c>
+      <c r="K94" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="L94" s="64">
+        <v>3.1604994427047235E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="B95" s="62">
         <v>4</v>
       </c>
-      <c r="C93" s="65" t="s">
+      <c r="C95" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="D95" s="66">
+        <v>3.4544013937706487E-2</v>
+      </c>
+      <c r="E95" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F95" s="64">
+        <v>2.0234160671947488E-2</v>
+      </c>
+      <c r="G95" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="H95" s="64">
+        <v>2.1902715559207166E-2</v>
+      </c>
+      <c r="I95" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="J95" s="64">
+        <v>2.1462670150117959E-2</v>
+      </c>
+      <c r="K95" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="L95" s="64">
+        <v>2.7287859262044602E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="2:12" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B96" s="67">
+        <v>5</v>
+      </c>
+      <c r="C96" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="D96" s="69">
+        <v>3.1606487483643669E-2</v>
+      </c>
+      <c r="E96" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="F96" s="71">
+        <v>1.80553499906233E-2</v>
+      </c>
+      <c r="G96" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="H96" s="71">
+        <v>1.4139897394631179E-2</v>
+      </c>
+      <c r="I96" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="J96" s="71">
+        <v>2.074889713383354E-2</v>
+      </c>
+      <c r="K96" s="70" t="s">
+        <v>51</v>
+      </c>
+      <c r="L96" s="71">
+        <v>1.7108357510828152E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B97" s="57"/>
+    </row>
+    <row r="98" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="121">
+        <v>2022</v>
+      </c>
+      <c r="D98" s="122"/>
+      <c r="E98" s="122"/>
+      <c r="F98" s="122"/>
+      <c r="G98" s="122"/>
+      <c r="H98" s="122"/>
+      <c r="I98" s="122"/>
+      <c r="J98" s="122"/>
+      <c r="K98" s="122"/>
+      <c r="L98" s="123"/>
+    </row>
+    <row r="99" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C99" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" s="128"/>
+      <c r="E99" s="127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99" s="129"/>
+      <c r="G99" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99" s="128"/>
+      <c r="I99" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="J99" s="128"/>
+      <c r="K99" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L99" s="128"/>
+    </row>
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B100" s="59">
+        <v>1</v>
+      </c>
+      <c r="C100" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="D100" s="61">
+        <v>0.39668740961219884</v>
+      </c>
+      <c r="E100" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="F100" s="61">
+        <v>0.43249919453036445</v>
+      </c>
+      <c r="G100" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D93" s="66">
-        <v>5.5840871983804254E-2</v>
-      </c>
-      <c r="E93" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="F93" s="64">
-        <v>4.3375638612069292E-2</v>
-      </c>
-      <c r="G93" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="H93" s="64">
-        <v>5.9143369350315118E-2</v>
-      </c>
-      <c r="I93" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="J93" s="64">
-        <v>3.356980915443359E-2</v>
-      </c>
-      <c r="K93" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="L93" s="64">
-        <v>4.5350865323364603E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="67">
-        <v>5</v>
-      </c>
-      <c r="C94" s="68" t="s">
-        <v>54</v>
-      </c>
-      <c r="D94" s="69">
-        <v>5.1726918889161116E-2</v>
-      </c>
-      <c r="E94" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="F94" s="71">
-        <v>3.256851492025116E-2</v>
-      </c>
-      <c r="G94" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="H94" s="71">
-        <v>3.0287284041950222E-2</v>
-      </c>
-      <c r="I94" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="J94" s="71">
-        <v>3.1449244493190455E-2</v>
-      </c>
-      <c r="K94" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="L94" s="71">
-        <v>2.4366116845010558E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B95" s="43"/>
-      <c r="C95" s="55"/>
-      <c r="D95" s="72"/>
-      <c r="E95" s="73"/>
-      <c r="F95" s="72"/>
-      <c r="G95" s="73"/>
-      <c r="H95" s="72"/>
-      <c r="I95" s="73"/>
-      <c r="J95" s="72"/>
-      <c r="K95" s="73"/>
-      <c r="L95" s="74"/>
-    </row>
-    <row r="96" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C97" s="121">
-        <v>2021</v>
-      </c>
-      <c r="D97" s="122"/>
-      <c r="E97" s="122"/>
-      <c r="F97" s="122"/>
-      <c r="G97" s="122"/>
-      <c r="H97" s="122"/>
-      <c r="I97" s="122"/>
-      <c r="J97" s="122"/>
-      <c r="K97" s="122"/>
-      <c r="L97" s="123"/>
-    </row>
-    <row r="98" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="C98" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="D98" s="128"/>
-      <c r="E98" s="127" t="s">
-        <v>29</v>
-      </c>
-      <c r="F98" s="129"/>
-      <c r="G98" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="H98" s="128"/>
-      <c r="I98" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="J98" s="128"/>
-      <c r="K98" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="L98" s="128"/>
-    </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B99" s="59">
-        <v>1</v>
-      </c>
-      <c r="C99" s="60" t="s">
+      <c r="H100" s="61">
+        <v>0.45412802596879892</v>
+      </c>
+      <c r="I100" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D99" s="61">
-        <v>0.29878727200845384</v>
-      </c>
-      <c r="E99" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="F99" s="61">
-        <v>0.32371541515701613</v>
-      </c>
-      <c r="G99" s="60" t="s">
+      <c r="J100" s="61">
+        <v>0.4099786164302508</v>
+      </c>
+      <c r="K100" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="H99" s="61">
-        <v>0.45497213595282182</v>
-      </c>
-      <c r="I99" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="J99" s="61">
-        <v>0.35990782087621853</v>
-      </c>
-      <c r="K99" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="L99" s="61">
-        <v>0.32359467705807943</v>
-      </c>
-    </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B100" s="62">
-        <v>2</v>
-      </c>
-      <c r="C100" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="D100" s="64">
-        <v>0.26337522063977042</v>
-      </c>
-      <c r="E100" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="F100" s="64">
-        <v>0.291047094728834</v>
-      </c>
-      <c r="G100" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="H100" s="64">
-        <v>0.32023820524498292</v>
-      </c>
-      <c r="I100" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="J100" s="64">
-        <v>0.28547656117796083</v>
-      </c>
-      <c r="K100" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="L100" s="64">
-        <v>0.31573708946411477</v>
+      <c r="L100" s="61">
+        <v>0.31375585681687096</v>
       </c>
     </row>
     <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B101" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C101" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D101" s="64">
+        <v>0.27098401412823242</v>
+      </c>
+      <c r="E101" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F101" s="64">
+        <v>0.20417848505646141</v>
+      </c>
+      <c r="G101" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D101" s="64">
-        <v>0.20523172007016927</v>
-      </c>
-      <c r="E101" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="F101" s="64">
-        <v>0.18856434728340798</v>
-      </c>
-      <c r="G101" s="63" t="s">
-        <v>41</v>
-      </c>
       <c r="H101" s="64">
-        <v>0.10148248772591527</v>
+        <v>0.18718578950639403</v>
       </c>
       <c r="I101" s="63" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J101" s="64">
-        <v>9.2032020284980018E-2</v>
+        <v>0.30281280233342495</v>
       </c>
       <c r="K101" s="63" t="s">
         <v>41</v>
       </c>
       <c r="L101" s="64">
-        <v>0.16430447808426896</v>
+        <v>0.28768494235253456</v>
       </c>
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B102" s="62">
+        <v>3</v>
+      </c>
+      <c r="C102" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" s="64">
+        <v>6.0381881383097906E-2</v>
+      </c>
+      <c r="E102" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F102" s="64">
+        <v>0.12661511227542196</v>
+      </c>
+      <c r="G102" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="H102" s="64">
+        <v>0.13301269634756607</v>
+      </c>
+      <c r="I102" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="J102" s="64">
+        <v>3.5777776369151831E-2</v>
+      </c>
+      <c r="K102" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="L102" s="64">
+        <v>0.1514849705154091</v>
+      </c>
+    </row>
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B103" s="62">
         <v>4</v>
       </c>
-      <c r="C102" s="65" t="s">
+      <c r="C103" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="D103" s="66">
+        <v>5.5840871983804254E-2</v>
+      </c>
+      <c r="E103" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="F103" s="64">
+        <v>4.3375638612069292E-2</v>
+      </c>
+      <c r="G103" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="D102" s="66">
-        <v>0.12116779544977975</v>
-      </c>
-      <c r="E102" s="63" t="s">
+      <c r="H103" s="64">
+        <v>5.9143369350315118E-2</v>
+      </c>
+      <c r="I103" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="F102" s="64">
-        <v>3.5642895211350896E-2</v>
-      </c>
-      <c r="G102" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="H102" s="64">
-        <v>2.1484153311571493E-2</v>
-      </c>
-      <c r="I102" s="63" t="s">
+      <c r="J103" s="64">
+        <v>3.356980915443359E-2</v>
+      </c>
+      <c r="K103" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="J102" s="64">
-        <v>5.1728769423881125E-2</v>
-      </c>
-      <c r="K102" s="63" t="s">
+      <c r="L103" s="64">
+        <v>4.5350865323364603E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="67">
+        <v>5</v>
+      </c>
+      <c r="C104" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="L102" s="64">
-        <v>4.6077732550328279E-2</v>
-      </c>
-    </row>
-    <row r="103" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="67">
-        <v>5</v>
-      </c>
-      <c r="C103" s="68" t="s">
-        <v>53</v>
-      </c>
-      <c r="D103" s="69">
-        <v>2.7763813670911144E-2</v>
-      </c>
-      <c r="E103" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="F103" s="71">
-        <v>3.3609956751027376E-2</v>
-      </c>
-      <c r="G103" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="H103" s="71">
-        <v>1.4490724038593415E-2</v>
-      </c>
-      <c r="I103" s="70" t="s">
+      <c r="D104" s="69">
+        <v>5.1726918889161116E-2</v>
+      </c>
+      <c r="E104" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="F104" s="71">
+        <v>3.256851492025116E-2</v>
+      </c>
+      <c r="G104" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="J103" s="71">
-        <v>2.8869966358997898E-2</v>
-      </c>
-      <c r="K103" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="L103" s="71">
-        <v>2.2314726403328145E-2</v>
-      </c>
-    </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B104" s="43"/>
-      <c r="C104" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D104" s="72"/>
-      <c r="E104" s="73"/>
-      <c r="F104" s="72"/>
-      <c r="G104" s="73"/>
-      <c r="H104" s="72"/>
-      <c r="I104" s="73"/>
-      <c r="J104" s="72"/>
-      <c r="K104" s="73"/>
-      <c r="L104" s="74"/>
-    </row>
-    <row r="105" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="106" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C106" s="121">
-        <v>2020</v>
-      </c>
-      <c r="D106" s="122"/>
-      <c r="E106" s="122"/>
-      <c r="F106" s="122"/>
-      <c r="G106" s="122"/>
-      <c r="H106" s="122"/>
-      <c r="I106" s="122"/>
-      <c r="J106" s="122"/>
-      <c r="K106" s="122"/>
-      <c r="L106" s="123"/>
-    </row>
+      <c r="H104" s="71">
+        <v>3.0287284041950222E-2</v>
+      </c>
+      <c r="I104" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="J104" s="71">
+        <v>3.1449244493190455E-2</v>
+      </c>
+      <c r="K104" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="L104" s="71">
+        <v>2.4366116845010558E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B105" s="43"/>
+      <c r="C105" s="55"/>
+      <c r="D105" s="72"/>
+      <c r="E105" s="73"/>
+      <c r="F105" s="72"/>
+      <c r="G105" s="73"/>
+      <c r="H105" s="72"/>
+      <c r="I105" s="73"/>
+      <c r="J105" s="72"/>
+      <c r="K105" s="73"/>
+      <c r="L105" s="74"/>
+    </row>
+    <row r="106" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="58" t="s">
+      <c r="C107" s="121">
+        <v>2021</v>
+      </c>
+      <c r="D107" s="122"/>
+      <c r="E107" s="122"/>
+      <c r="F107" s="122"/>
+      <c r="G107" s="122"/>
+      <c r="H107" s="122"/>
+      <c r="I107" s="122"/>
+      <c r="J107" s="122"/>
+      <c r="K107" s="122"/>
+      <c r="L107" s="123"/>
+    </row>
+    <row r="108" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C107" s="127" t="s">
+      <c r="C108" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D107" s="128"/>
-      <c r="E107" s="127" t="s">
+      <c r="D108" s="128"/>
+      <c r="E108" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F107" s="129"/>
-      <c r="G107" s="127" t="s">
+      <c r="F108" s="129"/>
+      <c r="G108" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H107" s="128"/>
-      <c r="I107" s="129" t="s">
+      <c r="H108" s="128"/>
+      <c r="I108" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J107" s="128"/>
-      <c r="K107" s="129" t="s">
+      <c r="J108" s="128"/>
+      <c r="K108" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L107" s="128"/>
-    </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B108" s="59">
+      <c r="L108" s="128"/>
+    </row>
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B109" s="59">
         <v>1</v>
       </c>
-      <c r="C108" s="60" t="s">
+      <c r="C109" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="D109" s="61">
+        <v>0.29878727200845384</v>
+      </c>
+      <c r="E109" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="F109" s="61">
+        <v>0.32371541515701613</v>
+      </c>
+      <c r="G109" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D108" s="61">
-        <v>0.59401945613555618</v>
-      </c>
-      <c r="E108" s="60" t="s">
+      <c r="H109" s="61">
+        <v>0.45497213595282182</v>
+      </c>
+      <c r="I109" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="J109" s="61">
+        <v>0.35990782087621853</v>
+      </c>
+      <c r="K109" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="F108" s="61">
-        <v>0.575745094692102</v>
-      </c>
-      <c r="G108" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="H108" s="61">
-        <v>0.37436641837390811</v>
-      </c>
-      <c r="I108" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="J108" s="61">
-        <v>0.40201203727845525</v>
-      </c>
-      <c r="K108" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="L108" s="61">
-        <v>0.47373288013894216</v>
-      </c>
-    </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B109" s="62">
-        <v>2</v>
-      </c>
-      <c r="C109" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="D109" s="64">
-        <v>0.12721723692319101</v>
-      </c>
-      <c r="E109" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="F109" s="64">
-        <v>0.13138048600356744</v>
-      </c>
-      <c r="G109" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="H109" s="64">
-        <v>0.34086223854153047</v>
-      </c>
-      <c r="I109" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="J109" s="64">
-        <v>0.35550758623865192</v>
-      </c>
-      <c r="K109" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="L109" s="64">
-        <v>0.2328698541206449</v>
+      <c r="L109" s="61">
+        <v>0.32359467705807943</v>
       </c>
     </row>
     <row r="110" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B110" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C110" s="63" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D110" s="64">
-        <v>8.0753940846481395E-2</v>
+        <v>0.26337522063977042</v>
       </c>
       <c r="E110" s="63" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F110" s="64">
-        <v>5.5091569582249915E-2</v>
+        <v>0.291047094728834</v>
       </c>
       <c r="G110" s="63" t="s">
         <v>47</v>
       </c>
       <c r="H110" s="64">
-        <v>0.16333058432566447</v>
+        <v>0.32023820524498292</v>
       </c>
       <c r="I110" s="63" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="J110" s="64">
-        <v>8.4045366963358528E-2</v>
+        <v>0.28547656117796083</v>
       </c>
       <c r="K110" s="63" t="s">
         <v>47</v>
       </c>
       <c r="L110" s="64">
-        <v>0.10423209593162566</v>
+        <v>0.31573708946411477</v>
       </c>
     </row>
     <row r="111" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B111" s="62">
+        <v>3</v>
+      </c>
+      <c r="C111" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="D111" s="64">
+        <v>0.20523172007016927</v>
+      </c>
+      <c r="E111" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F111" s="64">
+        <v>0.18856434728340798</v>
+      </c>
+      <c r="G111" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H111" s="64">
+        <v>0.10148248772591527</v>
+      </c>
+      <c r="I111" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="J111" s="64">
+        <v>9.2032020284980018E-2</v>
+      </c>
+      <c r="K111" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="L111" s="64">
+        <v>0.16430447808426896</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B112" s="62">
         <v>4</v>
       </c>
-      <c r="C111" s="65" t="s">
+      <c r="C112" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="D111" s="66">
-        <v>6.6878800783670506E-2</v>
-      </c>
-      <c r="E111" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="F111" s="64">
-        <v>4.5853392665322124E-2</v>
-      </c>
-      <c r="G111" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="H111" s="64">
-        <v>1.606276898781428E-2</v>
-      </c>
-      <c r="I111" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="J111" s="64">
-        <v>7.0248002457789629E-2</v>
-      </c>
-      <c r="K111" s="63" t="s">
+      <c r="D112" s="66">
+        <v>0.12116779544977975</v>
+      </c>
+      <c r="E112" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="L111" s="64">
-        <v>4.9426649043773058E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="67">
+      <c r="F112" s="64">
+        <v>3.5642895211350896E-2</v>
+      </c>
+      <c r="G112" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="H112" s="64">
+        <v>2.1484153311571493E-2</v>
+      </c>
+      <c r="I112" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="J112" s="64">
+        <v>5.1728769423881125E-2</v>
+      </c>
+      <c r="K112" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="L112" s="64">
+        <v>4.6077732550328279E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B113" s="67">
         <v>5</v>
       </c>
-      <c r="C112" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="D112" s="69">
-        <v>3.7365570163318963E-2</v>
-      </c>
-      <c r="E112" s="70" t="s">
+      <c r="C113" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D113" s="69">
+        <v>2.7763813670911144E-2</v>
+      </c>
+      <c r="E113" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="F113" s="71">
+        <v>3.3609956751027376E-2</v>
+      </c>
+      <c r="G113" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="F112" s="71">
-        <v>4.2491368970860095E-2</v>
-      </c>
-      <c r="G112" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="H112" s="71">
-        <v>1.5639754676991923E-2</v>
-      </c>
-      <c r="I112" s="70" t="s">
+      <c r="H113" s="71">
+        <v>1.4490724038593415E-2</v>
+      </c>
+      <c r="I113" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="J113" s="71">
+        <v>2.8869966358997898E-2</v>
+      </c>
+      <c r="K113" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="J112" s="71">
-        <v>2.2532044652139416E-2</v>
-      </c>
-      <c r="K112" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="L112" s="71">
-        <v>3.0798442507959167E-2</v>
-      </c>
-    </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B113" s="43"/>
-      <c r="C113" s="55" t="s">
+      <c r="L113" s="71">
+        <v>2.2314726403328145E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B114" s="43"/>
+      <c r="C114" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="D113" s="72"/>
-      <c r="E113" s="73"/>
-      <c r="F113" s="72"/>
-      <c r="G113" s="73"/>
-      <c r="H113" s="72"/>
-      <c r="I113" s="73"/>
-      <c r="J113" s="72"/>
-      <c r="K113" s="73"/>
-      <c r="L113" s="74"/>
-    </row>
-    <row r="114" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="115" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C115" s="121">
-        <v>2019</v>
-      </c>
-      <c r="D115" s="122"/>
-      <c r="E115" s="122"/>
-      <c r="F115" s="122"/>
-      <c r="G115" s="122"/>
-      <c r="H115" s="122"/>
-      <c r="I115" s="122"/>
-      <c r="J115" s="122"/>
-      <c r="K115" s="122"/>
-      <c r="L115" s="123"/>
-    </row>
+      <c r="D114" s="72"/>
+      <c r="E114" s="73"/>
+      <c r="F114" s="72"/>
+      <c r="G114" s="73"/>
+      <c r="H114" s="72"/>
+      <c r="I114" s="73"/>
+      <c r="J114" s="72"/>
+      <c r="K114" s="73"/>
+      <c r="L114" s="74"/>
+    </row>
+    <row r="115" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="58" t="s">
+      <c r="C116" s="121">
+        <v>2020</v>
+      </c>
+      <c r="D116" s="122"/>
+      <c r="E116" s="122"/>
+      <c r="F116" s="122"/>
+      <c r="G116" s="122"/>
+      <c r="H116" s="122"/>
+      <c r="I116" s="122"/>
+      <c r="J116" s="122"/>
+      <c r="K116" s="122"/>
+      <c r="L116" s="123"/>
+    </row>
+    <row r="117" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C116" s="127" t="s">
+      <c r="C117" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D116" s="128"/>
-      <c r="E116" s="127" t="s">
+      <c r="D117" s="128"/>
+      <c r="E117" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F116" s="129"/>
-      <c r="G116" s="127" t="s">
+      <c r="F117" s="129"/>
+      <c r="G117" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H116" s="128"/>
-      <c r="I116" s="129" t="s">
+      <c r="H117" s="128"/>
+      <c r="I117" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J116" s="128"/>
-      <c r="K116" s="129" t="s">
+      <c r="J117" s="128"/>
+      <c r="K117" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L116" s="128"/>
-    </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B117" s="59">
+      <c r="L117" s="128"/>
+    </row>
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B118" s="59">
         <v>1</v>
       </c>
-      <c r="C117" s="60" t="s">
+      <c r="C118" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D117" s="61">
-        <v>0.41317992413545113</v>
-      </c>
-      <c r="E117" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="F117" s="61">
-        <v>0.37052589864072571</v>
-      </c>
-      <c r="G117" s="60" t="s">
+      <c r="D118" s="61">
+        <v>0.59401945613555618</v>
+      </c>
+      <c r="E118" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="H117" s="61">
-        <v>0.52031593013762067</v>
-      </c>
-      <c r="I117" s="60" t="s">
+      <c r="F118" s="61">
+        <v>0.575745094692102</v>
+      </c>
+      <c r="G118" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="J117" s="61">
-        <v>0.46470710642225255</v>
-      </c>
-      <c r="K117" s="60" t="s">
+      <c r="H118" s="61">
+        <v>0.37436641837390811</v>
+      </c>
+      <c r="I118" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="L117" s="61">
-        <v>0.43030180886434577</v>
-      </c>
-    </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B118" s="62">
-        <v>2</v>
-      </c>
-      <c r="C118" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D118" s="64">
-        <v>0.24605399301807312</v>
-      </c>
-      <c r="E118" s="63" t="s">
+      <c r="J118" s="61">
+        <v>0.40201203727845525</v>
+      </c>
+      <c r="K118" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="F118" s="64">
-        <v>0.29061864897239531</v>
-      </c>
-      <c r="G118" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="H118" s="64">
-        <v>0.16068087525967303</v>
-      </c>
-      <c r="I118" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="J118" s="64">
-        <v>0.21991826755407629</v>
-      </c>
-      <c r="K118" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="L118" s="64">
-        <v>0.20313035651953912</v>
+      <c r="L118" s="61">
+        <v>0.47373288013894216</v>
       </c>
     </row>
     <row r="119" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B119" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119" s="63" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D119" s="64">
-        <v>0.12333803340260394</v>
+        <v>0.12721723692319101</v>
       </c>
       <c r="E119" s="63" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F119" s="64">
-        <v>0.13741144677816364</v>
+        <v>0.13138048600356744</v>
       </c>
       <c r="G119" s="63" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H119" s="64">
-        <v>9.1360762669025097E-2</v>
+        <v>0.34086223854153047</v>
       </c>
       <c r="I119" s="63" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="J119" s="64">
-        <v>9.5935899480450823E-2</v>
+        <v>0.35550758623865192</v>
       </c>
       <c r="K119" s="63" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L119" s="64">
-        <v>0.10570754986913165</v>
+        <v>0.2328698541206449</v>
       </c>
     </row>
     <row r="120" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B120" s="62">
-        <v>4</v>
-      </c>
-      <c r="C120" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="D120" s="66">
-        <v>0.10731044553625131</v>
+      <c r="D120" s="64">
+        <v>8.0753940846481395E-2</v>
       </c>
       <c r="E120" s="63" t="s">
         <v>54</v>
       </c>
       <c r="F120" s="64">
-        <v>7.1406458798528402E-2</v>
+        <v>5.5091569582249915E-2</v>
       </c>
       <c r="G120" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="H120" s="64">
+        <v>0.16333058432566447</v>
+      </c>
+      <c r="I120" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="H120" s="64">
-        <v>8.9315369860503743E-2</v>
-      </c>
-      <c r="I120" s="63" t="s">
+      <c r="J120" s="64">
+        <v>8.4045366963358528E-2</v>
+      </c>
+      <c r="K120" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="L120" s="64">
+        <v>0.10423209593162566</v>
+      </c>
+    </row>
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B121" s="62">
+        <v>4</v>
+      </c>
+      <c r="C121" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="D121" s="66">
+        <v>6.6878800783670506E-2</v>
+      </c>
+      <c r="E121" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F121" s="64">
+        <v>4.5853392665322124E-2</v>
+      </c>
+      <c r="G121" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="H121" s="64">
+        <v>1.606276898781428E-2</v>
+      </c>
+      <c r="I121" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="J121" s="64">
+        <v>7.0248002457789629E-2</v>
+      </c>
+      <c r="K121" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="L121" s="64">
+        <v>4.9426649043773058E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="67">
+        <v>5</v>
+      </c>
+      <c r="C122" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="D122" s="69">
+        <v>3.7365570163318963E-2</v>
+      </c>
+      <c r="E122" s="70" t="s">
+        <v>48</v>
+      </c>
+      <c r="F122" s="71">
+        <v>4.2491368970860095E-2</v>
+      </c>
+      <c r="G122" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="H122" s="71">
+        <v>1.5639754676991923E-2</v>
+      </c>
+      <c r="I122" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="J122" s="71">
+        <v>2.2532044652139416E-2</v>
+      </c>
+      <c r="K122" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="L122" s="71">
+        <v>3.0798442507959167E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B123" s="43"/>
+      <c r="C123" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" s="72"/>
+      <c r="E123" s="73"/>
+      <c r="F123" s="72"/>
+      <c r="G123" s="73"/>
+      <c r="H123" s="72"/>
+      <c r="I123" s="73"/>
+      <c r="J123" s="72"/>
+      <c r="K123" s="73"/>
+      <c r="L123" s="74"/>
+    </row>
+    <row r="124" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="125" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C125" s="121">
+        <v>2019</v>
+      </c>
+      <c r="D125" s="122"/>
+      <c r="E125" s="122"/>
+      <c r="F125" s="122"/>
+      <c r="G125" s="122"/>
+      <c r="H125" s="122"/>
+      <c r="I125" s="122"/>
+      <c r="J125" s="122"/>
+      <c r="K125" s="122"/>
+      <c r="L125" s="123"/>
+    </row>
+    <row r="126" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C126" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D126" s="128"/>
+      <c r="E126" s="127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F126" s="129"/>
+      <c r="G126" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="H126" s="128"/>
+      <c r="I126" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="J126" s="128"/>
+      <c r="K126" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L126" s="128"/>
+    </row>
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B127" s="59">
+        <v>1</v>
+      </c>
+      <c r="C127" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="D127" s="61">
+        <v>0.41317992413545113</v>
+      </c>
+      <c r="E127" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="J120" s="64">
-        <v>7.3641579299681043E-2</v>
-      </c>
-      <c r="K120" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="L120" s="64">
-        <v>8.2966504393697557E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="67">
-        <v>5</v>
-      </c>
-      <c r="C121" s="68" t="s">
-        <v>53</v>
-      </c>
-      <c r="D121" s="69">
-        <v>3.3804149035485113E-2</v>
-      </c>
-      <c r="E121" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="F121" s="71">
-        <v>2.3132555409079419E-2</v>
-      </c>
-      <c r="G121" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="H121" s="71">
-        <v>3.5549596010878426E-2</v>
-      </c>
-      <c r="I121" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="J121" s="71">
-        <v>5.5018857295076856E-2</v>
-      </c>
-      <c r="K121" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="L121" s="71">
-        <v>7.9722044855836408E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B122" s="43"/>
-      <c r="C122" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D122" s="72"/>
-      <c r="E122" s="73"/>
-      <c r="F122" s="72"/>
-      <c r="G122" s="73"/>
-      <c r="H122" s="72"/>
-      <c r="I122" s="73"/>
-      <c r="J122" s="72"/>
-      <c r="K122" s="73"/>
-      <c r="L122" s="74"/>
-    </row>
-    <row r="123" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="124" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C124" s="121">
-        <v>2018</v>
-      </c>
-      <c r="D124" s="122"/>
-      <c r="E124" s="122"/>
-      <c r="F124" s="122"/>
-      <c r="G124" s="122"/>
-      <c r="H124" s="122"/>
-      <c r="I124" s="122"/>
-      <c r="J124" s="122"/>
-      <c r="K124" s="122"/>
-      <c r="L124" s="123"/>
-    </row>
-    <row r="125" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="C125" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="D125" s="128"/>
-      <c r="E125" s="127" t="s">
-        <v>29</v>
-      </c>
-      <c r="F125" s="129"/>
-      <c r="G125" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="H125" s="128"/>
-      <c r="I125" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="J125" s="128"/>
-      <c r="K125" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="L125" s="128"/>
-    </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B126" s="59">
-        <v>1</v>
-      </c>
-      <c r="C126" s="60" t="s">
+      <c r="F127" s="61">
+        <v>0.37052589864072571</v>
+      </c>
+      <c r="G127" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D126" s="61">
-        <v>0.48518574151418264</v>
-      </c>
-      <c r="E126" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="F126" s="61">
-        <v>0.35419662769624927</v>
-      </c>
-      <c r="G126" s="60" t="s">
+      <c r="H127" s="61">
+        <v>0.52031593013762067</v>
+      </c>
+      <c r="I127" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="H126" s="61">
-        <v>0.47314460464308744</v>
-      </c>
-      <c r="I126" s="60" t="s">
+      <c r="J127" s="61">
+        <v>0.46470710642225255</v>
+      </c>
+      <c r="K127" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="J126" s="61">
-        <v>0.65648487840256775</v>
-      </c>
-      <c r="K126" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="L126" s="61">
-        <v>0.48897068342134636</v>
-      </c>
-    </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B127" s="62">
-        <v>2</v>
-      </c>
-      <c r="C127" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D127" s="64">
-        <v>0.22030875252019935</v>
-      </c>
-      <c r="E127" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="F127" s="64">
-        <v>0.26579397692089579</v>
-      </c>
-      <c r="G127" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="H127" s="64">
-        <v>0.19437037117056391</v>
-      </c>
-      <c r="I127" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="J127" s="64">
-        <v>0.1045362517611577</v>
-      </c>
-      <c r="K127" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="L127" s="64">
-        <v>0.1852279803038655</v>
+      <c r="L127" s="61">
+        <v>0.43030180886434577</v>
       </c>
     </row>
     <row r="128" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B128" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C128" s="63" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D128" s="64">
-        <v>0.11662168666399804</v>
+        <v>0.24605399301807312</v>
       </c>
       <c r="E128" s="63" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F128" s="64">
-        <v>0.12087914031016443</v>
+        <v>0.29061864897239531</v>
       </c>
       <c r="G128" s="63" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H128" s="64">
-        <v>7.5231519959309975E-2</v>
+        <v>0.16068087525967303</v>
       </c>
       <c r="I128" s="63" t="s">
         <v>47</v>
       </c>
       <c r="J128" s="64">
-        <v>7.9396087140674226E-2</v>
+        <v>0.21991826755407629</v>
       </c>
       <c r="K128" s="63" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L128" s="64">
-        <v>7.7687934516077972E-2</v>
+        <v>0.20313035651953912</v>
       </c>
     </row>
     <row r="129" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B129" s="62">
-        <v>4</v>
-      </c>
-      <c r="C129" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="D129" s="64">
+        <v>0.12333803340260394</v>
+      </c>
+      <c r="E129" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="D129" s="66">
-        <v>7.8335207767680368E-2</v>
-      </c>
-      <c r="E129" s="63" t="s">
-        <v>54</v>
-      </c>
       <c r="F129" s="64">
-        <v>0.10678946623421511</v>
+        <v>0.13741144677816364</v>
       </c>
       <c r="G129" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H129" s="64">
-        <v>7.1655437999183599E-2</v>
+        <v>9.1360762669025097E-2</v>
       </c>
       <c r="I129" s="63" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="J129" s="64">
-        <v>4.2540607216609433E-2</v>
+        <v>9.5935899480450823E-2</v>
       </c>
       <c r="K129" s="63" t="s">
         <v>47</v>
       </c>
       <c r="L129" s="64">
-        <v>7.4980931993806427E-2</v>
-      </c>
-    </row>
-    <row r="130" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B130" s="67">
+        <v>0.10570754986913165</v>
+      </c>
+    </row>
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B130" s="62">
+        <v>4</v>
+      </c>
+      <c r="C130" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="D130" s="66">
+        <v>0.10731044553625131</v>
+      </c>
+      <c r="E130" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F130" s="64">
+        <v>7.1406458798528402E-2</v>
+      </c>
+      <c r="G130" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H130" s="64">
+        <v>8.9315369860503743E-2</v>
+      </c>
+      <c r="I130" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="J130" s="64">
+        <v>7.3641579299681043E-2</v>
+      </c>
+      <c r="K130" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="L130" s="64">
+        <v>8.2966504393697557E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="67">
         <v>5</v>
       </c>
-      <c r="C130" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="D130" s="69">
-        <v>2.7479534781359654E-2</v>
-      </c>
-      <c r="E130" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="F130" s="71">
-        <v>6.2129046977217259E-2</v>
-      </c>
-      <c r="G130" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="H130" s="71">
-        <v>3.8617751437451782E-2</v>
-      </c>
-      <c r="I130" s="70" t="s">
+      <c r="C131" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D131" s="69">
+        <v>3.3804149035485113E-2</v>
+      </c>
+      <c r="E131" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="F131" s="71">
+        <v>2.3132555409079419E-2</v>
+      </c>
+      <c r="G131" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="H131" s="71">
+        <v>3.5549596010878426E-2</v>
+      </c>
+      <c r="I131" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="J130" s="71">
-        <v>4.1182639260946979E-2</v>
-      </c>
-      <c r="K130" s="70" t="s">
+      <c r="J131" s="71">
+        <v>5.5018857295076856E-2</v>
+      </c>
+      <c r="K131" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="L130" s="71">
-        <v>6.4173269244895359E-2</v>
-      </c>
-    </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B131" s="43"/>
-      <c r="C131" s="55" t="s">
+      <c r="L131" s="71">
+        <v>7.9722044855836408E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B132" s="43"/>
+      <c r="C132" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="D131" s="72"/>
-      <c r="E131" s="73"/>
-      <c r="F131" s="72"/>
-      <c r="G131" s="73"/>
-      <c r="H131" s="72"/>
-      <c r="I131" s="73"/>
-      <c r="J131" s="72"/>
-      <c r="K131" s="73"/>
-      <c r="L131" s="74"/>
+      <c r="D132" s="72"/>
+      <c r="E132" s="73"/>
+      <c r="F132" s="72"/>
+      <c r="G132" s="73"/>
+      <c r="H132" s="72"/>
+      <c r="I132" s="73"/>
+      <c r="J132" s="72"/>
+      <c r="K132" s="73"/>
+      <c r="L132" s="74"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="134" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C134" s="121">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D134" s="122"/>
       <c r="E134" s="122"/>
@@ -9338,34 +9289,34 @@
         <v>1</v>
       </c>
       <c r="C136" s="60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D136" s="61">
-        <v>0.61541729301256443</v>
+        <v>0.48518574151418264</v>
       </c>
       <c r="E136" s="60" t="s">
         <v>41</v>
       </c>
       <c r="F136" s="61">
-        <v>0.85905615058709672</v>
+        <v>0.35419662769624927</v>
       </c>
       <c r="G136" s="60" t="s">
         <v>42</v>
       </c>
       <c r="H136" s="61">
-        <v>0.34873240072967443</v>
+        <v>0.47314460464308744</v>
       </c>
       <c r="I136" s="60" t="s">
         <v>42</v>
       </c>
       <c r="J136" s="61">
-        <v>0.64159792179955311</v>
+        <v>0.65648487840256775</v>
       </c>
       <c r="K136" s="60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L136" s="61">
-        <v>0.39873949743652837</v>
+        <v>0.48897068342134636</v>
       </c>
     </row>
     <row r="137" spans="2:12" x14ac:dyDescent="0.25">
@@ -9373,34 +9324,34 @@
         <v>2</v>
       </c>
       <c r="C137" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D137" s="64">
+        <v>0.22030875252019935</v>
+      </c>
+      <c r="E137" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D137" s="64">
-        <v>0.1720764484338132</v>
-      </c>
-      <c r="E137" s="63" t="s">
+      <c r="F137" s="64">
+        <v>0.26579397692089579</v>
+      </c>
+      <c r="G137" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H137" s="64">
+        <v>0.19437037117056391</v>
+      </c>
+      <c r="I137" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="F137" s="64">
-        <v>4.8028429597426418E-2</v>
-      </c>
-      <c r="G137" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="H137" s="64">
-        <v>0.23149691470106132</v>
-      </c>
-      <c r="I137" s="63" t="s">
+      <c r="J137" s="64">
+        <v>0.1045362517611577</v>
+      </c>
+      <c r="K137" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="J137" s="64">
-        <v>0.11483021421003346</v>
-      </c>
-      <c r="K137" s="63" t="s">
-        <v>42</v>
-      </c>
       <c r="L137" s="64">
-        <v>0.34388265257327827</v>
+        <v>0.1852279803038655</v>
       </c>
     </row>
     <row r="138" spans="2:12" x14ac:dyDescent="0.25">
@@ -9408,34 +9359,34 @@
         <v>3</v>
       </c>
       <c r="C138" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="D138" s="64">
+        <v>0.11662168666399804</v>
+      </c>
+      <c r="E138" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F138" s="64">
+        <v>0.12087914031016443</v>
+      </c>
+      <c r="G138" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="D138" s="64">
-        <v>7.7812156290183607E-2</v>
-      </c>
-      <c r="E138" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="F138" s="64">
-        <v>3.9331191146096969E-2</v>
-      </c>
-      <c r="G138" s="63" t="s">
-        <v>41</v>
-      </c>
       <c r="H138" s="64">
-        <v>0.14115178443235601</v>
+        <v>7.5231519959309975E-2</v>
       </c>
       <c r="I138" s="63" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J138" s="64">
-        <v>0.11279232164023725</v>
+        <v>7.9396087140674226E-2</v>
       </c>
       <c r="K138" s="63" t="s">
         <v>54</v>
       </c>
       <c r="L138" s="64">
-        <v>8.3911506348846948E-2</v>
+        <v>7.7687934516077972E-2</v>
       </c>
     </row>
     <row r="139" spans="2:12" x14ac:dyDescent="0.25">
@@ -9443,34 +9394,34 @@
         <v>4</v>
       </c>
       <c r="C139" s="65" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D139" s="66">
-        <v>7.4020568607325365E-2</v>
+        <v>7.8335207767680368E-2</v>
       </c>
       <c r="E139" s="63" t="s">
         <v>54</v>
       </c>
       <c r="F139" s="64">
-        <v>2.1387596652042956E-2</v>
+        <v>0.10678946623421511</v>
       </c>
       <c r="G139" s="63" t="s">
         <v>54</v>
       </c>
       <c r="H139" s="64">
-        <v>0.10962000664731331</v>
+        <v>7.1655437999183599E-2</v>
       </c>
       <c r="I139" s="63" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="J139" s="64">
-        <v>2.6772969422241798E-2</v>
+        <v>4.2540607216609433E-2</v>
       </c>
       <c r="K139" s="63" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="L139" s="64">
-        <v>8.3155735356962676E-2</v>
+        <v>7.4980931993806427E-2</v>
       </c>
     </row>
     <row r="140" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9478,34 +9429,34 @@
         <v>5</v>
       </c>
       <c r="C140" s="68" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D140" s="69">
-        <v>1.8553044952324151E-2</v>
+        <v>2.7479534781359654E-2</v>
       </c>
       <c r="E140" s="70" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F140" s="71">
-        <v>1.1775957382934139E-2</v>
+        <v>6.2129046977217259E-2</v>
       </c>
       <c r="G140" s="70" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H140" s="71">
-        <v>4.6906858779115754E-2</v>
+        <v>3.8617751437451782E-2</v>
       </c>
       <c r="I140" s="70" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J140" s="71">
-        <v>2.5482874874337563E-2</v>
+        <v>4.1182639260946979E-2</v>
       </c>
       <c r="K140" s="70" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L140" s="71">
-        <v>1.7721323922607741E-2</v>
+        <v>6.4173269244895359E-2</v>
       </c>
     </row>
     <row r="141" spans="2:12" x14ac:dyDescent="0.25">
@@ -9523,2350 +9474,2586 @@
       <c r="K141" s="73"/>
       <c r="L141" s="74"/>
     </row>
-    <row r="142" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="143" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C143" s="121">
-        <v>2016</v>
-      </c>
-      <c r="D143" s="122"/>
-      <c r="E143" s="122"/>
-      <c r="F143" s="122"/>
-      <c r="G143" s="122"/>
-      <c r="H143" s="122"/>
-      <c r="I143" s="122"/>
-      <c r="J143" s="122"/>
-      <c r="K143" s="122"/>
-      <c r="L143" s="123"/>
-    </row>
+    <row r="143" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="144" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B144" s="58" t="s">
+      <c r="C144" s="121">
+        <v>2017</v>
+      </c>
+      <c r="D144" s="122"/>
+      <c r="E144" s="122"/>
+      <c r="F144" s="122"/>
+      <c r="G144" s="122"/>
+      <c r="H144" s="122"/>
+      <c r="I144" s="122"/>
+      <c r="J144" s="122"/>
+      <c r="K144" s="122"/>
+      <c r="L144" s="123"/>
+    </row>
+    <row r="145" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B145" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C144" s="127" t="s">
+      <c r="C145" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D144" s="128"/>
-      <c r="E144" s="127" t="s">
+      <c r="D145" s="128"/>
+      <c r="E145" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F144" s="129"/>
-      <c r="G144" s="127" t="s">
+      <c r="F145" s="129"/>
+      <c r="G145" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H144" s="128"/>
-      <c r="I144" s="129" t="s">
+      <c r="H145" s="128"/>
+      <c r="I145" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J144" s="128"/>
-      <c r="K144" s="129" t="s">
+      <c r="J145" s="128"/>
+      <c r="K145" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L144" s="128"/>
-    </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B145" s="59">
+      <c r="L145" s="128"/>
+    </row>
+    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B146" s="59">
         <v>1</v>
       </c>
-      <c r="C145" s="60" t="s">
+      <c r="C146" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D145" s="61">
-        <v>0.39030812539488718</v>
-      </c>
-      <c r="E145" s="60" t="s">
+      <c r="D146" s="61">
+        <v>0.61541729301256443</v>
+      </c>
+      <c r="E146" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="F145" s="61">
-        <v>0.81478503734630225</v>
-      </c>
-      <c r="G145" s="60" t="s">
+      <c r="F146" s="61">
+        <v>0.85905615058709672</v>
+      </c>
+      <c r="G146" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="H146" s="61">
+        <v>0.34873240072967443</v>
+      </c>
+      <c r="I146" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="J146" s="61">
+        <v>0.64159792179955311</v>
+      </c>
+      <c r="K146" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="H145" s="61">
-        <v>0.83338271075128967</v>
-      </c>
-      <c r="I145" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="J145" s="61">
-        <v>0.74004875337337939</v>
-      </c>
-      <c r="K145" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="L145" s="61">
-        <v>0.72439061307849062</v>
-      </c>
-    </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B146" s="62">
-        <v>2</v>
-      </c>
-      <c r="C146" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="D146" s="64">
-        <v>0.31335921594411287</v>
-      </c>
-      <c r="E146" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="F146" s="64">
-        <v>8.5333926312794559E-2</v>
-      </c>
-      <c r="G146" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H146" s="64">
-        <v>9.1288620204735202E-2</v>
-      </c>
-      <c r="I146" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="J146" s="64">
-        <v>0.10087729460166445</v>
-      </c>
-      <c r="K146" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="L146" s="64">
-        <v>0.11920857223106782</v>
+      <c r="L146" s="61">
+        <v>0.39873949743652837</v>
       </c>
     </row>
     <row r="147" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C147" s="63" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D147" s="64">
-        <v>0.11700971463982318</v>
+        <v>0.1720764484338132</v>
       </c>
       <c r="E147" s="63" t="s">
         <v>55</v>
       </c>
       <c r="F147" s="64">
-        <v>2.2967424899553009E-2</v>
+        <v>4.8028429597426418E-2</v>
       </c>
       <c r="G147" s="63" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H147" s="64">
-        <v>2.9397552955976628E-2</v>
+        <v>0.23149691470106132</v>
       </c>
       <c r="I147" s="63" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="J147" s="64">
-        <v>8.3298485437362429E-2</v>
+        <v>0.11483021421003346</v>
       </c>
       <c r="K147" s="63" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="L147" s="64">
-        <v>4.6374252522970463E-2</v>
+        <v>0.34388265257327827</v>
       </c>
     </row>
     <row r="148" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148" s="62">
+        <v>3</v>
+      </c>
+      <c r="C148" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="D148" s="64">
+        <v>7.7812156290183607E-2</v>
+      </c>
+      <c r="E148" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F148" s="64">
+        <v>3.9331191146096969E-2</v>
+      </c>
+      <c r="G148" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H148" s="64">
+        <v>0.14115178443235601</v>
+      </c>
+      <c r="I148" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="J148" s="64">
+        <v>0.11279232164023725</v>
+      </c>
+      <c r="K148" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="L148" s="64">
+        <v>8.3911506348846948E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B149" s="62">
         <v>4</v>
       </c>
-      <c r="C148" s="65" t="s">
-        <v>47</v>
-      </c>
-      <c r="D148" s="66">
-        <v>8.8878489059530982E-2</v>
-      </c>
-      <c r="E148" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="F148" s="64">
-        <v>2.1071694551815772E-2</v>
-      </c>
-      <c r="G148" s="63" t="s">
+      <c r="C149" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="D149" s="66">
+        <v>7.4020568607325365E-2</v>
+      </c>
+      <c r="E149" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F149" s="64">
+        <v>2.1387596652042956E-2</v>
+      </c>
+      <c r="G149" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H149" s="64">
+        <v>0.10962000664731331</v>
+      </c>
+      <c r="I149" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="H148" s="64">
-        <v>2.7953233565972256E-2</v>
-      </c>
-      <c r="I148" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="J148" s="64">
-        <v>3.3437198330390494E-2</v>
-      </c>
-      <c r="K148" s="63" t="s">
+      <c r="J149" s="64">
+        <v>2.6772969422241798E-2</v>
+      </c>
+      <c r="K149" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="L148" s="64">
-        <v>3.6470908880116122E-2</v>
-      </c>
-    </row>
-    <row r="149" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B149" s="67">
+      <c r="L149" s="64">
+        <v>8.3155735356962676E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B150" s="67">
         <v>5</v>
       </c>
-      <c r="C149" s="68" t="s">
-        <v>59</v>
-      </c>
-      <c r="D149" s="69">
-        <v>3.4157312604303172E-2</v>
-      </c>
-      <c r="E149" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="F149" s="71">
-        <v>9.8603050422608352E-3</v>
-      </c>
-      <c r="G149" s="70" t="s">
+      <c r="C150" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="D150" s="69">
+        <v>1.8553044952324151E-2</v>
+      </c>
+      <c r="E150" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="F150" s="71">
+        <v>1.1775957382934139E-2</v>
+      </c>
+      <c r="G150" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="H150" s="71">
+        <v>4.6906858779115754E-2</v>
+      </c>
+      <c r="I150" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="H149" s="71">
-        <v>4.2634798886179992E-3</v>
-      </c>
-      <c r="I149" s="70" t="s">
+      <c r="J150" s="71">
+        <v>2.5482874874337563E-2</v>
+      </c>
+      <c r="K150" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="J149" s="71">
-        <v>2.1176882695198591E-2</v>
-      </c>
-      <c r="K149" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="L149" s="71">
-        <v>2.4111336537993119E-2</v>
-      </c>
-    </row>
-    <row r="150" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B150" s="43"/>
-      <c r="C150" s="55" t="s">
+      <c r="L150" s="71">
+        <v>1.7721323922607741E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B151" s="43"/>
+      <c r="C151" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="D150" s="72"/>
-      <c r="E150" s="73"/>
-      <c r="F150" s="72"/>
-      <c r="G150" s="73"/>
-      <c r="H150" s="72"/>
-      <c r="I150" s="73"/>
-      <c r="J150" s="72"/>
-      <c r="K150" s="73"/>
-      <c r="L150" s="74"/>
-    </row>
-    <row r="151" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="152" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="121">
-        <v>2015</v>
-      </c>
-      <c r="D152" s="122"/>
-      <c r="E152" s="122"/>
-      <c r="F152" s="122"/>
-      <c r="G152" s="122"/>
-      <c r="H152" s="122"/>
-      <c r="I152" s="122"/>
-      <c r="J152" s="122"/>
-      <c r="K152" s="122"/>
-      <c r="L152" s="123"/>
-    </row>
+      <c r="D151" s="72"/>
+      <c r="E151" s="73"/>
+      <c r="F151" s="72"/>
+      <c r="G151" s="73"/>
+      <c r="H151" s="72"/>
+      <c r="I151" s="73"/>
+      <c r="J151" s="72"/>
+      <c r="K151" s="73"/>
+      <c r="L151" s="74"/>
+    </row>
+    <row r="152" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="153" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B153" s="58" t="s">
+      <c r="C153" s="121">
+        <v>2016</v>
+      </c>
+      <c r="D153" s="122"/>
+      <c r="E153" s="122"/>
+      <c r="F153" s="122"/>
+      <c r="G153" s="122"/>
+      <c r="H153" s="122"/>
+      <c r="I153" s="122"/>
+      <c r="J153" s="122"/>
+      <c r="K153" s="122"/>
+      <c r="L153" s="123"/>
+    </row>
+    <row r="154" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B154" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C153" s="127" t="s">
+      <c r="C154" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D153" s="128"/>
-      <c r="E153" s="127" t="s">
+      <c r="D154" s="128"/>
+      <c r="E154" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F153" s="129"/>
-      <c r="G153" s="127" t="s">
+      <c r="F154" s="129"/>
+      <c r="G154" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H153" s="128"/>
-      <c r="I153" s="129" t="s">
+      <c r="H154" s="128"/>
+      <c r="I154" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J153" s="128"/>
-      <c r="K153" s="129" t="s">
+      <c r="J154" s="128"/>
+      <c r="K154" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L153" s="128"/>
-    </row>
-    <row r="154" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B154" s="59">
+      <c r="L154" s="128"/>
+    </row>
+    <row r="155" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B155" s="59">
         <v>1</v>
       </c>
-      <c r="C154" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="D154" s="61">
-        <v>0.53504175937444709</v>
-      </c>
-      <c r="E154" s="60" t="s">
+      <c r="C155" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="F154" s="61">
-        <v>0.46299563995038379</v>
-      </c>
-      <c r="G154" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="H154" s="61">
-        <v>0.48436760686718527</v>
-      </c>
-      <c r="I154" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="J154" s="61">
-        <v>0.68808453824335425</v>
-      </c>
-      <c r="K154" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="L154" s="61">
-        <v>0.3424153019220616</v>
-      </c>
-    </row>
-    <row r="155" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B155" s="62">
-        <v>2</v>
-      </c>
-      <c r="C155" s="63" t="s">
+      <c r="D155" s="61">
+        <v>0.39030812539488718</v>
+      </c>
+      <c r="E155" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D155" s="64">
-        <v>0.36019710145782607</v>
-      </c>
-      <c r="E155" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="F155" s="64">
-        <v>0.35354560796326823</v>
-      </c>
-      <c r="G155" s="63" t="s">
+      <c r="F155" s="61">
+        <v>0.81478503734630225</v>
+      </c>
+      <c r="G155" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="H155" s="64">
-        <v>0.40037304562861181</v>
-      </c>
-      <c r="I155" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="J155" s="64">
-        <v>0.15820050601358712</v>
-      </c>
-      <c r="K155" s="63" t="s">
+      <c r="H155" s="61">
+        <v>0.83338271075128967</v>
+      </c>
+      <c r="I155" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="L155" s="64">
-        <v>0.3147452225493938</v>
+      <c r="J155" s="61">
+        <v>0.74004875337337939</v>
+      </c>
+      <c r="K155" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="L155" s="61">
+        <v>0.72439061307849062</v>
       </c>
     </row>
     <row r="156" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B156" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C156" s="63" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D156" s="64">
-        <v>4.2840771913129516E-2</v>
+        <v>0.31335921594411287</v>
       </c>
       <c r="E156" s="63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F156" s="64">
-        <v>8.5088826951069493E-2</v>
+        <v>8.5333926312794559E-2</v>
       </c>
       <c r="G156" s="63" t="s">
         <v>42</v>
       </c>
       <c r="H156" s="64">
-        <v>4.7015359765124574E-2</v>
+        <v>9.1288620204735202E-2</v>
       </c>
       <c r="I156" s="63" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="J156" s="64">
-        <v>5.8761668916191244E-2</v>
+        <v>0.10087729460166445</v>
       </c>
       <c r="K156" s="63" t="s">
         <v>42</v>
       </c>
       <c r="L156" s="64">
-        <v>0.22797990491969664</v>
+        <v>0.11920857223106782</v>
       </c>
     </row>
     <row r="157" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B157" s="62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C157" s="63" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D157" s="64">
-        <v>2.2227012778548615E-2</v>
+        <v>0.11700971463982318</v>
       </c>
       <c r="E157" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F157" s="64">
-        <v>6.5926862342592873E-2</v>
+        <v>2.2967424899553009E-2</v>
       </c>
       <c r="G157" s="63" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H157" s="64">
-        <v>3.736282532991364E-2</v>
+        <v>2.9397552955976628E-2</v>
       </c>
       <c r="I157" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J157" s="64">
-        <v>3.2325503388409151E-2</v>
+        <v>8.3298485437362429E-2</v>
       </c>
       <c r="K157" s="63" t="s">
         <v>54</v>
       </c>
       <c r="L157" s="64">
-        <v>3.6802362175851679E-2</v>
-      </c>
-    </row>
-    <row r="158" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B158" s="67">
+        <v>4.6374252522970463E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B158" s="62">
+        <v>4</v>
+      </c>
+      <c r="C158" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D158" s="66">
+        <v>8.8878489059530982E-2</v>
+      </c>
+      <c r="E158" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F158" s="64">
+        <v>2.1071694551815772E-2</v>
+      </c>
+      <c r="G158" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="H158" s="64">
+        <v>2.7953233565972256E-2</v>
+      </c>
+      <c r="I158" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="J158" s="64">
+        <v>3.3437198330390494E-2</v>
+      </c>
+      <c r="K158" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="L158" s="64">
+        <v>3.6470908880116122E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B159" s="67">
         <v>5</v>
       </c>
-      <c r="C158" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="D158" s="71">
-        <v>1.1693192333953578E-2</v>
-      </c>
-      <c r="E158" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="F158" s="71">
-        <v>1.5911393184143145E-2</v>
-      </c>
-      <c r="G158" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="H158" s="71">
-        <v>1.8406208972710805E-2</v>
-      </c>
-      <c r="I158" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="J158" s="71">
-        <v>1.9240067334593453E-2</v>
-      </c>
-      <c r="K158" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="L158" s="71">
-        <v>2.6962511802828951E-2</v>
-      </c>
-    </row>
-    <row r="159" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C159" s="55" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="160" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="161" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C161" s="121">
-        <v>2014</v>
-      </c>
-      <c r="D161" s="122"/>
-      <c r="E161" s="122"/>
-      <c r="F161" s="122"/>
-      <c r="G161" s="122"/>
-      <c r="H161" s="122"/>
-      <c r="I161" s="122"/>
-      <c r="J161" s="122"/>
-      <c r="K161" s="122"/>
-      <c r="L161" s="123"/>
-    </row>
+      <c r="C159" s="68" t="s">
+        <v>59</v>
+      </c>
+      <c r="D159" s="69">
+        <v>3.4157312604303172E-2</v>
+      </c>
+      <c r="E159" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="F159" s="71">
+        <v>9.8603050422608352E-3</v>
+      </c>
+      <c r="G159" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="H159" s="71">
+        <v>4.2634798886179992E-3</v>
+      </c>
+      <c r="I159" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="J159" s="71">
+        <v>2.1176882695198591E-2</v>
+      </c>
+      <c r="K159" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="L159" s="71">
+        <v>2.4111336537993119E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B160" s="43"/>
+      <c r="C160" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D160" s="72"/>
+      <c r="E160" s="73"/>
+      <c r="F160" s="72"/>
+      <c r="G160" s="73"/>
+      <c r="H160" s="72"/>
+      <c r="I160" s="73"/>
+      <c r="J160" s="72"/>
+      <c r="K160" s="73"/>
+      <c r="L160" s="74"/>
+    </row>
+    <row r="161" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="162" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B162" s="58" t="s">
+      <c r="C162" s="121">
+        <v>2015</v>
+      </c>
+      <c r="D162" s="122"/>
+      <c r="E162" s="122"/>
+      <c r="F162" s="122"/>
+      <c r="G162" s="122"/>
+      <c r="H162" s="122"/>
+      <c r="I162" s="122"/>
+      <c r="J162" s="122"/>
+      <c r="K162" s="122"/>
+      <c r="L162" s="123"/>
+    </row>
+    <row r="163" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B163" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C162" s="127" t="s">
+      <c r="C163" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D162" s="128"/>
-      <c r="E162" s="127" t="s">
+      <c r="D163" s="128"/>
+      <c r="E163" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F162" s="129"/>
-      <c r="G162" s="127" t="s">
+      <c r="F163" s="129"/>
+      <c r="G163" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H162" s="128"/>
-      <c r="I162" s="129" t="s">
+      <c r="H163" s="128"/>
+      <c r="I163" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J162" s="128"/>
-      <c r="K162" s="129" t="s">
+      <c r="J163" s="128"/>
+      <c r="K163" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L162" s="128"/>
-    </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B163" s="59">
+      <c r="L163" s="128"/>
+    </row>
+    <row r="164" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B164" s="59">
         <v>1</v>
       </c>
-      <c r="C163" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="D163" s="61">
-        <v>0.35303102759335558</v>
-      </c>
-      <c r="E163" s="60" t="s">
+      <c r="C164" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="D164" s="61">
+        <v>0.53504175937444709</v>
+      </c>
+      <c r="E164" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="F164" s="61">
+        <v>0.46299563995038379</v>
+      </c>
+      <c r="G164" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="F163" s="61">
-        <v>0.54043709483375768</v>
-      </c>
-      <c r="G163" s="60" t="s">
+      <c r="H164" s="61">
+        <v>0.48436760686718527</v>
+      </c>
+      <c r="I164" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H163" s="61">
-        <v>0.37397009143091609</v>
-      </c>
-      <c r="I163" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="J163" s="61">
-        <v>0.29608663572744515</v>
-      </c>
-      <c r="K163" s="60" t="s">
+      <c r="J164" s="61">
+        <v>0.68808453824335425</v>
+      </c>
+      <c r="K164" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="L163" s="61">
-        <v>0.4000050447309148</v>
-      </c>
-    </row>
-    <row r="164" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B164" s="62">
-        <v>2</v>
-      </c>
-      <c r="C164" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="D164" s="64">
-        <v>0.33016023316913623</v>
-      </c>
-      <c r="E164" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="F164" s="64">
-        <v>0.15021429354024046</v>
-      </c>
-      <c r="G164" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H164" s="64">
-        <v>0.23333391436244807</v>
-      </c>
-      <c r="I164" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="J164" s="64">
-        <v>0.28725887699701946</v>
-      </c>
-      <c r="K164" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="L164" s="64">
-        <v>0.15470072550889394</v>
+      <c r="L164" s="61">
+        <v>0.3424153019220616</v>
       </c>
     </row>
     <row r="165" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B165" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C165" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D165" s="64">
+        <v>0.36019710145782607</v>
+      </c>
+      <c r="E165" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D165" s="64">
-        <v>0.1852721722674015</v>
-      </c>
-      <c r="E165" s="63" t="s">
+      <c r="F165" s="64">
+        <v>0.35354560796326823</v>
+      </c>
+      <c r="G165" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="F165" s="64">
-        <v>0.12082774791337439</v>
-      </c>
-      <c r="G165" s="63" t="s">
-        <v>43</v>
-      </c>
       <c r="H165" s="64">
-        <v>0.15037150116906767</v>
+        <v>0.40037304562861181</v>
       </c>
       <c r="I165" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="J165" s="64">
+        <v>0.15820050601358712</v>
+      </c>
+      <c r="K165" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="J165" s="64">
-        <v>0.28723525588121712</v>
-      </c>
-      <c r="K165" s="63" t="s">
-        <v>47</v>
-      </c>
       <c r="L165" s="64">
-        <v>0.15172114682150784</v>
+        <v>0.3147452225493938</v>
       </c>
     </row>
     <row r="166" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B166" s="62">
+        <v>3</v>
+      </c>
+      <c r="C166" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="D166" s="64">
+        <v>4.2840771913129516E-2</v>
+      </c>
+      <c r="E166" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="F166" s="64">
+        <v>8.5088826951069493E-2</v>
+      </c>
+      <c r="G166" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H166" s="64">
+        <v>4.7015359765124574E-2</v>
+      </c>
+      <c r="I166" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="J166" s="64">
+        <v>5.8761668916191244E-2</v>
+      </c>
+      <c r="K166" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L166" s="64">
+        <v>0.22797990491969664</v>
+      </c>
+    </row>
+    <row r="167" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B167" s="62">
         <v>4</v>
       </c>
-      <c r="C166" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="D166" s="64">
-        <v>4.5532052134282679E-2</v>
-      </c>
-      <c r="E166" s="63" t="s">
+      <c r="C167" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D167" s="64">
+        <v>2.2227012778548615E-2</v>
+      </c>
+      <c r="E167" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="F166" s="64">
-        <v>7.0728088054646962E-2</v>
-      </c>
-      <c r="G166" s="63" t="s">
+      <c r="F167" s="64">
+        <v>6.5926862342592873E-2</v>
+      </c>
+      <c r="G167" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="H167" s="64">
+        <v>3.736282532991364E-2</v>
+      </c>
+      <c r="I167" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="H166" s="64">
-        <v>8.5307440259536238E-2</v>
-      </c>
-      <c r="I166" s="63" t="s">
-        <v>48</v>
-      </c>
-      <c r="J166" s="64">
-        <v>8.2090814074898918E-2</v>
-      </c>
-      <c r="K166" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="L166" s="64">
-        <v>0.10921931857179011</v>
-      </c>
-    </row>
-    <row r="167" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="67">
+      <c r="J167" s="64">
+        <v>3.2325503388409151E-2</v>
+      </c>
+      <c r="K167" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="L167" s="64">
+        <v>3.6802362175851679E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B168" s="67">
         <v>5</v>
       </c>
-      <c r="C167" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="D167" s="71">
-        <v>4.3745263246390706E-2</v>
-      </c>
-      <c r="E167" s="70" t="s">
+      <c r="C168" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="D168" s="71">
+        <v>1.1693192333953578E-2</v>
+      </c>
+      <c r="E168" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="F168" s="71">
+        <v>1.5911393184143145E-2</v>
+      </c>
+      <c r="G168" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="H168" s="71">
+        <v>1.8406208972710805E-2</v>
+      </c>
+      <c r="I168" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="J168" s="71">
+        <v>1.9240067334593453E-2</v>
+      </c>
+      <c r="K168" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="L168" s="71">
+        <v>2.6962511802828951E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C169" s="55" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="170" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="171" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C171" s="121">
+        <v>2014</v>
+      </c>
+      <c r="D171" s="122"/>
+      <c r="E171" s="122"/>
+      <c r="F171" s="122"/>
+      <c r="G171" s="122"/>
+      <c r="H171" s="122"/>
+      <c r="I171" s="122"/>
+      <c r="J171" s="122"/>
+      <c r="K171" s="122"/>
+      <c r="L171" s="123"/>
+    </row>
+    <row r="172" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B172" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C172" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D172" s="128"/>
+      <c r="E172" s="127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F172" s="129"/>
+      <c r="G172" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="H172" s="128"/>
+      <c r="I172" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="J172" s="128"/>
+      <c r="K172" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L172" s="128"/>
+    </row>
+    <row r="173" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B173" s="59">
+        <v>1</v>
+      </c>
+      <c r="C173" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="F167" s="71">
-        <v>5.1242741750176082E-2</v>
-      </c>
-      <c r="G167" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="H167" s="71">
-        <v>7.5719859170663803E-2</v>
-      </c>
-      <c r="I167" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="J167" s="71">
-        <v>1.0823423760214189E-2</v>
-      </c>
-      <c r="K167" s="70" t="s">
+      <c r="D173" s="61">
+        <v>0.35303102759335558</v>
+      </c>
+      <c r="E173" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="F173" s="61">
+        <v>0.54043709483375768</v>
+      </c>
+      <c r="G173" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H173" s="61">
+        <v>0.37397009143091609</v>
+      </c>
+      <c r="I173" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="L167" s="71">
-        <v>8.8999977405094438E-2</v>
-      </c>
-    </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C168" s="55" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="169" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="170" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C170" s="121" t="s">
-        <v>62</v>
-      </c>
-      <c r="D170" s="122"/>
-      <c r="E170" s="122"/>
-      <c r="F170" s="122"/>
-      <c r="G170" s="122"/>
-      <c r="H170" s="122"/>
-      <c r="I170" s="122"/>
-      <c r="J170" s="122"/>
-      <c r="K170" s="122"/>
-      <c r="L170" s="123"/>
-    </row>
-    <row r="171" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B171" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="C171" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="D171" s="128"/>
-      <c r="E171" s="127" t="s">
-        <v>29</v>
-      </c>
-      <c r="F171" s="129"/>
-      <c r="G171" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="H171" s="128"/>
-      <c r="I171" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="J171" s="128"/>
-      <c r="K171" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="L171" s="128"/>
-    </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B172" s="59">
-        <v>1</v>
-      </c>
-      <c r="C172" s="60" t="s">
+      <c r="J173" s="61">
+        <v>0.29608663572744515</v>
+      </c>
+      <c r="K173" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D172" s="61">
-        <v>0.63649410274936569</v>
-      </c>
-      <c r="E172" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="F172" s="61">
-        <v>0.51223385257064658</v>
-      </c>
-      <c r="G172" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="H172" s="61">
-        <v>0.36942528406944874</v>
-      </c>
-      <c r="I172" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="J172" s="61">
-        <v>0.49028244112400543</v>
-      </c>
-      <c r="K172" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="L172" s="61">
-        <v>0.40586434489474205</v>
-      </c>
-    </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B173" s="62">
-        <v>2</v>
-      </c>
-      <c r="C173" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D173" s="64">
-        <v>0.26635141037644589</v>
-      </c>
-      <c r="E173" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="F173" s="64">
-        <v>0.30115436889377417</v>
-      </c>
-      <c r="G173" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="H173" s="64">
-        <v>0.26960107218485957</v>
-      </c>
-      <c r="I173" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="J173" s="64">
-        <v>0.21603809859399034</v>
-      </c>
-      <c r="K173" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="L173" s="64">
-        <v>0.26388836479280681</v>
+      <c r="L173" s="61">
+        <v>0.4000050447309148</v>
       </c>
     </row>
     <row r="174" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B174" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C174" s="63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D174" s="64">
-        <v>3.6589946407362683E-2</v>
+        <v>0.33016023316913623</v>
       </c>
       <c r="E174" s="63" t="s">
         <v>42</v>
       </c>
       <c r="F174" s="64">
-        <v>5.3601498325642101E-2</v>
+        <v>0.15021429354024046</v>
       </c>
       <c r="G174" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H174" s="64">
+        <v>0.23333391436244807</v>
+      </c>
+      <c r="I174" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="H174" s="64">
-        <v>0.25378660109823681</v>
-      </c>
-      <c r="I174" s="63" t="s">
+      <c r="J174" s="64">
+        <v>0.28725887699701946</v>
+      </c>
+      <c r="K174" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="J174" s="64">
-        <v>0.19381062831452189</v>
-      </c>
-      <c r="K174" s="63" t="s">
-        <v>47</v>
-      </c>
       <c r="L174" s="64">
-        <v>0.1720486559768597</v>
+        <v>0.15470072550889394</v>
       </c>
     </row>
     <row r="175" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B175" s="62">
+        <v>3</v>
+      </c>
+      <c r="C175" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="D175" s="64">
+        <v>0.1852721722674015</v>
+      </c>
+      <c r="E175" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F175" s="64">
+        <v>0.12082774791337439</v>
+      </c>
+      <c r="G175" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="H175" s="64">
+        <v>0.15037150116906767</v>
+      </c>
+      <c r="I175" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="J175" s="64">
+        <v>0.28723525588121712</v>
+      </c>
+      <c r="K175" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="L175" s="64">
+        <v>0.15172114682150784</v>
+      </c>
+    </row>
+    <row r="176" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B176" s="62">
         <v>4</v>
       </c>
-      <c r="C175" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="D175" s="64">
-        <v>1.69653663024559E-2</v>
-      </c>
-      <c r="E175" s="63" t="s">
+      <c r="C176" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D176" s="64">
+        <v>4.5532052134282679E-2</v>
+      </c>
+      <c r="E176" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F176" s="64">
+        <v>7.0728088054646962E-2</v>
+      </c>
+      <c r="G176" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H176" s="64">
+        <v>8.5307440259536238E-2</v>
+      </c>
+      <c r="I176" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="J176" s="64">
+        <v>8.2090814074898918E-2</v>
+      </c>
+      <c r="K176" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="L176" s="64">
+        <v>0.10921931857179011</v>
+      </c>
+    </row>
+    <row r="177" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B177" s="67">
+        <v>5</v>
+      </c>
+      <c r="C177" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="D177" s="71">
+        <v>4.3745263246390706E-2</v>
+      </c>
+      <c r="E177" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="F175" s="64">
-        <v>4.8879684601334884E-2</v>
-      </c>
-      <c r="G175" s="63" t="s">
+      <c r="F177" s="71">
+        <v>5.1242741750176082E-2</v>
+      </c>
+      <c r="G177" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="H177" s="71">
+        <v>7.5719859170663803E-2</v>
+      </c>
+      <c r="I177" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="J177" s="71">
+        <v>1.0823423760214189E-2</v>
+      </c>
+      <c r="K177" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="H175" s="64">
-        <v>6.3694354205840825E-2</v>
-      </c>
-      <c r="I175" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="J175" s="64">
-        <v>3.6899574824585057E-2</v>
-      </c>
-      <c r="K175" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="L175" s="64">
-        <v>7.5036655165964999E-2</v>
-      </c>
-    </row>
-    <row r="176" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B176" s="67">
-        <v>5</v>
-      </c>
-      <c r="C176" s="70" t="s">
-        <v>63</v>
-      </c>
-      <c r="D176" s="71">
-        <v>9.8618239503575136E-3</v>
-      </c>
-      <c r="E176" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="F176" s="71">
-        <v>3.0124826315179851E-2</v>
-      </c>
-      <c r="G176" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="H176" s="71">
-        <v>1.6348850240469517E-2</v>
-      </c>
-      <c r="I176" s="70" t="s">
+      <c r="L177" s="71">
+        <v>8.8999977405094438E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C178" s="55" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="179" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="180" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C180" s="121" t="s">
+        <v>62</v>
+      </c>
+      <c r="D180" s="122"/>
+      <c r="E180" s="122"/>
+      <c r="F180" s="122"/>
+      <c r="G180" s="122"/>
+      <c r="H180" s="122"/>
+      <c r="I180" s="122"/>
+      <c r="J180" s="122"/>
+      <c r="K180" s="122"/>
+      <c r="L180" s="123"/>
+    </row>
+    <row r="181" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B181" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C181" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D181" s="128"/>
+      <c r="E181" s="127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F181" s="129"/>
+      <c r="G181" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="H181" s="128"/>
+      <c r="I181" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="J181" s="128"/>
+      <c r="K181" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L181" s="128"/>
+    </row>
+    <row r="182" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B182" s="59">
+        <v>1</v>
+      </c>
+      <c r="C182" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D182" s="61">
+        <v>0.63649410274936569</v>
+      </c>
+      <c r="E182" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="J176" s="71">
-        <v>2.9001160955910741E-2</v>
-      </c>
-      <c r="K176" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="L176" s="71">
-        <v>3.0815182856372417E-2</v>
-      </c>
-    </row>
-    <row r="177" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C177" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="I177" s="1"/>
-    </row>
-    <row r="178" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="179" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C179" s="121" t="s">
-        <v>64</v>
-      </c>
-      <c r="D179" s="122"/>
-      <c r="E179" s="122"/>
-      <c r="F179" s="122"/>
-      <c r="G179" s="122"/>
-      <c r="H179" s="122"/>
-      <c r="I179" s="122"/>
-      <c r="J179" s="122"/>
-      <c r="K179" s="122"/>
-      <c r="L179" s="123"/>
-    </row>
-    <row r="180" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B180" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="C180" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="D180" s="128"/>
-      <c r="E180" s="127" t="s">
-        <v>29</v>
-      </c>
-      <c r="F180" s="129"/>
-      <c r="G180" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="H180" s="128"/>
-      <c r="I180" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="J180" s="128"/>
-      <c r="K180" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="L180" s="128"/>
-    </row>
-    <row r="181" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B181" s="59">
-        <v>1</v>
-      </c>
-      <c r="C181" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="D181" s="61">
-        <v>0.45029999999999998</v>
-      </c>
-      <c r="E181" s="60" t="s">
+      <c r="F182" s="61">
+        <v>0.51223385257064658</v>
+      </c>
+      <c r="G182" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="F181" s="61">
-        <v>0.62799103297155212</v>
-      </c>
-      <c r="G181" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="H181" s="61">
-        <v>0.66332697836058707</v>
-      </c>
-      <c r="I181" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="J181" s="61">
-        <v>0.74188444978472012</v>
-      </c>
-      <c r="K181" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="L181" s="61">
-        <v>0.56009615005259272</v>
-      </c>
-    </row>
-    <row r="182" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B182" s="62">
-        <v>2</v>
-      </c>
-      <c r="C182" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D182" s="64">
-        <v>0.22889999999999999</v>
-      </c>
-      <c r="E182" s="63" t="s">
+      <c r="H182" s="61">
+        <v>0.36942528406944874</v>
+      </c>
+      <c r="I182" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="F182" s="64">
-        <v>0.20815370409161937</v>
-      </c>
-      <c r="G182" s="63" t="s">
+      <c r="J182" s="61">
+        <v>0.49028244112400543</v>
+      </c>
+      <c r="K182" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H182" s="64">
-        <v>0.31567436082025857</v>
-      </c>
-      <c r="I182" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="J182" s="64">
-        <v>0.16020827075197758</v>
-      </c>
-      <c r="K182" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="L182" s="64">
-        <v>0.19123177260392824</v>
+      <c r="L182" s="61">
+        <v>0.40586434489474205</v>
       </c>
     </row>
     <row r="183" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B183" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C183" s="63" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D183" s="64">
-        <v>0.12039999999999999</v>
+        <v>0.26635141037644589</v>
       </c>
       <c r="E183" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="F183" s="64">
+        <v>0.30115436889377417</v>
+      </c>
+      <c r="G183" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="F183" s="64">
-        <v>3.6086348760789533E-2</v>
-      </c>
-      <c r="G183" s="63" t="s">
-        <v>50</v>
-      </c>
       <c r="H183" s="64">
-        <v>5.7835397270450412E-3</v>
+        <v>0.26960107218485957</v>
       </c>
       <c r="I183" s="63" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J183" s="64">
-        <v>3.2041654150395511E-2</v>
+        <v>0.21603809859399034</v>
       </c>
       <c r="K183" s="63" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L183" s="64">
-        <v>0.12819710394351375</v>
+        <v>0.26388836479280681</v>
       </c>
     </row>
     <row r="184" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B184" s="62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C184" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D184" s="64">
+        <v>3.6589946407362683E-2</v>
+      </c>
+      <c r="E184" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F184" s="64">
+        <v>5.3601498325642101E-2</v>
+      </c>
+      <c r="G184" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="D184" s="64">
-        <v>0.11</v>
-      </c>
-      <c r="E184" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="F184" s="64">
-        <v>3.3950816610743048E-2</v>
-      </c>
-      <c r="G184" s="63" t="s">
-        <v>57</v>
-      </c>
       <c r="H184" s="64">
-        <v>4.3521728933314727E-3</v>
+        <v>0.25378660109823681</v>
       </c>
       <c r="I184" s="63" t="s">
         <v>42</v>
       </c>
       <c r="J184" s="64">
-        <v>2.4031240612796635E-2</v>
+        <v>0.19381062831452189</v>
       </c>
       <c r="K184" s="63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L184" s="64">
-        <v>3.1732783226852718E-2</v>
-      </c>
-    </row>
-    <row r="185" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B185" s="67">
+        <v>0.1720486559768597</v>
+      </c>
+    </row>
+    <row r="185" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B185" s="62">
+        <v>4</v>
+      </c>
+      <c r="C185" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="D185" s="64">
+        <v>1.69653663024559E-2</v>
+      </c>
+      <c r="E185" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F185" s="64">
+        <v>4.8879684601334884E-2</v>
+      </c>
+      <c r="G185" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H185" s="64">
+        <v>6.3694354205840825E-2</v>
+      </c>
+      <c r="I185" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="J185" s="64">
+        <v>3.6899574824585057E-2</v>
+      </c>
+      <c r="K185" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L185" s="64">
+        <v>7.5036655165964999E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B186" s="67">
         <v>5</v>
       </c>
-      <c r="C185" s="70" t="s">
+      <c r="C186" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="D186" s="71">
+        <v>9.8618239503575136E-3</v>
+      </c>
+      <c r="E186" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="F186" s="71">
+        <v>3.0124826315179851E-2</v>
+      </c>
+      <c r="G186" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="D185" s="71">
-        <v>5.8799999999999998E-2</v>
-      </c>
-      <c r="E185" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="F185" s="71">
-        <v>2.9394127780606526E-2</v>
-      </c>
-      <c r="G185" s="70" t="s">
+      <c r="H186" s="71">
+        <v>1.6348850240469517E-2</v>
+      </c>
+      <c r="I186" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="J186" s="71">
+        <v>2.9001160955910741E-2</v>
+      </c>
+      <c r="K186" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="H185" s="71">
-        <v>3.3923064708847165E-3</v>
-      </c>
-      <c r="I185" s="70" t="s">
-        <v>65</v>
-      </c>
-      <c r="J185" s="71">
-        <v>1.5860618804445781E-2</v>
-      </c>
-      <c r="K185" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="L185" s="71">
-        <v>2.6113367108704596E-2</v>
-      </c>
-    </row>
-    <row r="186" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C186" s="55" t="s">
+      <c r="L186" s="71">
+        <v>3.0815182856372417E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C187" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I186" s="1"/>
-    </row>
-    <row r="187" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="188" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C188" s="121" t="s">
-        <v>66</v>
-      </c>
-      <c r="D188" s="122"/>
-      <c r="E188" s="122"/>
-      <c r="F188" s="122"/>
-      <c r="G188" s="122"/>
-      <c r="H188" s="122"/>
-      <c r="I188" s="122"/>
-      <c r="J188" s="122"/>
-      <c r="K188" s="122"/>
-      <c r="L188" s="123"/>
-    </row>
-    <row r="189" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B189" s="58" t="s">
+      <c r="I187" s="1"/>
+    </row>
+    <row r="188" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="189" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C189" s="121" t="s">
+        <v>64</v>
+      </c>
+      <c r="D189" s="122"/>
+      <c r="E189" s="122"/>
+      <c r="F189" s="122"/>
+      <c r="G189" s="122"/>
+      <c r="H189" s="122"/>
+      <c r="I189" s="122"/>
+      <c r="J189" s="122"/>
+      <c r="K189" s="122"/>
+      <c r="L189" s="123"/>
+    </row>
+    <row r="190" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B190" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C189" s="127" t="s">
+      <c r="C190" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D189" s="128"/>
-      <c r="E189" s="127" t="s">
+      <c r="D190" s="128"/>
+      <c r="E190" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F189" s="129"/>
-      <c r="G189" s="127" t="s">
+      <c r="F190" s="129"/>
+      <c r="G190" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H189" s="128"/>
-      <c r="I189" s="129" t="s">
+      <c r="H190" s="128"/>
+      <c r="I190" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J189" s="128"/>
-      <c r="K189" s="129" t="s">
+      <c r="J190" s="128"/>
+      <c r="K190" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L189" s="128"/>
-    </row>
-    <row r="190" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B190" s="59">
+      <c r="L190" s="128"/>
+    </row>
+    <row r="191" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B191" s="59">
         <v>1</v>
       </c>
-      <c r="C190" s="60" t="s">
+      <c r="C191" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="D191" s="61">
+        <v>0.45029999999999998</v>
+      </c>
+      <c r="E191" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D190" s="61">
-        <v>0.38341665486747623</v>
-      </c>
-      <c r="E190" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="F190" s="61">
-        <v>0.38904446152664746</v>
-      </c>
-      <c r="G190" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="H190" s="61">
-        <v>0.49744610076612755</v>
-      </c>
-      <c r="I190" s="60" t="s">
+      <c r="F191" s="61">
+        <v>0.62799103297155212</v>
+      </c>
+      <c r="G191" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="J190" s="61">
-        <v>0.35915463730881969</v>
-      </c>
-      <c r="K190" s="60" t="s">
+      <c r="H191" s="61">
+        <v>0.66332697836058707</v>
+      </c>
+      <c r="I191" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="L190" s="61">
-        <v>0.33059073620770085</v>
-      </c>
-    </row>
-    <row r="191" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B191" s="62">
-        <v>2</v>
-      </c>
-      <c r="C191" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="D191" s="64">
-        <v>0.29567360402030857</v>
-      </c>
-      <c r="E191" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="F191" s="64">
-        <v>0.26747914724759236</v>
-      </c>
-      <c r="G191" s="63" t="s">
+      <c r="J191" s="61">
+        <v>0.74188444978472012</v>
+      </c>
+      <c r="K191" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="H191" s="64">
-        <v>0.38673530392857286</v>
-      </c>
-      <c r="I191" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="J191" s="64">
-        <v>0.26537209628805097</v>
-      </c>
-      <c r="K191" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="L191" s="64">
-        <v>0.30499969251560843</v>
+      <c r="L191" s="61">
+        <v>0.56009615005259272</v>
       </c>
     </row>
     <row r="192" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B192" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C192" s="63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D192" s="64">
-        <v>0.18098252108561677</v>
+        <v>0.22889999999999999</v>
       </c>
       <c r="E192" s="63" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F192" s="64">
-        <v>0.2061997106511694</v>
+        <v>0.20815370409161937</v>
       </c>
       <c r="G192" s="63" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="H192" s="64">
-        <v>7.8603419966623955E-2</v>
+        <v>0.31567436082025857</v>
       </c>
       <c r="I192" s="63" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J192" s="64">
-        <v>0.19101727824159773</v>
+        <v>0.16020827075197758</v>
       </c>
       <c r="K192" s="63" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L192" s="64">
-        <v>0.18301746910003341</v>
+        <v>0.19123177260392824</v>
       </c>
     </row>
     <row r="193" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B193" s="62">
+        <v>3</v>
+      </c>
+      <c r="C193" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="D193" s="64">
+        <v>0.12039999999999999</v>
+      </c>
+      <c r="E193" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F193" s="64">
+        <v>3.6086348760789533E-2</v>
+      </c>
+      <c r="G193" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="H193" s="64">
+        <v>5.7835397270450412E-3</v>
+      </c>
+      <c r="I193" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="J193" s="64">
+        <v>3.2041654150395511E-2</v>
+      </c>
+      <c r="K193" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="L193" s="64">
+        <v>0.12819710394351375</v>
+      </c>
+    </row>
+    <row r="194" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B194" s="62">
         <v>4</v>
       </c>
-      <c r="C193" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="D193" s="64">
-        <v>2.3283089457255775E-2</v>
-      </c>
-      <c r="E193" s="63" t="s">
+      <c r="C194" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="D194" s="64">
+        <v>0.11</v>
+      </c>
+      <c r="E194" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F194" s="64">
+        <v>3.3950816610743048E-2</v>
+      </c>
+      <c r="G194" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="H194" s="64">
+        <v>4.3521728933314727E-3</v>
+      </c>
+      <c r="I194" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="F193" s="64">
-        <v>8.3339647253379903E-2</v>
-      </c>
-      <c r="G193" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="H193" s="64">
-        <v>1.6891211719736642E-2</v>
-      </c>
-      <c r="I193" s="63" t="s">
+      <c r="J194" s="64">
+        <v>2.4031240612796635E-2</v>
+      </c>
+      <c r="K194" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="L194" s="64">
+        <v>3.1732783226852718E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B195" s="67">
+        <v>5</v>
+      </c>
+      <c r="C195" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="D195" s="71">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="E195" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="F195" s="71">
+        <v>2.9394127780606526E-2</v>
+      </c>
+      <c r="G195" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="J193" s="64">
-        <v>0.10577911651823832</v>
-      </c>
-      <c r="K193" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="L193" s="64">
-        <v>0.10752415874965109</v>
-      </c>
-    </row>
-    <row r="194" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B194" s="67">
-        <v>5</v>
-      </c>
-      <c r="C194" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="D194" s="71">
-        <v>1.8596750438780167E-2</v>
-      </c>
-      <c r="E194" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F194" s="71">
-        <v>2.3815912929158911E-2</v>
-      </c>
-      <c r="G194" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="H194" s="71">
-        <v>4.6908594361254842E-3</v>
-      </c>
-      <c r="I194" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="J194" s="71">
-        <v>4.8102005527994006E-2</v>
-      </c>
-      <c r="K194" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="L194" s="71">
-        <v>1.1572786907853535E-2</v>
-      </c>
-    </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C195" s="55" t="s">
+      <c r="H195" s="71">
+        <v>3.3923064708847165E-3</v>
+      </c>
+      <c r="I195" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="J195" s="71">
+        <v>1.5860618804445781E-2</v>
+      </c>
+      <c r="K195" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="L195" s="71">
+        <v>2.6113367108704596E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C196" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I195" s="1"/>
-    </row>
-    <row r="196" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="197" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C197" s="121" t="s">
-        <v>67</v>
-      </c>
-      <c r="D197" s="122"/>
-      <c r="E197" s="122"/>
-      <c r="F197" s="122"/>
-      <c r="G197" s="122"/>
-      <c r="H197" s="122"/>
-      <c r="I197" s="122"/>
-      <c r="J197" s="122"/>
-      <c r="K197" s="122"/>
-      <c r="L197" s="123"/>
-    </row>
-    <row r="198" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B198" s="58" t="s">
+      <c r="I196" s="1"/>
+    </row>
+    <row r="197" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="198" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C198" s="121" t="s">
+        <v>66</v>
+      </c>
+      <c r="D198" s="122"/>
+      <c r="E198" s="122"/>
+      <c r="F198" s="122"/>
+      <c r="G198" s="122"/>
+      <c r="H198" s="122"/>
+      <c r="I198" s="122"/>
+      <c r="J198" s="122"/>
+      <c r="K198" s="122"/>
+      <c r="L198" s="123"/>
+    </row>
+    <row r="199" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B199" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C198" s="127" t="s">
+      <c r="C199" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D198" s="128"/>
-      <c r="E198" s="127" t="s">
+      <c r="D199" s="128"/>
+      <c r="E199" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F198" s="129"/>
-      <c r="G198" s="127" t="s">
+      <c r="F199" s="129"/>
+      <c r="G199" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H198" s="128"/>
-      <c r="I198" s="129" t="s">
+      <c r="H199" s="128"/>
+      <c r="I199" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J198" s="128"/>
-      <c r="K198" s="129" t="s">
+      <c r="J199" s="128"/>
+      <c r="K199" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L198" s="128"/>
-    </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B199" s="59">
+      <c r="L199" s="128"/>
+    </row>
+    <row r="200" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B200" s="59">
         <v>1</v>
       </c>
-      <c r="C199" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="D199" s="75">
-        <v>33.08</v>
-      </c>
-      <c r="E199" s="63" t="s">
+      <c r="C200" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="D200" s="61">
+        <v>0.38341665486747623</v>
+      </c>
+      <c r="E200" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="F199" s="76">
-        <v>32.85</v>
-      </c>
-      <c r="G199" s="63" t="s">
+      <c r="F200" s="61">
+        <v>0.38904446152664746</v>
+      </c>
+      <c r="G200" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H199" s="75">
-        <v>62.26</v>
-      </c>
-      <c r="I199" s="77" t="s">
+      <c r="H200" s="61">
+        <v>0.49744610076612755</v>
+      </c>
+      <c r="I200" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="J199" s="75">
-        <v>47.57</v>
-      </c>
-      <c r="K199" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="L199" s="78">
-        <v>28.731616780943668</v>
-      </c>
-    </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B200" s="62">
-        <v>2</v>
-      </c>
-      <c r="C200" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="D200" s="75">
-        <v>18.91</v>
-      </c>
-      <c r="E200" s="63" t="s">
+      <c r="J200" s="61">
+        <v>0.35915463730881969</v>
+      </c>
+      <c r="K200" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="F200" s="76">
-        <v>31.02</v>
-      </c>
-      <c r="G200" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="H200" s="75">
-        <v>12.99</v>
-      </c>
-      <c r="I200" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="J200" s="75">
-        <v>17.510000000000002</v>
-      </c>
-      <c r="K200" s="77" t="s">
-        <v>41</v>
-      </c>
-      <c r="L200" s="78">
-        <v>24.900244431581076</v>
+      <c r="L200" s="61">
+        <v>0.33059073620770085</v>
       </c>
     </row>
     <row r="201" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B201" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C201" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D201" s="75">
-        <v>9.61</v>
+        <v>54</v>
+      </c>
+      <c r="D201" s="64">
+        <v>0.29567360402030857</v>
       </c>
       <c r="E201" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="F201" s="76">
-        <v>26.73</v>
+      <c r="F201" s="64">
+        <v>0.26747914724759236</v>
       </c>
       <c r="G201" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H201" s="75">
-        <v>11.57</v>
-      </c>
-      <c r="I201" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="J201" s="75">
-        <v>14.59</v>
-      </c>
-      <c r="K201" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="L201" s="78">
-        <v>14.504883696204814</v>
+        <v>41</v>
+      </c>
+      <c r="H201" s="64">
+        <v>0.38673530392857286</v>
+      </c>
+      <c r="I201" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="J201" s="64">
+        <v>0.26537209628805097</v>
+      </c>
+      <c r="K201" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="L201" s="64">
+        <v>0.30499969251560843</v>
       </c>
     </row>
     <row r="202" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B202" s="62">
+        <v>3</v>
+      </c>
+      <c r="C202" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="D202" s="64">
+        <v>0.18098252108561677</v>
+      </c>
+      <c r="E202" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F202" s="64">
+        <v>0.2061997106511694</v>
+      </c>
+      <c r="G202" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H202" s="64">
+        <v>7.8603419966623955E-2</v>
+      </c>
+      <c r="I202" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="J202" s="64">
+        <v>0.19101727824159773</v>
+      </c>
+      <c r="K202" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="L202" s="64">
+        <v>0.18301746910003341</v>
+      </c>
+    </row>
+    <row r="203" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B203" s="62">
         <v>4</v>
       </c>
-      <c r="C202" s="63" t="s">
+      <c r="C203" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D203" s="64">
+        <v>2.3283089457255775E-2</v>
+      </c>
+      <c r="E203" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F203" s="64">
+        <v>8.3339647253379903E-2</v>
+      </c>
+      <c r="G203" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="D202" s="75">
-        <v>8.42</v>
-      </c>
-      <c r="E202" s="63" t="s">
+      <c r="H203" s="64">
+        <v>1.6891211719736642E-2</v>
+      </c>
+      <c r="I203" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="J203" s="64">
+        <v>0.10577911651823832</v>
+      </c>
+      <c r="K203" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L203" s="64">
+        <v>0.10752415874965109</v>
+      </c>
+    </row>
+    <row r="204" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B204" s="67">
+        <v>5</v>
+      </c>
+      <c r="C204" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="F202" s="76">
-        <v>3.21</v>
-      </c>
-      <c r="G202" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="H202" s="75">
-        <v>2.35</v>
-      </c>
-      <c r="I202" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="J202" s="75">
-        <v>5.91</v>
-      </c>
-      <c r="K202" s="77" t="s">
+      <c r="D204" s="71">
+        <v>1.8596750438780167E-2</v>
+      </c>
+      <c r="E204" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="F204" s="71">
+        <v>2.3815912929158911E-2</v>
+      </c>
+      <c r="G204" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="H204" s="71">
+        <v>4.6908594361254842E-3</v>
+      </c>
+      <c r="I204" s="70" t="s">
+        <v>48</v>
+      </c>
+      <c r="J204" s="71">
+        <v>4.8102005527994006E-2</v>
+      </c>
+      <c r="K204" s="70" t="s">
+        <v>48</v>
+      </c>
+      <c r="L204" s="71">
+        <v>1.1572786907853535E-2</v>
+      </c>
+    </row>
+    <row r="205" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C205" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="I205" s="1"/>
+    </row>
+    <row r="206" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="207" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C207" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="D207" s="122"/>
+      <c r="E207" s="122"/>
+      <c r="F207" s="122"/>
+      <c r="G207" s="122"/>
+      <c r="H207" s="122"/>
+      <c r="I207" s="122"/>
+      <c r="J207" s="122"/>
+      <c r="K207" s="122"/>
+      <c r="L207" s="123"/>
+    </row>
+    <row r="208" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B208" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C208" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D208" s="128"/>
+      <c r="E208" s="127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F208" s="129"/>
+      <c r="G208" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="H208" s="128"/>
+      <c r="I208" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="J208" s="128"/>
+      <c r="K208" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L208" s="128"/>
+    </row>
+    <row r="209" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B209" s="59">
+        <v>1</v>
+      </c>
+      <c r="C209" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="L202" s="78">
-        <v>14.24093170968335</v>
-      </c>
-    </row>
-    <row r="203" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B203" s="67">
-        <v>5</v>
-      </c>
-      <c r="C203" s="70" t="s">
-        <v>51</v>
-      </c>
-      <c r="D203" s="79">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="E203" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F203" s="80">
-        <v>1.52</v>
-      </c>
-      <c r="G203" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="H203" s="79">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="I203" s="81" t="s">
-        <v>54</v>
-      </c>
-      <c r="J203" s="79">
-        <v>4.3099999999999996</v>
-      </c>
-      <c r="K203" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="L203" s="82">
-        <v>2.683768534675095</v>
-      </c>
-    </row>
-    <row r="204" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C204" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="I204" s="1"/>
-    </row>
-    <row r="205" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="206" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C206" s="121" t="s">
-        <v>68</v>
-      </c>
-      <c r="D206" s="122"/>
-      <c r="E206" s="122"/>
-      <c r="F206" s="122"/>
-      <c r="G206" s="122"/>
-      <c r="H206" s="122"/>
-      <c r="I206" s="122"/>
-      <c r="J206" s="122"/>
-      <c r="K206" s="122"/>
-      <c r="L206" s="123"/>
-    </row>
-    <row r="207" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B207" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="C207" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="D207" s="128"/>
-      <c r="E207" s="127" t="s">
-        <v>29</v>
-      </c>
-      <c r="F207" s="129"/>
-      <c r="G207" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="H207" s="128"/>
-      <c r="I207" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="J207" s="128"/>
-      <c r="K207" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="L207" s="128"/>
-    </row>
-    <row r="208" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B208" s="59">
-        <v>1</v>
-      </c>
-      <c r="C208" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D208" s="75">
-        <v>49.92</v>
-      </c>
-      <c r="E208" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="F208" s="76">
-        <v>45.17</v>
-      </c>
-      <c r="G208" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="H208" s="75">
-        <v>36.33</v>
-      </c>
-      <c r="I208" s="77" t="s">
+      <c r="D209" s="75">
+        <v>33.08</v>
+      </c>
+      <c r="E209" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="J208" s="75">
-        <v>17.350000000000001</v>
-      </c>
-      <c r="K208" s="77" t="s">
-        <v>41</v>
-      </c>
-      <c r="L208" s="78">
-        <v>31.979410918310268</v>
-      </c>
-    </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B209" s="62">
-        <v>2</v>
-      </c>
-      <c r="C209" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="D209" s="75">
-        <v>18.809999999999999</v>
-      </c>
-      <c r="E209" s="63" t="s">
-        <v>54</v>
-      </c>
       <c r="F209" s="76">
-        <v>19.14</v>
+        <v>32.85</v>
       </c>
       <c r="G209" s="63" t="s">
         <v>44</v>
       </c>
       <c r="H209" s="75">
-        <v>18.46</v>
+        <v>62.26</v>
       </c>
       <c r="I209" s="77" t="s">
         <v>41</v>
       </c>
       <c r="J209" s="75">
-        <v>15.07</v>
+        <v>47.57</v>
       </c>
       <c r="K209" s="77" t="s">
         <v>44</v>
       </c>
       <c r="L209" s="78">
-        <v>15.252300717474624</v>
+        <v>28.731616780943668</v>
       </c>
     </row>
     <row r="210" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B210" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C210" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="D210" s="75">
+        <v>18.91</v>
+      </c>
+      <c r="E210" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F210" s="76">
+        <v>31.02</v>
+      </c>
+      <c r="G210" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H210" s="75">
+        <v>12.99</v>
+      </c>
+      <c r="I210" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="D210" s="75">
-        <v>8.6</v>
-      </c>
-      <c r="E210" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="F210" s="76">
-        <v>10.36</v>
-      </c>
-      <c r="G210" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="H210" s="75">
-        <v>16.170000000000002</v>
-      </c>
-      <c r="I210" s="77" t="s">
-        <v>42</v>
-      </c>
       <c r="J210" s="75">
-        <v>12.02</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="K210" s="77" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L210" s="78">
-        <v>15.013636578327644</v>
+        <v>24.900244431581076</v>
       </c>
     </row>
     <row r="211" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B211" s="62">
+        <v>3</v>
+      </c>
+      <c r="C211" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D211" s="75">
+        <v>9.61</v>
+      </c>
+      <c r="E211" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F211" s="76">
+        <v>26.73</v>
+      </c>
+      <c r="G211" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H211" s="75">
+        <v>11.57</v>
+      </c>
+      <c r="I211" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="J211" s="75">
+        <v>14.59</v>
+      </c>
+      <c r="K211" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="L211" s="78">
+        <v>14.504883696204814</v>
+      </c>
+    </row>
+    <row r="212" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B212" s="62">
         <v>4</v>
       </c>
-      <c r="C211" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="D211" s="75">
-        <v>6.45</v>
-      </c>
-      <c r="E211" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="F211" s="76">
-        <v>9.9700000000000006</v>
-      </c>
-      <c r="G211" s="63" t="s">
+      <c r="C212" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D212" s="75">
+        <v>8.42</v>
+      </c>
+      <c r="E212" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="F212" s="76">
+        <v>3.21</v>
+      </c>
+      <c r="G212" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="H212" s="75">
+        <v>2.35</v>
+      </c>
+      <c r="I212" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="J212" s="75">
+        <v>5.91</v>
+      </c>
+      <c r="K212" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="L212" s="78">
+        <v>14.24093170968335</v>
+      </c>
+    </row>
+    <row r="213" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B213" s="67">
+        <v>5</v>
+      </c>
+      <c r="C213" s="70" t="s">
+        <v>51</v>
+      </c>
+      <c r="D213" s="79">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="E213" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F213" s="80">
+        <v>1.52</v>
+      </c>
+      <c r="G213" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="H213" s="79">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="I213" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="H211" s="75">
-        <v>15.97</v>
-      </c>
-      <c r="I211" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="J211" s="75">
-        <v>10.69</v>
-      </c>
-      <c r="K211" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="L211" s="78">
-        <v>11.496527327476299</v>
-      </c>
-    </row>
-    <row r="212" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B212" s="67">
-        <v>5</v>
-      </c>
-      <c r="C212" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="D212" s="79">
-        <v>4.82</v>
-      </c>
-      <c r="E212" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="F212" s="80">
-        <v>7.65</v>
-      </c>
-      <c r="G212" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="H212" s="79">
-        <v>3.17</v>
-      </c>
-      <c r="I212" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="J212" s="79">
-        <v>9.5299999999999994</v>
-      </c>
-      <c r="K212" s="81" t="s">
-        <v>42</v>
-      </c>
-      <c r="L212" s="82">
-        <v>5.103206378380694</v>
-      </c>
-    </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C213" s="55" t="s">
+      <c r="J213" s="79">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="K213" s="81" t="s">
+        <v>47</v>
+      </c>
+      <c r="L213" s="82">
+        <v>2.683768534675095</v>
+      </c>
+    </row>
+    <row r="214" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C214" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I213" s="1"/>
-    </row>
-    <row r="214" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="215" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C215" s="121" t="s">
-        <v>71</v>
-      </c>
-      <c r="D215" s="122"/>
-      <c r="E215" s="122"/>
-      <c r="F215" s="122"/>
-      <c r="G215" s="122"/>
-      <c r="H215" s="122"/>
-      <c r="I215" s="122"/>
-      <c r="J215" s="122"/>
-      <c r="K215" s="122"/>
-      <c r="L215" s="123"/>
-    </row>
-    <row r="216" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B216" s="58" t="s">
+      <c r="I214" s="1"/>
+    </row>
+    <row r="215" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="216" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C216" s="121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" s="122"/>
+      <c r="E216" s="122"/>
+      <c r="F216" s="122"/>
+      <c r="G216" s="122"/>
+      <c r="H216" s="122"/>
+      <c r="I216" s="122"/>
+      <c r="J216" s="122"/>
+      <c r="K216" s="122"/>
+      <c r="L216" s="123"/>
+    </row>
+    <row r="217" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B217" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C216" s="127" t="s">
+      <c r="C217" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D216" s="128"/>
-      <c r="E216" s="127" t="s">
+      <c r="D217" s="128"/>
+      <c r="E217" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F216" s="129"/>
-      <c r="G216" s="127" t="s">
+      <c r="F217" s="129"/>
+      <c r="G217" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H216" s="128"/>
-      <c r="I216" s="129" t="s">
+      <c r="H217" s="128"/>
+      <c r="I217" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J216" s="128"/>
-      <c r="K216" s="129" t="s">
+      <c r="J217" s="128"/>
+      <c r="K217" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L216" s="128"/>
-    </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B217" s="59">
+      <c r="L217" s="128"/>
+    </row>
+    <row r="218" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B218" s="59">
         <v>1</v>
       </c>
-      <c r="C217" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="D217" s="75">
-        <v>60.73</v>
-      </c>
-      <c r="E217" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="F217" s="76">
-        <v>71.02</v>
-      </c>
-      <c r="G217" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="H217" s="75">
-        <v>64.930000000000007</v>
-      </c>
-      <c r="I217" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="J217" s="75">
-        <v>56.49</v>
-      </c>
-      <c r="K217" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="L217" s="78">
-        <v>57.975112877136368</v>
-      </c>
-    </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B218" s="62">
-        <v>2</v>
-      </c>
       <c r="C218" s="63" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D218" s="75">
-        <v>16.61</v>
+        <v>49.92</v>
       </c>
       <c r="E218" s="63" t="s">
         <v>41</v>
       </c>
       <c r="F218" s="76">
-        <v>15.04</v>
+        <v>45.17</v>
       </c>
       <c r="G218" s="63" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="H218" s="75">
-        <v>17.66</v>
+        <v>36.33</v>
       </c>
       <c r="I218" s="77" t="s">
         <v>44</v>
       </c>
       <c r="J218" s="75">
-        <v>28.3</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="K218" s="77" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L218" s="78">
-        <v>23.909086455400878</v>
+        <v>31.979410918310268</v>
       </c>
     </row>
     <row r="219" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B219" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C219" s="63" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D219" s="75">
-        <v>13.71</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="E219" s="63" t="s">
         <v>54</v>
       </c>
       <c r="F219" s="76">
-        <v>10.09</v>
+        <v>19.14</v>
       </c>
       <c r="G219" s="63" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="H219" s="75">
-        <v>6.77</v>
+        <v>18.46</v>
       </c>
       <c r="I219" s="77" t="s">
         <v>41</v>
       </c>
       <c r="J219" s="75">
-        <v>4.96</v>
+        <v>15.07</v>
       </c>
       <c r="K219" s="77" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L219" s="78">
-        <v>9.2748392805072868</v>
+        <v>15.252300717474624</v>
       </c>
     </row>
     <row r="220" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B220" s="62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C220" s="63" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D220" s="75">
-        <v>3.62</v>
+        <v>8.6</v>
       </c>
       <c r="E220" s="63" t="s">
         <v>69</v>
       </c>
       <c r="F220" s="76">
-        <v>2.74</v>
+        <v>10.36</v>
       </c>
       <c r="G220" s="63" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="H220" s="75">
-        <v>5.51</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="I220" s="77" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J220" s="75">
-        <v>4.33</v>
+        <v>12.02</v>
       </c>
       <c r="K220" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="L220" s="78">
+        <v>15.013636578327644</v>
+      </c>
+    </row>
+    <row r="221" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B221" s="62">
+        <v>4</v>
+      </c>
+      <c r="C221" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="L220" s="78">
-        <v>3.6608380925300299</v>
-      </c>
-    </row>
-    <row r="221" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B221" s="67">
+      <c r="D221" s="75">
+        <v>6.45</v>
+      </c>
+      <c r="E221" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="F221" s="76">
+        <v>9.9700000000000006</v>
+      </c>
+      <c r="G221" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H221" s="75">
+        <v>15.97</v>
+      </c>
+      <c r="I221" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="J221" s="75">
+        <v>10.69</v>
+      </c>
+      <c r="K221" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="L221" s="78">
+        <v>11.496527327476299</v>
+      </c>
+    </row>
+    <row r="222" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B222" s="67">
         <v>5</v>
       </c>
-      <c r="C221" s="70" t="s">
+      <c r="C222" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="D222" s="79">
+        <v>4.82</v>
+      </c>
+      <c r="E222" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="F222" s="80">
+        <v>7.65</v>
+      </c>
+      <c r="G222" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="H222" s="79">
+        <v>3.17</v>
+      </c>
+      <c r="I222" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="D221" s="79">
-        <v>1.61</v>
-      </c>
-      <c r="E221" s="70" t="s">
-        <v>72</v>
-      </c>
-      <c r="F221" s="80">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="G221" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="H221" s="79">
-        <v>3.19</v>
-      </c>
-      <c r="I221" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="J221" s="79">
-        <v>1.24</v>
-      </c>
-      <c r="K221" s="81" t="s">
-        <v>49</v>
-      </c>
-      <c r="L221" s="82">
-        <v>2.6064493809976668</v>
-      </c>
-    </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C222" s="55" t="s">
+      <c r="J222" s="79">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="K222" s="81" t="s">
+        <v>42</v>
+      </c>
+      <c r="L222" s="82">
+        <v>5.103206378380694</v>
+      </c>
+    </row>
+    <row r="223" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C223" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I222" s="1"/>
-    </row>
-    <row r="223" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="224" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C224" s="132" t="s">
-        <v>73</v>
-      </c>
-      <c r="D224" s="130"/>
-      <c r="E224" s="130"/>
-      <c r="F224" s="130"/>
-      <c r="G224" s="130"/>
-      <c r="H224" s="130"/>
-      <c r="I224" s="130"/>
-      <c r="J224" s="130"/>
-      <c r="K224" s="130"/>
-      <c r="L224" s="131"/>
-    </row>
-    <row r="225" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B225" s="58" t="s">
+      <c r="I223" s="1"/>
+    </row>
+    <row r="224" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="225" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C225" s="121" t="s">
+        <v>71</v>
+      </c>
+      <c r="D225" s="122"/>
+      <c r="E225" s="122"/>
+      <c r="F225" s="122"/>
+      <c r="G225" s="122"/>
+      <c r="H225" s="122"/>
+      <c r="I225" s="122"/>
+      <c r="J225" s="122"/>
+      <c r="K225" s="122"/>
+      <c r="L225" s="123"/>
+    </row>
+    <row r="226" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B226" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C225" s="127" t="s">
+      <c r="C226" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="D225" s="128"/>
-      <c r="E225" s="127" t="s">
+      <c r="D226" s="128"/>
+      <c r="E226" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="F225" s="129"/>
-      <c r="G225" s="127" t="s">
+      <c r="F226" s="129"/>
+      <c r="G226" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="H225" s="128"/>
-      <c r="I225" s="129" t="s">
+      <c r="H226" s="128"/>
+      <c r="I226" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="J225" s="128"/>
-      <c r="K225" s="129" t="s">
+      <c r="J226" s="128"/>
+      <c r="K226" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L225" s="128"/>
-    </row>
-    <row r="226" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B226" s="59">
+      <c r="L226" s="128"/>
+    </row>
+    <row r="227" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B227" s="59">
         <v>1</v>
       </c>
-      <c r="C226" s="63" t="s">
+      <c r="C227" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="D226" s="75">
-        <v>59.98</v>
-      </c>
-      <c r="E226" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="F226" s="76">
-        <v>46.12</v>
-      </c>
-      <c r="G226" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="H226" s="75">
-        <v>36.07</v>
-      </c>
-      <c r="I226" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="J226" s="75">
-        <v>29.41</v>
-      </c>
-      <c r="K226" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="L226" s="78">
-        <v>31.040763024700802</v>
-      </c>
-    </row>
-    <row r="227" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B227" s="62">
-        <v>2</v>
-      </c>
-      <c r="C227" s="63" t="s">
-        <v>41</v>
-      </c>
       <c r="D227" s="75">
-        <v>20.41</v>
+        <v>60.73</v>
       </c>
       <c r="E227" s="63" t="s">
         <v>44</v>
       </c>
       <c r="F227" s="76">
-        <v>25.94</v>
+        <v>71.02</v>
       </c>
       <c r="G227" s="63" t="s">
         <v>44</v>
       </c>
       <c r="H227" s="75">
-        <v>23.13</v>
+        <v>64.930000000000007</v>
       </c>
       <c r="I227" s="77" t="s">
         <v>54</v>
       </c>
       <c r="J227" s="75">
-        <v>28.43</v>
+        <v>56.49</v>
       </c>
       <c r="K227" s="77" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L227" s="78">
-        <v>29.892189243529099</v>
+        <v>57.975112877136368</v>
       </c>
     </row>
     <row r="228" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B228" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C228" s="63" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D228" s="75">
-        <v>8.23</v>
+        <v>16.61</v>
       </c>
       <c r="E228" s="63" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F228" s="76">
-        <v>4.92</v>
+        <v>15.04</v>
       </c>
       <c r="G228" s="63" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H228" s="75">
-        <v>12.01</v>
+        <v>17.66</v>
       </c>
       <c r="I228" s="77" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J228" s="75">
-        <v>9.31</v>
+        <v>28.3</v>
       </c>
       <c r="K228" s="77" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="L228" s="78">
-        <v>6.81745727761386</v>
+        <v>23.909086455400878</v>
       </c>
     </row>
     <row r="229" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B229" s="62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C229" s="63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D229" s="75">
-        <v>5.94</v>
+        <v>13.71</v>
       </c>
       <c r="E229" s="63" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F229" s="76">
-        <v>4.46</v>
+        <v>10.09</v>
       </c>
       <c r="G229" s="63" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H229" s="75">
-        <v>6.61</v>
+        <v>6.77</v>
       </c>
       <c r="I229" s="77" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="J229" s="75">
-        <v>9.2100000000000009</v>
+        <v>4.96</v>
       </c>
       <c r="K229" s="77" t="s">
         <v>41</v>
       </c>
       <c r="L229" s="78">
+        <v>9.2748392805072868</v>
+      </c>
+    </row>
+    <row r="230" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B230" s="62">
+        <v>4</v>
+      </c>
+      <c r="C230" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="D230" s="75">
+        <v>3.62</v>
+      </c>
+      <c r="E230" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="F230" s="76">
+        <v>2.74</v>
+      </c>
+      <c r="G230" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H230" s="75">
+        <v>5.51</v>
+      </c>
+      <c r="I230" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="J230" s="75">
+        <v>4.33</v>
+      </c>
+      <c r="K230" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="L230" s="78">
+        <v>3.6608380925300299</v>
+      </c>
+    </row>
+    <row r="231" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B231" s="67">
+        <v>5</v>
+      </c>
+      <c r="C231" s="70" t="s">
+        <v>69</v>
+      </c>
+      <c r="D231" s="79">
+        <v>1.61</v>
+      </c>
+      <c r="E231" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="F231" s="80">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G231" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="H231" s="79">
+        <v>3.19</v>
+      </c>
+      <c r="I231" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="J231" s="79">
+        <v>1.24</v>
+      </c>
+      <c r="K231" s="81" t="s">
+        <v>49</v>
+      </c>
+      <c r="L231" s="82">
+        <v>2.6064493809976668</v>
+      </c>
+    </row>
+    <row r="232" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C232" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="I232" s="1"/>
+    </row>
+    <row r="233" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="234" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C234" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="D234" s="130"/>
+      <c r="E234" s="130"/>
+      <c r="F234" s="130"/>
+      <c r="G234" s="130"/>
+      <c r="H234" s="130"/>
+      <c r="I234" s="130"/>
+      <c r="J234" s="130"/>
+      <c r="K234" s="130"/>
+      <c r="L234" s="131"/>
+    </row>
+    <row r="235" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B235" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C235" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D235" s="128"/>
+      <c r="E235" s="127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F235" s="129"/>
+      <c r="G235" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="H235" s="128"/>
+      <c r="I235" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="J235" s="128"/>
+      <c r="K235" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L235" s="128"/>
+    </row>
+    <row r="236" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B236" s="59">
+        <v>1</v>
+      </c>
+      <c r="C236" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="D236" s="75">
+        <v>59.98</v>
+      </c>
+      <c r="E236" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F236" s="76">
+        <v>46.12</v>
+      </c>
+      <c r="G236" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H236" s="75">
+        <v>36.07</v>
+      </c>
+      <c r="I236" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="J236" s="75">
+        <v>29.41</v>
+      </c>
+      <c r="K236" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="L236" s="78">
+        <v>31.040763024700802</v>
+      </c>
+    </row>
+    <row r="237" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B237" s="62">
+        <v>2</v>
+      </c>
+      <c r="C237" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D237" s="75">
+        <v>20.41</v>
+      </c>
+      <c r="E237" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="F237" s="76">
+        <v>25.94</v>
+      </c>
+      <c r="G237" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H237" s="75">
+        <v>23.13</v>
+      </c>
+      <c r="I237" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="J237" s="75">
+        <v>28.43</v>
+      </c>
+      <c r="K237" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="L237" s="78">
+        <v>29.892189243529099</v>
+      </c>
+    </row>
+    <row r="238" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B238" s="62">
+        <v>3</v>
+      </c>
+      <c r="C238" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="D238" s="75">
+        <v>8.23</v>
+      </c>
+      <c r="E238" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="F238" s="76">
+        <v>4.92</v>
+      </c>
+      <c r="G238" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H238" s="75">
+        <v>12.01</v>
+      </c>
+      <c r="I238" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="J238" s="75">
+        <v>9.31</v>
+      </c>
+      <c r="K238" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="L238" s="78">
+        <v>6.81745727761386</v>
+      </c>
+    </row>
+    <row r="239" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B239" s="62">
+        <v>4</v>
+      </c>
+      <c r="C239" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="D239" s="75">
+        <v>5.94</v>
+      </c>
+      <c r="E239" s="63" t="s">
+        <v>56</v>
+      </c>
+      <c r="F239" s="76">
+        <v>4.46</v>
+      </c>
+      <c r="G239" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="H239" s="75">
+        <v>6.61</v>
+      </c>
+      <c r="I239" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="J239" s="75">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="K239" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="L239" s="78">
         <v>5.6742187307122496</v>
       </c>
     </row>
-    <row r="230" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B230" s="67">
+    <row r="240" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B240" s="67">
         <v>5</v>
       </c>
-      <c r="C230" s="70" t="s">
+      <c r="C240" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="D230" s="79">
+      <c r="D240" s="79">
         <v>2.2400000000000002</v>
       </c>
-      <c r="E230" s="70" t="s">
+      <c r="E240" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="F230" s="80">
+      <c r="F240" s="80">
         <v>3.23</v>
       </c>
-      <c r="G230" s="70" t="s">
+      <c r="G240" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="H230" s="79">
+      <c r="H240" s="79">
         <v>6.35</v>
       </c>
-      <c r="I230" s="81" t="s">
+      <c r="I240" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="J230" s="79">
+      <c r="J240" s="79">
         <v>6.81</v>
       </c>
-      <c r="K230" s="81" t="s">
+      <c r="K240" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="L230" s="82">
+      <c r="L240" s="82">
         <v>5.47056925643325</v>
       </c>
     </row>
-    <row r="231" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C231" s="55" t="s">
+    <row r="241" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C241" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I231" s="1"/>
+      <c r="I241" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="125">
-    <mergeCell ref="I198:J198"/>
-    <mergeCell ref="K198:L198"/>
-    <mergeCell ref="C206:L206"/>
-    <mergeCell ref="C224:L224"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="E207:F207"/>
-    <mergeCell ref="G207:H207"/>
-    <mergeCell ref="I207:J207"/>
-    <mergeCell ref="C225:D225"/>
-    <mergeCell ref="E225:F225"/>
-    <mergeCell ref="G225:H225"/>
-    <mergeCell ref="I225:J225"/>
-    <mergeCell ref="K225:L225"/>
-    <mergeCell ref="C216:D216"/>
-    <mergeCell ref="E216:F216"/>
-    <mergeCell ref="G216:H216"/>
-    <mergeCell ref="I216:J216"/>
-    <mergeCell ref="K216:L216"/>
-    <mergeCell ref="C170:L170"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="E171:F171"/>
-    <mergeCell ref="G171:H171"/>
-    <mergeCell ref="I171:J171"/>
-    <mergeCell ref="K171:L171"/>
-    <mergeCell ref="K207:L207"/>
-    <mergeCell ref="C215:L215"/>
-    <mergeCell ref="C179:L179"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="E180:F180"/>
-    <mergeCell ref="G180:H180"/>
-    <mergeCell ref="I180:J180"/>
-    <mergeCell ref="K180:L180"/>
-    <mergeCell ref="C188:L188"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="E189:F189"/>
-    <mergeCell ref="G189:H189"/>
-    <mergeCell ref="I189:J189"/>
-    <mergeCell ref="K189:L189"/>
-    <mergeCell ref="C197:L197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="E198:F198"/>
-    <mergeCell ref="G198:H198"/>
-    <mergeCell ref="C152:L152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="E153:F153"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="I153:J153"/>
-    <mergeCell ref="K153:L153"/>
-    <mergeCell ref="C161:L161"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="E162:F162"/>
-    <mergeCell ref="G162:H162"/>
-    <mergeCell ref="I162:J162"/>
-    <mergeCell ref="K162:L162"/>
-    <mergeCell ref="C134:L134"/>
+  <mergeCells count="131">
+    <mergeCell ref="I208:J208"/>
+    <mergeCell ref="K208:L208"/>
+    <mergeCell ref="C216:L216"/>
+    <mergeCell ref="C234:L234"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="I217:J217"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="I235:J235"/>
+    <mergeCell ref="K235:L235"/>
+    <mergeCell ref="C226:D226"/>
+    <mergeCell ref="E226:F226"/>
+    <mergeCell ref="G226:H226"/>
+    <mergeCell ref="I226:J226"/>
+    <mergeCell ref="K226:L226"/>
+    <mergeCell ref="C180:L180"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="E181:F181"/>
+    <mergeCell ref="G181:H181"/>
+    <mergeCell ref="I181:J181"/>
+    <mergeCell ref="K181:L181"/>
+    <mergeCell ref="K217:L217"/>
+    <mergeCell ref="C225:L225"/>
+    <mergeCell ref="C189:L189"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="E190:F190"/>
+    <mergeCell ref="G190:H190"/>
+    <mergeCell ref="I190:J190"/>
+    <mergeCell ref="K190:L190"/>
+    <mergeCell ref="C198:L198"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="E199:F199"/>
+    <mergeCell ref="G199:H199"/>
+    <mergeCell ref="I199:J199"/>
+    <mergeCell ref="K199:L199"/>
+    <mergeCell ref="C207:L207"/>
+    <mergeCell ref="C208:D208"/>
+    <mergeCell ref="E208:F208"/>
+    <mergeCell ref="G208:H208"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="C171:L171"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="I172:J172"/>
+    <mergeCell ref="K172:L172"/>
+    <mergeCell ref="C144:L144"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="C153:L153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="K154:L154"/>
     <mergeCell ref="C135:D135"/>
     <mergeCell ref="E135:F135"/>
     <mergeCell ref="G135:H135"/>
     <mergeCell ref="I135:J135"/>
     <mergeCell ref="K135:L135"/>
-    <mergeCell ref="C143:L143"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="G144:H144"/>
-    <mergeCell ref="I144:J144"/>
-    <mergeCell ref="K144:L144"/>
-    <mergeCell ref="C97:L97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="E125:F125"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="C124:L124"/>
-    <mergeCell ref="C115:L115"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="C106:L106"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="I107:J107"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="C88:L88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="C134:L134"/>
+    <mergeCell ref="C125:L125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="C116:L116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="K117:L117"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C107:L107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="C72:L72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="C80:L80"/>
-    <mergeCell ref="C64:L64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11875,7 +12062,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B9:I244"/>
+  <dimension ref="B9:I245"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -15117,7 +15304,7 @@
       </c>
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B241" s="32">
+      <c r="B241" s="92">
         <v>46023</v>
       </c>
       <c r="C241" s="88">
@@ -15131,7 +15318,7 @@
       </c>
     </row>
     <row r="242" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B242" s="33">
+      <c r="B242" s="93">
         <v>46054</v>
       </c>
       <c r="C242" s="87">
@@ -15145,13 +15332,35 @@
       </c>
     </row>
     <row r="243" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B243" s="135"/>
-      <c r="C243" s="83"/>
-      <c r="D243" s="83"/>
-      <c r="E243" s="83"/>
+      <c r="B243" s="93">
+        <v>46082</v>
+      </c>
+      <c r="C243" s="87">
+        <v>57450456</v>
+      </c>
+      <c r="D243" s="83">
+        <v>16137</v>
+      </c>
+      <c r="E243" s="22">
+        <v>3560.1695482431678</v>
+      </c>
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B244" s="55" t="s">
+      <c r="B244" s="107">
+        <v>46113</v>
+      </c>
+      <c r="C244" s="105">
+        <v>46922560</v>
+      </c>
+      <c r="D244" s="21">
+        <v>13081</v>
+      </c>
+      <c r="E244" s="20">
+        <v>3587.077440562648</v>
+      </c>
+    </row>
+    <row r="245" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B245" s="55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -15169,19 +15378,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -15422,7 +15622,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
@@ -15433,15 +15633,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
@@ -15449,7 +15650,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC8F936-4AF3-4FF9-8B1E-0736929643E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15468,7 +15669,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -15477,4 +15678,12 @@
     <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data_raw/exportacion_leche_polvo_entera.xlsx
+++ b/data_raw/exportacion_leche_polvo_entera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/2- Mercado externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="661" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D12FD62A-1B3C-46EA-933C-39F26657C5A4}"/>
+  <xr:revisionPtr revIDLastSave="672" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC4F1BFF-158C-4215-B8E0-7E504AE08118}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="703" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1785,6 +1785,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1803,21 +1804,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="153">
     <cellStyle name="20% - Énfasis1" xfId="11" builtinId="30" customBuiltin="1"/>
@@ -2560,12 +2560,12 @@
     </row>
     <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G11" s="121" t="s">
+      <c r="G11" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="123"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="124"/>
       <c r="K11" s="31" t="s">
         <v>2</v>
       </c>
@@ -2573,12 +2573,12 @@
     <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13"/>
-      <c r="G13" s="124" t="s">
+      <c r="G13" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="H13" s="125"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="127"/>
     </row>
     <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3459,7 +3459,7 @@
         <f t="shared" si="2"/>
         <v>2.5649255177751185E-2</v>
       </c>
-      <c r="Q32" s="135"/>
+      <c r="Q32" s="121"/>
       <c r="R32" s="104"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
@@ -3510,7 +3510,7 @@
         <f t="shared" si="2"/>
         <v>-8.6761415610088211E-3</v>
       </c>
-      <c r="Q33" s="135"/>
+      <c r="Q33" s="121"/>
       <c r="R33" s="104"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
@@ -3559,7 +3559,7 @@
       <c r="P34" s="3">
         <v>0.18613443776225669</v>
       </c>
-      <c r="Q34" s="135"/>
+      <c r="Q34" s="121"/>
       <c r="R34" s="104"/>
     </row>
     <row r="35" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3578,7 +3578,9 @@
       <c r="F35" s="100">
         <v>46922560</v>
       </c>
-      <c r="G35" s="100"/>
+      <c r="G35" s="100">
+        <v>62622331</v>
+      </c>
       <c r="H35" s="99"/>
       <c r="I35" s="100"/>
       <c r="J35" s="100"/>
@@ -3588,7 +3590,7 @@
       <c r="N35" s="99"/>
       <c r="O35" s="16"/>
       <c r="P35" s="17"/>
-      <c r="Q35" s="135"/>
+      <c r="Q35" s="121"/>
       <c r="R35" s="104"/>
     </row>
     <row r="36" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3612,18 +3614,18 @@
     </row>
     <row r="37" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37"/>
-      <c r="G37" s="124" t="s">
+      <c r="G37" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="125"/>
-      <c r="I37" s="125"/>
-      <c r="J37" s="126"/>
+      <c r="H37" s="126"/>
+      <c r="I37" s="126"/>
+      <c r="J37" s="127"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
-      <c r="Q37" s="135"/>
+      <c r="Q37" s="121"/>
     </row>
     <row r="38" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
@@ -3638,7 +3640,7 @@
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
-      <c r="Q38" s="135"/>
+      <c r="Q38" s="121"/>
     </row>
     <row r="39" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="36" t="s">
@@ -4618,7 +4620,7 @@
       <c r="P58" s="3">
         <v>5.9639816496076969E-2</v>
       </c>
-      <c r="Q58" s="135"/>
+      <c r="Q58" s="121"/>
       <c r="R58" s="104"/>
     </row>
     <row r="59" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4637,7 +4639,9 @@
       <c r="F59" s="95">
         <v>13081</v>
       </c>
-      <c r="G59" s="91"/>
+      <c r="G59" s="91">
+        <v>16871</v>
+      </c>
       <c r="H59" s="91"/>
       <c r="I59" s="91"/>
       <c r="J59" s="91"/>
@@ -4647,7 +4651,7 @@
       <c r="N59" s="95"/>
       <c r="O59" s="16"/>
       <c r="P59" s="17"/>
-      <c r="Q59" s="135"/>
+      <c r="Q59" s="121"/>
       <c r="R59" s="104"/>
     </row>
     <row r="60" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4671,12 +4675,12 @@
     </row>
     <row r="61" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E61" s="14"/>
-      <c r="G61" s="124" t="s">
+      <c r="G61" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="H61" s="125"/>
-      <c r="I61" s="125"/>
-      <c r="J61" s="126"/>
+      <c r="H61" s="126"/>
+      <c r="I61" s="126"/>
+      <c r="J61" s="127"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
@@ -5693,7 +5697,7 @@
         <f t="shared" si="8"/>
         <v>3978.4184285259557</v>
       </c>
-      <c r="Q82" s="135"/>
+      <c r="Q82" s="121"/>
       <c r="R82" s="104"/>
       <c r="XFD82" s="1"/>
     </row>
@@ -5714,7 +5718,9 @@
       <c r="F83" s="18">
         <v>3587.077440562648</v>
       </c>
-      <c r="G83" s="18"/>
+      <c r="G83" s="18">
+        <v>3711.8327899946653</v>
+      </c>
       <c r="H83" s="18"/>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
@@ -5724,7 +5730,7 @@
       <c r="N83" s="18"/>
       <c r="O83" s="16"/>
       <c r="P83" s="16"/>
-      <c r="Q83" s="135"/>
+      <c r="Q83" s="121"/>
       <c r="R83" s="104"/>
     </row>
     <row r="84" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
@@ -5876,34 +5882,34 @@
     </row>
     <row r="10" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F11" s="121" t="s">
+      <c r="F11" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="130"/>
-      <c r="H11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="132"/>
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:13" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="127" t="s">
+      <c r="C13" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="128"/>
-      <c r="E13" s="127" t="s">
+      <c r="D13" s="129"/>
+      <c r="E13" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="128"/>
-      <c r="G13" s="127" t="s">
+      <c r="F13" s="129"/>
+      <c r="G13" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="128"/>
-      <c r="I13" s="127" t="s">
+      <c r="H13" s="129"/>
+      <c r="I13" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="128"/>
-      <c r="K13" s="127" t="s">
+      <c r="J13" s="129"/>
+      <c r="K13" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="L13" s="128"/>
+      <c r="L13" s="129"/>
     </row>
     <row r="14" spans="2:13" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="44" t="s">
@@ -6702,26 +6708,26 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="127" t="s">
+      <c r="C37" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="128"/>
-      <c r="E37" s="127" t="s">
+      <c r="D37" s="129"/>
+      <c r="E37" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F37" s="128"/>
-      <c r="G37" s="127" t="s">
+      <c r="F37" s="129"/>
+      <c r="G37" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H37" s="128"/>
-      <c r="I37" s="127" t="s">
+      <c r="H37" s="129"/>
+      <c r="I37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="J37" s="128"/>
-      <c r="K37" s="127" t="s">
+      <c r="J37" s="129"/>
+      <c r="K37" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="L37" s="128"/>
+      <c r="L37" s="129"/>
     </row>
     <row r="38" spans="2:12" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="44" t="s">
@@ -7540,43 +7546,43 @@
       <c r="B65" s="57"/>
     </row>
     <row r="66" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="121">
+      <c r="C66" s="122">
         <v>2026</v>
       </c>
-      <c r="D66" s="122"/>
-      <c r="E66" s="122"/>
-      <c r="F66" s="122"/>
-      <c r="G66" s="122"/>
-      <c r="H66" s="122"/>
-      <c r="I66" s="122"/>
-      <c r="J66" s="122"/>
-      <c r="K66" s="122"/>
-      <c r="L66" s="123"/>
+      <c r="D66" s="123"/>
+      <c r="E66" s="123"/>
+      <c r="F66" s="123"/>
+      <c r="G66" s="123"/>
+      <c r="H66" s="123"/>
+      <c r="I66" s="123"/>
+      <c r="J66" s="123"/>
+      <c r="K66" s="123"/>
+      <c r="L66" s="124"/>
     </row>
     <row r="67" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C67" s="127" t="s">
+      <c r="C67" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D67" s="128"/>
-      <c r="E67" s="127" t="s">
+      <c r="D67" s="129"/>
+      <c r="E67" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F67" s="129"/>
-      <c r="G67" s="127" t="s">
+      <c r="F67" s="128"/>
+      <c r="G67" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H67" s="128"/>
-      <c r="I67" s="129" t="s">
+      <c r="H67" s="129"/>
+      <c r="I67" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J67" s="128"/>
-      <c r="K67" s="129" t="s">
+      <c r="J67" s="129"/>
+      <c r="K67" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L67" s="128"/>
+      <c r="L67" s="129"/>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B68" s="59">
@@ -7677,43 +7683,43 @@
       <c r="B73" s="57"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="121">
+      <c r="C74" s="122">
         <v>2025</v>
       </c>
-      <c r="D74" s="122"/>
-      <c r="E74" s="122"/>
-      <c r="F74" s="122"/>
-      <c r="G74" s="122"/>
-      <c r="H74" s="122"/>
-      <c r="I74" s="122"/>
-      <c r="J74" s="122"/>
-      <c r="K74" s="122"/>
-      <c r="L74" s="123"/>
+      <c r="D74" s="123"/>
+      <c r="E74" s="123"/>
+      <c r="F74" s="123"/>
+      <c r="G74" s="123"/>
+      <c r="H74" s="123"/>
+      <c r="I74" s="123"/>
+      <c r="J74" s="123"/>
+      <c r="K74" s="123"/>
+      <c r="L74" s="124"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C75" s="127" t="s">
+      <c r="C75" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D75" s="128"/>
-      <c r="E75" s="127" t="s">
+      <c r="D75" s="129"/>
+      <c r="E75" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F75" s="129"/>
-      <c r="G75" s="127" t="s">
+      <c r="F75" s="128"/>
+      <c r="G75" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H75" s="128"/>
-      <c r="I75" s="129" t="s">
+      <c r="H75" s="129"/>
+      <c r="I75" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J75" s="128"/>
-      <c r="K75" s="129" t="s">
+      <c r="J75" s="129"/>
+      <c r="K75" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L75" s="128"/>
+      <c r="L75" s="129"/>
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B76" s="59">
@@ -7894,43 +7900,43 @@
       <c r="B81" s="57"/>
     </row>
     <row r="82" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C82" s="121">
+      <c r="C82" s="122">
         <v>2024</v>
       </c>
-      <c r="D82" s="122"/>
-      <c r="E82" s="122"/>
-      <c r="F82" s="122"/>
-      <c r="G82" s="122"/>
-      <c r="H82" s="122"/>
-      <c r="I82" s="122"/>
-      <c r="J82" s="122"/>
-      <c r="K82" s="122"/>
-      <c r="L82" s="123"/>
+      <c r="D82" s="123"/>
+      <c r="E82" s="123"/>
+      <c r="F82" s="123"/>
+      <c r="G82" s="123"/>
+      <c r="H82" s="123"/>
+      <c r="I82" s="123"/>
+      <c r="J82" s="123"/>
+      <c r="K82" s="123"/>
+      <c r="L82" s="124"/>
     </row>
     <row r="83" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C83" s="127" t="s">
+      <c r="C83" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D83" s="128"/>
-      <c r="E83" s="127" t="s">
+      <c r="D83" s="129"/>
+      <c r="E83" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F83" s="129"/>
-      <c r="G83" s="127" t="s">
+      <c r="F83" s="128"/>
+      <c r="G83" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H83" s="128"/>
-      <c r="I83" s="129" t="s">
+      <c r="H83" s="129"/>
+      <c r="I83" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J83" s="128"/>
-      <c r="K83" s="129" t="s">
+      <c r="J83" s="129"/>
+      <c r="K83" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L83" s="128"/>
+      <c r="L83" s="129"/>
     </row>
     <row r="84" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B84" s="59">
@@ -8111,43 +8117,43 @@
       <c r="B89" s="57"/>
     </row>
     <row r="90" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C90" s="121">
+      <c r="C90" s="122">
         <v>2023</v>
       </c>
-      <c r="D90" s="122"/>
-      <c r="E90" s="122"/>
-      <c r="F90" s="122"/>
-      <c r="G90" s="122"/>
-      <c r="H90" s="122"/>
-      <c r="I90" s="122"/>
-      <c r="J90" s="122"/>
-      <c r="K90" s="122"/>
-      <c r="L90" s="123"/>
+      <c r="D90" s="123"/>
+      <c r="E90" s="123"/>
+      <c r="F90" s="123"/>
+      <c r="G90" s="123"/>
+      <c r="H90" s="123"/>
+      <c r="I90" s="123"/>
+      <c r="J90" s="123"/>
+      <c r="K90" s="123"/>
+      <c r="L90" s="124"/>
     </row>
     <row r="91" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C91" s="127" t="s">
+      <c r="C91" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D91" s="128"/>
-      <c r="E91" s="127" t="s">
+      <c r="D91" s="129"/>
+      <c r="E91" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F91" s="129"/>
-      <c r="G91" s="127" t="s">
+      <c r="F91" s="128"/>
+      <c r="G91" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H91" s="128"/>
-      <c r="I91" s="129" t="s">
+      <c r="H91" s="129"/>
+      <c r="I91" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J91" s="128"/>
-      <c r="K91" s="129" t="s">
+      <c r="J91" s="129"/>
+      <c r="K91" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L91" s="128"/>
+      <c r="L91" s="129"/>
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B92" s="59">
@@ -8328,43 +8334,43 @@
       <c r="B97" s="57"/>
     </row>
     <row r="98" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="121">
+      <c r="C98" s="122">
         <v>2022</v>
       </c>
-      <c r="D98" s="122"/>
-      <c r="E98" s="122"/>
-      <c r="F98" s="122"/>
-      <c r="G98" s="122"/>
-      <c r="H98" s="122"/>
-      <c r="I98" s="122"/>
-      <c r="J98" s="122"/>
-      <c r="K98" s="122"/>
-      <c r="L98" s="123"/>
+      <c r="D98" s="123"/>
+      <c r="E98" s="123"/>
+      <c r="F98" s="123"/>
+      <c r="G98" s="123"/>
+      <c r="H98" s="123"/>
+      <c r="I98" s="123"/>
+      <c r="J98" s="123"/>
+      <c r="K98" s="123"/>
+      <c r="L98" s="124"/>
     </row>
     <row r="99" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C99" s="127" t="s">
+      <c r="C99" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D99" s="128"/>
-      <c r="E99" s="127" t="s">
+      <c r="D99" s="129"/>
+      <c r="E99" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F99" s="129"/>
-      <c r="G99" s="127" t="s">
+      <c r="F99" s="128"/>
+      <c r="G99" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H99" s="128"/>
-      <c r="I99" s="129" t="s">
+      <c r="H99" s="129"/>
+      <c r="I99" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J99" s="128"/>
-      <c r="K99" s="129" t="s">
+      <c r="J99" s="129"/>
+      <c r="K99" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L99" s="128"/>
+      <c r="L99" s="129"/>
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B100" s="59">
@@ -8556,43 +8562,43 @@
     </row>
     <row r="106" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C107" s="121">
+      <c r="C107" s="122">
         <v>2021</v>
       </c>
-      <c r="D107" s="122"/>
-      <c r="E107" s="122"/>
-      <c r="F107" s="122"/>
-      <c r="G107" s="122"/>
-      <c r="H107" s="122"/>
-      <c r="I107" s="122"/>
-      <c r="J107" s="122"/>
-      <c r="K107" s="122"/>
-      <c r="L107" s="123"/>
+      <c r="D107" s="123"/>
+      <c r="E107" s="123"/>
+      <c r="F107" s="123"/>
+      <c r="G107" s="123"/>
+      <c r="H107" s="123"/>
+      <c r="I107" s="123"/>
+      <c r="J107" s="123"/>
+      <c r="K107" s="123"/>
+      <c r="L107" s="124"/>
     </row>
     <row r="108" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C108" s="127" t="s">
+      <c r="C108" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D108" s="128"/>
-      <c r="E108" s="127" t="s">
+      <c r="D108" s="129"/>
+      <c r="E108" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F108" s="129"/>
-      <c r="G108" s="127" t="s">
+      <c r="F108" s="128"/>
+      <c r="G108" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H108" s="128"/>
-      <c r="I108" s="129" t="s">
+      <c r="H108" s="129"/>
+      <c r="I108" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J108" s="128"/>
-      <c r="K108" s="129" t="s">
+      <c r="J108" s="129"/>
+      <c r="K108" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L108" s="128"/>
+      <c r="L108" s="129"/>
     </row>
     <row r="109" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B109" s="59">
@@ -8786,43 +8792,43 @@
     </row>
     <row r="115" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="121">
+      <c r="C116" s="122">
         <v>2020</v>
       </c>
-      <c r="D116" s="122"/>
-      <c r="E116" s="122"/>
-      <c r="F116" s="122"/>
-      <c r="G116" s="122"/>
-      <c r="H116" s="122"/>
-      <c r="I116" s="122"/>
-      <c r="J116" s="122"/>
-      <c r="K116" s="122"/>
-      <c r="L116" s="123"/>
+      <c r="D116" s="123"/>
+      <c r="E116" s="123"/>
+      <c r="F116" s="123"/>
+      <c r="G116" s="123"/>
+      <c r="H116" s="123"/>
+      <c r="I116" s="123"/>
+      <c r="J116" s="123"/>
+      <c r="K116" s="123"/>
+      <c r="L116" s="124"/>
     </row>
     <row r="117" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B117" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C117" s="127" t="s">
+      <c r="C117" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D117" s="128"/>
-      <c r="E117" s="127" t="s">
+      <c r="D117" s="129"/>
+      <c r="E117" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F117" s="129"/>
-      <c r="G117" s="127" t="s">
+      <c r="F117" s="128"/>
+      <c r="G117" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H117" s="128"/>
-      <c r="I117" s="129" t="s">
+      <c r="H117" s="129"/>
+      <c r="I117" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J117" s="128"/>
-      <c r="K117" s="129" t="s">
+      <c r="J117" s="129"/>
+      <c r="K117" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L117" s="128"/>
+      <c r="L117" s="129"/>
     </row>
     <row r="118" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B118" s="59">
@@ -9016,43 +9022,43 @@
     </row>
     <row r="124" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="125" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C125" s="121">
+      <c r="C125" s="122">
         <v>2019</v>
       </c>
-      <c r="D125" s="122"/>
-      <c r="E125" s="122"/>
-      <c r="F125" s="122"/>
-      <c r="G125" s="122"/>
-      <c r="H125" s="122"/>
-      <c r="I125" s="122"/>
-      <c r="J125" s="122"/>
-      <c r="K125" s="122"/>
-      <c r="L125" s="123"/>
+      <c r="D125" s="123"/>
+      <c r="E125" s="123"/>
+      <c r="F125" s="123"/>
+      <c r="G125" s="123"/>
+      <c r="H125" s="123"/>
+      <c r="I125" s="123"/>
+      <c r="J125" s="123"/>
+      <c r="K125" s="123"/>
+      <c r="L125" s="124"/>
     </row>
     <row r="126" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B126" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C126" s="127" t="s">
+      <c r="C126" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D126" s="128"/>
-      <c r="E126" s="127" t="s">
+      <c r="D126" s="129"/>
+      <c r="E126" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F126" s="129"/>
-      <c r="G126" s="127" t="s">
+      <c r="F126" s="128"/>
+      <c r="G126" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H126" s="128"/>
-      <c r="I126" s="129" t="s">
+      <c r="H126" s="129"/>
+      <c r="I126" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J126" s="128"/>
-      <c r="K126" s="129" t="s">
+      <c r="J126" s="129"/>
+      <c r="K126" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L126" s="128"/>
+      <c r="L126" s="129"/>
     </row>
     <row r="127" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B127" s="59">
@@ -9246,43 +9252,43 @@
     </row>
     <row r="133" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="134" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C134" s="121">
+      <c r="C134" s="122">
         <v>2018</v>
       </c>
-      <c r="D134" s="122"/>
-      <c r="E134" s="122"/>
-      <c r="F134" s="122"/>
-      <c r="G134" s="122"/>
-      <c r="H134" s="122"/>
-      <c r="I134" s="122"/>
-      <c r="J134" s="122"/>
-      <c r="K134" s="122"/>
-      <c r="L134" s="123"/>
+      <c r="D134" s="123"/>
+      <c r="E134" s="123"/>
+      <c r="F134" s="123"/>
+      <c r="G134" s="123"/>
+      <c r="H134" s="123"/>
+      <c r="I134" s="123"/>
+      <c r="J134" s="123"/>
+      <c r="K134" s="123"/>
+      <c r="L134" s="124"/>
     </row>
     <row r="135" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B135" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C135" s="127" t="s">
+      <c r="C135" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D135" s="128"/>
-      <c r="E135" s="127" t="s">
+      <c r="D135" s="129"/>
+      <c r="E135" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F135" s="129"/>
-      <c r="G135" s="127" t="s">
+      <c r="F135" s="128"/>
+      <c r="G135" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H135" s="128"/>
-      <c r="I135" s="129" t="s">
+      <c r="H135" s="129"/>
+      <c r="I135" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J135" s="128"/>
-      <c r="K135" s="129" t="s">
+      <c r="J135" s="129"/>
+      <c r="K135" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L135" s="128"/>
+      <c r="L135" s="129"/>
     </row>
     <row r="136" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B136" s="59">
@@ -9476,43 +9482,43 @@
     </row>
     <row r="143" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="144" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C144" s="121">
+      <c r="C144" s="122">
         <v>2017</v>
       </c>
-      <c r="D144" s="122"/>
-      <c r="E144" s="122"/>
-      <c r="F144" s="122"/>
-      <c r="G144" s="122"/>
-      <c r="H144" s="122"/>
-      <c r="I144" s="122"/>
-      <c r="J144" s="122"/>
-      <c r="K144" s="122"/>
-      <c r="L144" s="123"/>
+      <c r="D144" s="123"/>
+      <c r="E144" s="123"/>
+      <c r="F144" s="123"/>
+      <c r="G144" s="123"/>
+      <c r="H144" s="123"/>
+      <c r="I144" s="123"/>
+      <c r="J144" s="123"/>
+      <c r="K144" s="123"/>
+      <c r="L144" s="124"/>
     </row>
     <row r="145" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B145" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C145" s="127" t="s">
+      <c r="C145" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D145" s="128"/>
-      <c r="E145" s="127" t="s">
+      <c r="D145" s="129"/>
+      <c r="E145" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F145" s="129"/>
-      <c r="G145" s="127" t="s">
+      <c r="F145" s="128"/>
+      <c r="G145" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H145" s="128"/>
-      <c r="I145" s="129" t="s">
+      <c r="H145" s="129"/>
+      <c r="I145" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J145" s="128"/>
-      <c r="K145" s="129" t="s">
+      <c r="J145" s="129"/>
+      <c r="K145" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L145" s="128"/>
+      <c r="L145" s="129"/>
     </row>
     <row r="146" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146" s="59">
@@ -9706,43 +9712,43 @@
     </row>
     <row r="152" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="153" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="121">
+      <c r="C153" s="122">
         <v>2016</v>
       </c>
-      <c r="D153" s="122"/>
-      <c r="E153" s="122"/>
-      <c r="F153" s="122"/>
-      <c r="G153" s="122"/>
-      <c r="H153" s="122"/>
-      <c r="I153" s="122"/>
-      <c r="J153" s="122"/>
-      <c r="K153" s="122"/>
-      <c r="L153" s="123"/>
+      <c r="D153" s="123"/>
+      <c r="E153" s="123"/>
+      <c r="F153" s="123"/>
+      <c r="G153" s="123"/>
+      <c r="H153" s="123"/>
+      <c r="I153" s="123"/>
+      <c r="J153" s="123"/>
+      <c r="K153" s="123"/>
+      <c r="L153" s="124"/>
     </row>
     <row r="154" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B154" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C154" s="127" t="s">
+      <c r="C154" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D154" s="128"/>
-      <c r="E154" s="127" t="s">
+      <c r="D154" s="129"/>
+      <c r="E154" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F154" s="129"/>
-      <c r="G154" s="127" t="s">
+      <c r="F154" s="128"/>
+      <c r="G154" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H154" s="128"/>
-      <c r="I154" s="129" t="s">
+      <c r="H154" s="129"/>
+      <c r="I154" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J154" s="128"/>
-      <c r="K154" s="129" t="s">
+      <c r="J154" s="129"/>
+      <c r="K154" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L154" s="128"/>
+      <c r="L154" s="129"/>
     </row>
     <row r="155" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B155" s="59">
@@ -9936,43 +9942,43 @@
     </row>
     <row r="161" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="162" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C162" s="121">
+      <c r="C162" s="122">
         <v>2015</v>
       </c>
-      <c r="D162" s="122"/>
-      <c r="E162" s="122"/>
-      <c r="F162" s="122"/>
-      <c r="G162" s="122"/>
-      <c r="H162" s="122"/>
-      <c r="I162" s="122"/>
-      <c r="J162" s="122"/>
-      <c r="K162" s="122"/>
-      <c r="L162" s="123"/>
+      <c r="D162" s="123"/>
+      <c r="E162" s="123"/>
+      <c r="F162" s="123"/>
+      <c r="G162" s="123"/>
+      <c r="H162" s="123"/>
+      <c r="I162" s="123"/>
+      <c r="J162" s="123"/>
+      <c r="K162" s="123"/>
+      <c r="L162" s="124"/>
     </row>
     <row r="163" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B163" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C163" s="127" t="s">
+      <c r="C163" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D163" s="128"/>
-      <c r="E163" s="127" t="s">
+      <c r="D163" s="129"/>
+      <c r="E163" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F163" s="129"/>
-      <c r="G163" s="127" t="s">
+      <c r="F163" s="128"/>
+      <c r="G163" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H163" s="128"/>
-      <c r="I163" s="129" t="s">
+      <c r="H163" s="129"/>
+      <c r="I163" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J163" s="128"/>
-      <c r="K163" s="129" t="s">
+      <c r="J163" s="129"/>
+      <c r="K163" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L163" s="128"/>
+      <c r="L163" s="129"/>
     </row>
     <row r="164" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B164" s="59">
@@ -10156,43 +10162,43 @@
     </row>
     <row r="170" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="171" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C171" s="121">
+      <c r="C171" s="122">
         <v>2014</v>
       </c>
-      <c r="D171" s="122"/>
-      <c r="E171" s="122"/>
-      <c r="F171" s="122"/>
-      <c r="G171" s="122"/>
-      <c r="H171" s="122"/>
-      <c r="I171" s="122"/>
-      <c r="J171" s="122"/>
-      <c r="K171" s="122"/>
-      <c r="L171" s="123"/>
+      <c r="D171" s="123"/>
+      <c r="E171" s="123"/>
+      <c r="F171" s="123"/>
+      <c r="G171" s="123"/>
+      <c r="H171" s="123"/>
+      <c r="I171" s="123"/>
+      <c r="J171" s="123"/>
+      <c r="K171" s="123"/>
+      <c r="L171" s="124"/>
     </row>
     <row r="172" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B172" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C172" s="127" t="s">
+      <c r="C172" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D172" s="128"/>
-      <c r="E172" s="127" t="s">
+      <c r="D172" s="129"/>
+      <c r="E172" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F172" s="129"/>
-      <c r="G172" s="127" t="s">
+      <c r="F172" s="128"/>
+      <c r="G172" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H172" s="128"/>
-      <c r="I172" s="129" t="s">
+      <c r="H172" s="129"/>
+      <c r="I172" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J172" s="128"/>
-      <c r="K172" s="129" t="s">
+      <c r="J172" s="129"/>
+      <c r="K172" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L172" s="128"/>
+      <c r="L172" s="129"/>
     </row>
     <row r="173" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B173" s="59">
@@ -10376,43 +10382,43 @@
     </row>
     <row r="179" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="180" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C180" s="121" t="s">
+      <c r="C180" s="122" t="s">
         <v>62</v>
       </c>
-      <c r="D180" s="122"/>
-      <c r="E180" s="122"/>
-      <c r="F180" s="122"/>
-      <c r="G180" s="122"/>
-      <c r="H180" s="122"/>
-      <c r="I180" s="122"/>
-      <c r="J180" s="122"/>
-      <c r="K180" s="122"/>
-      <c r="L180" s="123"/>
+      <c r="D180" s="123"/>
+      <c r="E180" s="123"/>
+      <c r="F180" s="123"/>
+      <c r="G180" s="123"/>
+      <c r="H180" s="123"/>
+      <c r="I180" s="123"/>
+      <c r="J180" s="123"/>
+      <c r="K180" s="123"/>
+      <c r="L180" s="124"/>
     </row>
     <row r="181" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B181" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C181" s="127" t="s">
+      <c r="C181" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D181" s="128"/>
-      <c r="E181" s="127" t="s">
+      <c r="D181" s="129"/>
+      <c r="E181" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F181" s="129"/>
-      <c r="G181" s="127" t="s">
+      <c r="F181" s="128"/>
+      <c r="G181" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H181" s="128"/>
-      <c r="I181" s="129" t="s">
+      <c r="H181" s="129"/>
+      <c r="I181" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J181" s="128"/>
-      <c r="K181" s="129" t="s">
+      <c r="J181" s="129"/>
+      <c r="K181" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L181" s="128"/>
+      <c r="L181" s="129"/>
     </row>
     <row r="182" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B182" s="59">
@@ -10597,43 +10603,43 @@
     </row>
     <row r="188" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="189" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C189" s="121" t="s">
+      <c r="C189" s="122" t="s">
         <v>64</v>
       </c>
-      <c r="D189" s="122"/>
-      <c r="E189" s="122"/>
-      <c r="F189" s="122"/>
-      <c r="G189" s="122"/>
-      <c r="H189" s="122"/>
-      <c r="I189" s="122"/>
-      <c r="J189" s="122"/>
-      <c r="K189" s="122"/>
-      <c r="L189" s="123"/>
+      <c r="D189" s="123"/>
+      <c r="E189" s="123"/>
+      <c r="F189" s="123"/>
+      <c r="G189" s="123"/>
+      <c r="H189" s="123"/>
+      <c r="I189" s="123"/>
+      <c r="J189" s="123"/>
+      <c r="K189" s="123"/>
+      <c r="L189" s="124"/>
     </row>
     <row r="190" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B190" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C190" s="127" t="s">
+      <c r="C190" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D190" s="128"/>
-      <c r="E190" s="127" t="s">
+      <c r="D190" s="129"/>
+      <c r="E190" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F190" s="129"/>
-      <c r="G190" s="127" t="s">
+      <c r="F190" s="128"/>
+      <c r="G190" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H190" s="128"/>
-      <c r="I190" s="129" t="s">
+      <c r="H190" s="129"/>
+      <c r="I190" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J190" s="128"/>
-      <c r="K190" s="129" t="s">
+      <c r="J190" s="129"/>
+      <c r="K190" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L190" s="128"/>
+      <c r="L190" s="129"/>
     </row>
     <row r="191" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B191" s="59">
@@ -10818,43 +10824,43 @@
     </row>
     <row r="197" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="198" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C198" s="121" t="s">
+      <c r="C198" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="D198" s="122"/>
-      <c r="E198" s="122"/>
-      <c r="F198" s="122"/>
-      <c r="G198" s="122"/>
-      <c r="H198" s="122"/>
-      <c r="I198" s="122"/>
-      <c r="J198" s="122"/>
-      <c r="K198" s="122"/>
-      <c r="L198" s="123"/>
+      <c r="D198" s="123"/>
+      <c r="E198" s="123"/>
+      <c r="F198" s="123"/>
+      <c r="G198" s="123"/>
+      <c r="H198" s="123"/>
+      <c r="I198" s="123"/>
+      <c r="J198" s="123"/>
+      <c r="K198" s="123"/>
+      <c r="L198" s="124"/>
     </row>
     <row r="199" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B199" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C199" s="127" t="s">
+      <c r="C199" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D199" s="128"/>
-      <c r="E199" s="127" t="s">
+      <c r="D199" s="129"/>
+      <c r="E199" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F199" s="129"/>
-      <c r="G199" s="127" t="s">
+      <c r="F199" s="128"/>
+      <c r="G199" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H199" s="128"/>
-      <c r="I199" s="129" t="s">
+      <c r="H199" s="129"/>
+      <c r="I199" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J199" s="128"/>
-      <c r="K199" s="129" t="s">
+      <c r="J199" s="129"/>
+      <c r="K199" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L199" s="128"/>
+      <c r="L199" s="129"/>
     </row>
     <row r="200" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B200" s="59">
@@ -11039,43 +11045,43 @@
     </row>
     <row r="206" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="207" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C207" s="121" t="s">
+      <c r="C207" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="D207" s="122"/>
-      <c r="E207" s="122"/>
-      <c r="F207" s="122"/>
-      <c r="G207" s="122"/>
-      <c r="H207" s="122"/>
-      <c r="I207" s="122"/>
-      <c r="J207" s="122"/>
-      <c r="K207" s="122"/>
-      <c r="L207" s="123"/>
+      <c r="D207" s="123"/>
+      <c r="E207" s="123"/>
+      <c r="F207" s="123"/>
+      <c r="G207" s="123"/>
+      <c r="H207" s="123"/>
+      <c r="I207" s="123"/>
+      <c r="J207" s="123"/>
+      <c r="K207" s="123"/>
+      <c r="L207" s="124"/>
     </row>
     <row r="208" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B208" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C208" s="127" t="s">
+      <c r="C208" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D208" s="128"/>
-      <c r="E208" s="127" t="s">
+      <c r="D208" s="129"/>
+      <c r="E208" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F208" s="129"/>
-      <c r="G208" s="127" t="s">
+      <c r="F208" s="128"/>
+      <c r="G208" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H208" s="128"/>
-      <c r="I208" s="129" t="s">
+      <c r="H208" s="129"/>
+      <c r="I208" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J208" s="128"/>
-      <c r="K208" s="129" t="s">
+      <c r="J208" s="129"/>
+      <c r="K208" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L208" s="128"/>
+      <c r="L208" s="129"/>
     </row>
     <row r="209" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B209" s="59">
@@ -11260,43 +11266,43 @@
     </row>
     <row r="215" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="216" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C216" s="121" t="s">
+      <c r="C216" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="D216" s="122"/>
-      <c r="E216" s="122"/>
-      <c r="F216" s="122"/>
-      <c r="G216" s="122"/>
-      <c r="H216" s="122"/>
-      <c r="I216" s="122"/>
-      <c r="J216" s="122"/>
-      <c r="K216" s="122"/>
-      <c r="L216" s="123"/>
+      <c r="D216" s="123"/>
+      <c r="E216" s="123"/>
+      <c r="F216" s="123"/>
+      <c r="G216" s="123"/>
+      <c r="H216" s="123"/>
+      <c r="I216" s="123"/>
+      <c r="J216" s="123"/>
+      <c r="K216" s="123"/>
+      <c r="L216" s="124"/>
     </row>
     <row r="217" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B217" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C217" s="127" t="s">
+      <c r="C217" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D217" s="128"/>
-      <c r="E217" s="127" t="s">
+      <c r="D217" s="129"/>
+      <c r="E217" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F217" s="129"/>
-      <c r="G217" s="127" t="s">
+      <c r="F217" s="128"/>
+      <c r="G217" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H217" s="128"/>
-      <c r="I217" s="129" t="s">
+      <c r="H217" s="129"/>
+      <c r="I217" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J217" s="128"/>
-      <c r="K217" s="129" t="s">
+      <c r="J217" s="129"/>
+      <c r="K217" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L217" s="128"/>
+      <c r="L217" s="129"/>
     </row>
     <row r="218" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B218" s="59">
@@ -11481,43 +11487,43 @@
     </row>
     <row r="224" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="225" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C225" s="121" t="s">
+      <c r="C225" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="D225" s="122"/>
-      <c r="E225" s="122"/>
-      <c r="F225" s="122"/>
-      <c r="G225" s="122"/>
-      <c r="H225" s="122"/>
-      <c r="I225" s="122"/>
-      <c r="J225" s="122"/>
-      <c r="K225" s="122"/>
-      <c r="L225" s="123"/>
+      <c r="D225" s="123"/>
+      <c r="E225" s="123"/>
+      <c r="F225" s="123"/>
+      <c r="G225" s="123"/>
+      <c r="H225" s="123"/>
+      <c r="I225" s="123"/>
+      <c r="J225" s="123"/>
+      <c r="K225" s="123"/>
+      <c r="L225" s="124"/>
     </row>
     <row r="226" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B226" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C226" s="127" t="s">
+      <c r="C226" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D226" s="128"/>
-      <c r="E226" s="127" t="s">
+      <c r="D226" s="129"/>
+      <c r="E226" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F226" s="129"/>
-      <c r="G226" s="127" t="s">
+      <c r="F226" s="128"/>
+      <c r="G226" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H226" s="128"/>
-      <c r="I226" s="129" t="s">
+      <c r="H226" s="129"/>
+      <c r="I226" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J226" s="128"/>
-      <c r="K226" s="129" t="s">
+      <c r="J226" s="129"/>
+      <c r="K226" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L226" s="128"/>
+      <c r="L226" s="129"/>
     </row>
     <row r="227" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B227" s="59">
@@ -11702,43 +11708,43 @@
     </row>
     <row r="233" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="234" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C234" s="132" t="s">
+      <c r="C234" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="D234" s="130"/>
-      <c r="E234" s="130"/>
-      <c r="F234" s="130"/>
-      <c r="G234" s="130"/>
-      <c r="H234" s="130"/>
-      <c r="I234" s="130"/>
-      <c r="J234" s="130"/>
-      <c r="K234" s="130"/>
-      <c r="L234" s="131"/>
+      <c r="D234" s="131"/>
+      <c r="E234" s="131"/>
+      <c r="F234" s="131"/>
+      <c r="G234" s="131"/>
+      <c r="H234" s="131"/>
+      <c r="I234" s="131"/>
+      <c r="J234" s="131"/>
+      <c r="K234" s="131"/>
+      <c r="L234" s="132"/>
     </row>
     <row r="235" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B235" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C235" s="127" t="s">
+      <c r="C235" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D235" s="128"/>
-      <c r="E235" s="127" t="s">
+      <c r="D235" s="129"/>
+      <c r="E235" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F235" s="129"/>
-      <c r="G235" s="127" t="s">
+      <c r="F235" s="128"/>
+      <c r="G235" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="H235" s="128"/>
-      <c r="I235" s="129" t="s">
+      <c r="H235" s="129"/>
+      <c r="I235" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J235" s="128"/>
-      <c r="K235" s="129" t="s">
+      <c r="J235" s="129"/>
+      <c r="K235" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="L235" s="128"/>
+      <c r="L235" s="129"/>
     </row>
     <row r="236" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B236" s="59">
@@ -11923,24 +11929,95 @@
     </row>
   </sheetData>
   <mergeCells count="131">
-    <mergeCell ref="I208:J208"/>
-    <mergeCell ref="K208:L208"/>
-    <mergeCell ref="C216:L216"/>
-    <mergeCell ref="C234:L234"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="E217:F217"/>
-    <mergeCell ref="G217:H217"/>
-    <mergeCell ref="I217:J217"/>
-    <mergeCell ref="C235:D235"/>
-    <mergeCell ref="E235:F235"/>
-    <mergeCell ref="G235:H235"/>
-    <mergeCell ref="I235:J235"/>
-    <mergeCell ref="K235:L235"/>
-    <mergeCell ref="C226:D226"/>
-    <mergeCell ref="E226:F226"/>
-    <mergeCell ref="G226:H226"/>
-    <mergeCell ref="I226:J226"/>
-    <mergeCell ref="K226:L226"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C107:L107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="C134:L134"/>
+    <mergeCell ref="C125:L125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="C116:L116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="K117:L117"/>
+    <mergeCell ref="C144:L144"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="C153:L153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="K154:L154"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="C171:L171"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="I172:J172"/>
+    <mergeCell ref="K172:L172"/>
     <mergeCell ref="C180:L180"/>
     <mergeCell ref="C181:D181"/>
     <mergeCell ref="E181:F181"/>
@@ -11965,95 +12042,24 @@
     <mergeCell ref="C208:D208"/>
     <mergeCell ref="E208:F208"/>
     <mergeCell ref="G208:H208"/>
-    <mergeCell ref="C162:L162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="K163:L163"/>
-    <mergeCell ref="C171:L171"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="I172:J172"/>
-    <mergeCell ref="K172:L172"/>
-    <mergeCell ref="C144:L144"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="E145:F145"/>
-    <mergeCell ref="G145:H145"/>
-    <mergeCell ref="I145:J145"/>
-    <mergeCell ref="K145:L145"/>
-    <mergeCell ref="C153:L153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="I154:J154"/>
-    <mergeCell ref="K154:L154"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="C134:L134"/>
-    <mergeCell ref="C125:L125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="G126:H126"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="K126:L126"/>
-    <mergeCell ref="C116:L116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="G117:H117"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="K117:L117"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C107:L107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="I208:J208"/>
+    <mergeCell ref="K208:L208"/>
+    <mergeCell ref="C216:L216"/>
+    <mergeCell ref="C234:L234"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="I217:J217"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="I235:J235"/>
+    <mergeCell ref="K235:L235"/>
+    <mergeCell ref="C226:D226"/>
+    <mergeCell ref="E226:F226"/>
+    <mergeCell ref="G226:H226"/>
+    <mergeCell ref="I226:J226"/>
+    <mergeCell ref="K226:L226"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12062,7 +12068,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B9:I245"/>
+  <dimension ref="B9:I246"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -12077,10 +12083,10 @@
   <sheetData>
     <row r="9" spans="2:5" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="133" t="s">
+      <c r="C10" s="134" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="134"/>
+      <c r="D10" s="135"/>
       <c r="E10" s="28" t="s">
         <v>75</v>
       </c>
@@ -15346,21 +15352,35 @@
       </c>
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B244" s="107">
+      <c r="B244" s="93">
         <v>46113</v>
       </c>
-      <c r="C244" s="105">
+      <c r="C244" s="87">
         <v>46922560</v>
       </c>
-      <c r="D244" s="21">
+      <c r="D244" s="83">
         <v>13081</v>
       </c>
-      <c r="E244" s="20">
+      <c r="E244" s="22">
         <v>3587.077440562648</v>
       </c>
     </row>
     <row r="245" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B245" s="55" t="s">
+      <c r="B245" s="107">
+        <v>46143</v>
+      </c>
+      <c r="C245" s="105">
+        <v>62622331</v>
+      </c>
+      <c r="D245" s="21">
+        <v>16871</v>
+      </c>
+      <c r="E245" s="20">
+        <v>3711.8327899946653</v>
+      </c>
+    </row>
+    <row r="246" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B246" s="55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -15378,10 +15398,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -15622,35 +15658,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC8F936-4AF3-4FF9-8B1E-0736929643E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15669,21 +15700,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data_raw/exportacion_leche_polvo_entera.xlsx
+++ b/data_raw/exportacion_leche_polvo_entera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/2- Mercado externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="672" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC4F1BFF-158C-4215-B8E0-7E504AE08118}"/>
+  <xr:revisionPtr revIDLastSave="697" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFF0918C-6DE5-4A9E-B5C2-F9B8B12C6E11}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="703" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="85">
   <si>
     <t>Estos datos se consideran preliminares a partir del 23/10/2020 e incluyen Admisiones temporales. Estas modificaciones recientes se deben a cambios realizados por la Agencia de Aduanas de Uruguay.</t>
   </si>
@@ -1804,14 +1804,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3581,7 +3581,9 @@
       <c r="G35" s="100">
         <v>62622331</v>
       </c>
-      <c r="H35" s="99"/>
+      <c r="H35" s="99">
+        <v>50078562.629999995</v>
+      </c>
       <c r="I35" s="100"/>
       <c r="J35" s="100"/>
       <c r="K35" s="100"/>
@@ -4642,7 +4644,9 @@
       <c r="G59" s="91">
         <v>16871</v>
       </c>
-      <c r="H59" s="91"/>
+      <c r="H59" s="91">
+        <v>13469.828960000001</v>
+      </c>
       <c r="I59" s="91"/>
       <c r="J59" s="91"/>
       <c r="K59" s="91"/>
@@ -5721,7 +5725,9 @@
       <c r="G83" s="18">
         <v>3711.8327899946653</v>
       </c>
-      <c r="H83" s="18"/>
+      <c r="H83" s="18">
+        <v>3717.8321104680153</v>
+      </c>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
       <c r="K83" s="18"/>
@@ -5890,23 +5896,23 @@
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:13" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="133" t="s">
+      <c r="C13" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="129"/>
-      <c r="E13" s="133" t="s">
+      <c r="E13" s="128" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="129"/>
-      <c r="G13" s="133" t="s">
+      <c r="G13" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="129"/>
-      <c r="I13" s="133" t="s">
+      <c r="I13" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="129"/>
-      <c r="K13" s="133" t="s">
+      <c r="K13" s="128" t="s">
         <v>32</v>
       </c>
       <c r="L13" s="129"/>
@@ -6687,8 +6693,12 @@
         <f>+C34/C33-1</f>
         <v>2.9597011555922759E-2</v>
       </c>
-      <c r="E34" s="53"/>
-      <c r="F34" s="54"/>
+      <c r="E34" s="53">
+        <v>43421.828959999999</v>
+      </c>
+      <c r="F34" s="54">
+        <v>0.28107286975257928</v>
+      </c>
       <c r="G34" s="18"/>
       <c r="H34" s="54"/>
       <c r="I34" s="53"/>
@@ -6708,23 +6718,23 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="133" t="s">
+      <c r="C37" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="129"/>
-      <c r="E37" s="133" t="s">
+      <c r="E37" s="128" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="129"/>
-      <c r="G37" s="133" t="s">
+      <c r="G37" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H37" s="129"/>
-      <c r="I37" s="133" t="s">
+      <c r="I37" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J37" s="129"/>
-      <c r="K37" s="133" t="s">
+      <c r="K37" s="128" t="s">
         <v>32</v>
       </c>
       <c r="L37" s="129"/>
@@ -7509,8 +7519,12 @@
         <f>+C58/C57-1</f>
         <v>-7.3453676943462276E-2</v>
       </c>
-      <c r="E58" s="53"/>
-      <c r="F58" s="54"/>
+      <c r="E58" s="53">
+        <v>3676.1107823681132</v>
+      </c>
+      <c r="F58" s="54">
+        <v>-9.3127046747667586E-2</v>
+      </c>
       <c r="G58" s="53"/>
       <c r="H58" s="54"/>
       <c r="I58" s="53"/>
@@ -7563,23 +7577,23 @@
       <c r="B67" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C67" s="133" t="s">
+      <c r="C67" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D67" s="129"/>
-      <c r="E67" s="133" t="s">
+      <c r="E67" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F67" s="128"/>
-      <c r="G67" s="133" t="s">
+      <c r="F67" s="130"/>
+      <c r="G67" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H67" s="129"/>
-      <c r="I67" s="128" t="s">
+      <c r="I67" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J67" s="129"/>
-      <c r="K67" s="128" t="s">
+      <c r="K67" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L67" s="129"/>
@@ -7594,8 +7608,12 @@
       <c r="D68" s="61">
         <v>0.42775763889315399</v>
       </c>
-      <c r="E68" s="60"/>
-      <c r="F68" s="61"/>
+      <c r="E68" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="61">
+        <v>0.41115705106505651</v>
+      </c>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="60"/>
@@ -7613,8 +7631,12 @@
       <c r="D69" s="64">
         <v>0.30671046829801124</v>
       </c>
-      <c r="E69" s="63"/>
-      <c r="F69" s="64"/>
+      <c r="E69" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F69" s="64">
+        <v>0.28617390053916414</v>
+      </c>
       <c r="G69" s="63"/>
       <c r="H69" s="64"/>
       <c r="I69" s="63"/>
@@ -7632,8 +7654,12 @@
       <c r="D70" s="64">
         <v>4.4019583367787392E-2</v>
       </c>
-      <c r="E70" s="63"/>
-      <c r="F70" s="64"/>
+      <c r="E70" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="F70" s="64">
+        <v>5.1827652884059092E-2</v>
+      </c>
       <c r="G70" s="63"/>
       <c r="H70" s="64"/>
       <c r="I70" s="63"/>
@@ -7651,8 +7677,12 @@
       <c r="D71" s="66">
         <v>2.6975318259112924E-2</v>
       </c>
-      <c r="E71" s="63"/>
-      <c r="F71" s="64"/>
+      <c r="E71" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71" s="64">
+        <v>4.7047697731091499E-2</v>
+      </c>
       <c r="G71" s="63"/>
       <c r="H71" s="64"/>
       <c r="I71" s="63"/>
@@ -7670,8 +7700,12 @@
       <c r="D72" s="69">
         <v>2.6262356589528607E-2</v>
       </c>
-      <c r="E72" s="70"/>
-      <c r="F72" s="71"/>
+      <c r="E72" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="F72" s="71">
+        <v>4.2187842352278848E-2</v>
+      </c>
       <c r="G72" s="70"/>
       <c r="H72" s="71"/>
       <c r="I72" s="70"/>
@@ -7700,23 +7734,23 @@
       <c r="B75" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C75" s="133" t="s">
+      <c r="C75" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="129"/>
-      <c r="E75" s="133" t="s">
+      <c r="E75" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F75" s="128"/>
-      <c r="G75" s="133" t="s">
+      <c r="F75" s="130"/>
+      <c r="G75" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H75" s="129"/>
-      <c r="I75" s="128" t="s">
+      <c r="I75" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J75" s="129"/>
-      <c r="K75" s="128" t="s">
+      <c r="K75" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L75" s="129"/>
@@ -7917,23 +7951,23 @@
       <c r="B83" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C83" s="133" t="s">
+      <c r="C83" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D83" s="129"/>
-      <c r="E83" s="133" t="s">
+      <c r="E83" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F83" s="128"/>
-      <c r="G83" s="133" t="s">
+      <c r="F83" s="130"/>
+      <c r="G83" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H83" s="129"/>
-      <c r="I83" s="128" t="s">
+      <c r="I83" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J83" s="129"/>
-      <c r="K83" s="128" t="s">
+      <c r="K83" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L83" s="129"/>
@@ -8134,23 +8168,23 @@
       <c r="B91" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C91" s="133" t="s">
+      <c r="C91" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="129"/>
-      <c r="E91" s="133" t="s">
+      <c r="E91" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F91" s="128"/>
-      <c r="G91" s="133" t="s">
+      <c r="F91" s="130"/>
+      <c r="G91" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H91" s="129"/>
-      <c r="I91" s="128" t="s">
+      <c r="I91" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J91" s="129"/>
-      <c r="K91" s="128" t="s">
+      <c r="K91" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L91" s="129"/>
@@ -8351,23 +8385,23 @@
       <c r="B99" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C99" s="133" t="s">
+      <c r="C99" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="129"/>
-      <c r="E99" s="133" t="s">
+      <c r="E99" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F99" s="128"/>
-      <c r="G99" s="133" t="s">
+      <c r="F99" s="130"/>
+      <c r="G99" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H99" s="129"/>
-      <c r="I99" s="128" t="s">
+      <c r="I99" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J99" s="129"/>
-      <c r="K99" s="128" t="s">
+      <c r="K99" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L99" s="129"/>
@@ -8579,23 +8613,23 @@
       <c r="B108" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C108" s="133" t="s">
+      <c r="C108" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="129"/>
-      <c r="E108" s="133" t="s">
+      <c r="E108" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F108" s="128"/>
-      <c r="G108" s="133" t="s">
+      <c r="F108" s="130"/>
+      <c r="G108" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H108" s="129"/>
-      <c r="I108" s="128" t="s">
+      <c r="I108" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J108" s="129"/>
-      <c r="K108" s="128" t="s">
+      <c r="K108" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L108" s="129"/>
@@ -8809,23 +8843,23 @@
       <c r="B117" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C117" s="133" t="s">
+      <c r="C117" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D117" s="129"/>
-      <c r="E117" s="133" t="s">
+      <c r="E117" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F117" s="128"/>
-      <c r="G117" s="133" t="s">
+      <c r="F117" s="130"/>
+      <c r="G117" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H117" s="129"/>
-      <c r="I117" s="128" t="s">
+      <c r="I117" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J117" s="129"/>
-      <c r="K117" s="128" t="s">
+      <c r="K117" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L117" s="129"/>
@@ -9039,23 +9073,23 @@
       <c r="B126" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C126" s="133" t="s">
+      <c r="C126" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="129"/>
-      <c r="E126" s="133" t="s">
+      <c r="E126" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F126" s="128"/>
-      <c r="G126" s="133" t="s">
+      <c r="F126" s="130"/>
+      <c r="G126" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H126" s="129"/>
-      <c r="I126" s="128" t="s">
+      <c r="I126" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J126" s="129"/>
-      <c r="K126" s="128" t="s">
+      <c r="K126" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L126" s="129"/>
@@ -9269,23 +9303,23 @@
       <c r="B135" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C135" s="133" t="s">
+      <c r="C135" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="129"/>
-      <c r="E135" s="133" t="s">
+      <c r="E135" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F135" s="128"/>
-      <c r="G135" s="133" t="s">
+      <c r="F135" s="130"/>
+      <c r="G135" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H135" s="129"/>
-      <c r="I135" s="128" t="s">
+      <c r="I135" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J135" s="129"/>
-      <c r="K135" s="128" t="s">
+      <c r="K135" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L135" s="129"/>
@@ -9499,23 +9533,23 @@
       <c r="B145" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C145" s="133" t="s">
+      <c r="C145" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="129"/>
-      <c r="E145" s="133" t="s">
+      <c r="E145" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F145" s="128"/>
-      <c r="G145" s="133" t="s">
+      <c r="F145" s="130"/>
+      <c r="G145" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H145" s="129"/>
-      <c r="I145" s="128" t="s">
+      <c r="I145" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J145" s="129"/>
-      <c r="K145" s="128" t="s">
+      <c r="K145" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L145" s="129"/>
@@ -9729,23 +9763,23 @@
       <c r="B154" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C154" s="133" t="s">
+      <c r="C154" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D154" s="129"/>
-      <c r="E154" s="133" t="s">
+      <c r="E154" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F154" s="128"/>
-      <c r="G154" s="133" t="s">
+      <c r="F154" s="130"/>
+      <c r="G154" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H154" s="129"/>
-      <c r="I154" s="128" t="s">
+      <c r="I154" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J154" s="129"/>
-      <c r="K154" s="128" t="s">
+      <c r="K154" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L154" s="129"/>
@@ -9959,23 +9993,23 @@
       <c r="B163" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C163" s="133" t="s">
+      <c r="C163" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D163" s="129"/>
-      <c r="E163" s="133" t="s">
+      <c r="E163" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F163" s="128"/>
-      <c r="G163" s="133" t="s">
+      <c r="F163" s="130"/>
+      <c r="G163" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H163" s="129"/>
-      <c r="I163" s="128" t="s">
+      <c r="I163" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J163" s="129"/>
-      <c r="K163" s="128" t="s">
+      <c r="K163" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L163" s="129"/>
@@ -10179,23 +10213,23 @@
       <c r="B172" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C172" s="133" t="s">
+      <c r="C172" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D172" s="129"/>
-      <c r="E172" s="133" t="s">
+      <c r="E172" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F172" s="128"/>
-      <c r="G172" s="133" t="s">
+      <c r="F172" s="130"/>
+      <c r="G172" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H172" s="129"/>
-      <c r="I172" s="128" t="s">
+      <c r="I172" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J172" s="129"/>
-      <c r="K172" s="128" t="s">
+      <c r="K172" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L172" s="129"/>
@@ -10399,23 +10433,23 @@
       <c r="B181" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C181" s="133" t="s">
+      <c r="C181" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D181" s="129"/>
-      <c r="E181" s="133" t="s">
+      <c r="E181" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F181" s="128"/>
-      <c r="G181" s="133" t="s">
+      <c r="F181" s="130"/>
+      <c r="G181" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H181" s="129"/>
-      <c r="I181" s="128" t="s">
+      <c r="I181" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J181" s="129"/>
-      <c r="K181" s="128" t="s">
+      <c r="K181" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L181" s="129"/>
@@ -10620,23 +10654,23 @@
       <c r="B190" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C190" s="133" t="s">
+      <c r="C190" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D190" s="129"/>
-      <c r="E190" s="133" t="s">
+      <c r="E190" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F190" s="128"/>
-      <c r="G190" s="133" t="s">
+      <c r="F190" s="130"/>
+      <c r="G190" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H190" s="129"/>
-      <c r="I190" s="128" t="s">
+      <c r="I190" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J190" s="129"/>
-      <c r="K190" s="128" t="s">
+      <c r="K190" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L190" s="129"/>
@@ -10841,23 +10875,23 @@
       <c r="B199" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C199" s="133" t="s">
+      <c r="C199" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D199" s="129"/>
-      <c r="E199" s="133" t="s">
+      <c r="E199" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F199" s="128"/>
-      <c r="G199" s="133" t="s">
+      <c r="F199" s="130"/>
+      <c r="G199" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H199" s="129"/>
-      <c r="I199" s="128" t="s">
+      <c r="I199" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J199" s="129"/>
-      <c r="K199" s="128" t="s">
+      <c r="K199" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L199" s="129"/>
@@ -11062,23 +11096,23 @@
       <c r="B208" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C208" s="133" t="s">
+      <c r="C208" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D208" s="129"/>
-      <c r="E208" s="133" t="s">
+      <c r="E208" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F208" s="128"/>
-      <c r="G208" s="133" t="s">
+      <c r="F208" s="130"/>
+      <c r="G208" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H208" s="129"/>
-      <c r="I208" s="128" t="s">
+      <c r="I208" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J208" s="129"/>
-      <c r="K208" s="128" t="s">
+      <c r="K208" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L208" s="129"/>
@@ -11283,23 +11317,23 @@
       <c r="B217" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C217" s="133" t="s">
+      <c r="C217" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D217" s="129"/>
-      <c r="E217" s="133" t="s">
+      <c r="E217" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F217" s="128"/>
-      <c r="G217" s="133" t="s">
+      <c r="F217" s="130"/>
+      <c r="G217" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H217" s="129"/>
-      <c r="I217" s="128" t="s">
+      <c r="I217" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J217" s="129"/>
-      <c r="K217" s="128" t="s">
+      <c r="K217" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L217" s="129"/>
@@ -11504,23 +11538,23 @@
       <c r="B226" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C226" s="133" t="s">
+      <c r="C226" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D226" s="129"/>
-      <c r="E226" s="133" t="s">
+      <c r="E226" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F226" s="128"/>
-      <c r="G226" s="133" t="s">
+      <c r="F226" s="130"/>
+      <c r="G226" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H226" s="129"/>
-      <c r="I226" s="128" t="s">
+      <c r="I226" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J226" s="129"/>
-      <c r="K226" s="128" t="s">
+      <c r="K226" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L226" s="129"/>
@@ -11708,7 +11742,7 @@
     </row>
     <row r="233" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="234" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C234" s="130" t="s">
+      <c r="C234" s="133" t="s">
         <v>73</v>
       </c>
       <c r="D234" s="131"/>
@@ -11725,23 +11759,23 @@
       <c r="B235" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C235" s="133" t="s">
+      <c r="C235" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D235" s="129"/>
-      <c r="E235" s="133" t="s">
+      <c r="E235" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F235" s="128"/>
-      <c r="G235" s="133" t="s">
+      <c r="F235" s="130"/>
+      <c r="G235" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H235" s="129"/>
-      <c r="I235" s="128" t="s">
+      <c r="I235" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J235" s="129"/>
-      <c r="K235" s="128" t="s">
+      <c r="K235" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L235" s="129"/>
@@ -11929,95 +11963,24 @@
     </row>
   </sheetData>
   <mergeCells count="131">
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C107:L107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="C134:L134"/>
-    <mergeCell ref="C125:L125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="G126:H126"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="K126:L126"/>
-    <mergeCell ref="C116:L116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="G117:H117"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="K117:L117"/>
-    <mergeCell ref="C144:L144"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="E145:F145"/>
-    <mergeCell ref="G145:H145"/>
-    <mergeCell ref="I145:J145"/>
-    <mergeCell ref="K145:L145"/>
-    <mergeCell ref="C153:L153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="I154:J154"/>
-    <mergeCell ref="K154:L154"/>
-    <mergeCell ref="C162:L162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="K163:L163"/>
-    <mergeCell ref="C171:L171"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="I172:J172"/>
-    <mergeCell ref="K172:L172"/>
+    <mergeCell ref="I208:J208"/>
+    <mergeCell ref="K208:L208"/>
+    <mergeCell ref="C216:L216"/>
+    <mergeCell ref="C234:L234"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="I217:J217"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="I235:J235"/>
+    <mergeCell ref="K235:L235"/>
+    <mergeCell ref="C226:D226"/>
+    <mergeCell ref="E226:F226"/>
+    <mergeCell ref="G226:H226"/>
+    <mergeCell ref="I226:J226"/>
+    <mergeCell ref="K226:L226"/>
     <mergeCell ref="C180:L180"/>
     <mergeCell ref="C181:D181"/>
     <mergeCell ref="E181:F181"/>
@@ -12042,24 +12005,95 @@
     <mergeCell ref="C208:D208"/>
     <mergeCell ref="E208:F208"/>
     <mergeCell ref="G208:H208"/>
-    <mergeCell ref="I208:J208"/>
-    <mergeCell ref="K208:L208"/>
-    <mergeCell ref="C216:L216"/>
-    <mergeCell ref="C234:L234"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="E217:F217"/>
-    <mergeCell ref="G217:H217"/>
-    <mergeCell ref="I217:J217"/>
-    <mergeCell ref="C235:D235"/>
-    <mergeCell ref="E235:F235"/>
-    <mergeCell ref="G235:H235"/>
-    <mergeCell ref="I235:J235"/>
-    <mergeCell ref="K235:L235"/>
-    <mergeCell ref="C226:D226"/>
-    <mergeCell ref="E226:F226"/>
-    <mergeCell ref="G226:H226"/>
-    <mergeCell ref="I226:J226"/>
-    <mergeCell ref="K226:L226"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="C171:L171"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="I172:J172"/>
+    <mergeCell ref="K172:L172"/>
+    <mergeCell ref="C144:L144"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="C153:L153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="K154:L154"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="C134:L134"/>
+    <mergeCell ref="C125:L125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="C116:L116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="K117:L117"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C107:L107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12068,7 +12102,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B9:I246"/>
+  <dimension ref="B9:I247"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -15366,21 +15400,35 @@
       </c>
     </row>
     <row r="245" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B245" s="107">
+      <c r="B245" s="93">
         <v>46143</v>
       </c>
-      <c r="C245" s="105">
+      <c r="C245" s="87">
         <v>62622331</v>
       </c>
-      <c r="D245" s="21">
+      <c r="D245" s="83">
         <v>16871</v>
       </c>
-      <c r="E245" s="20">
+      <c r="E245" s="22">
         <v>3711.8327899946653</v>
       </c>
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B246" s="55" t="s">
+      <c r="B246" s="107">
+        <v>46174</v>
+      </c>
+      <c r="C246" s="105">
+        <v>50078562.629999995</v>
+      </c>
+      <c r="D246" s="21">
+        <v>13469.828960000001</v>
+      </c>
+      <c r="E246" s="20">
+        <v>3717.8321104680153</v>
+      </c>
+    </row>
+    <row r="247" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B247" s="55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -15398,26 +15446,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -15658,30 +15690,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC8F936-4AF3-4FF9-8B1E-0736929643E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15700,10 +15737,21 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data_raw/exportacion_leche_polvo_entera.xlsx
+++ b/data_raw/exportacion_leche_polvo_entera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/2- Mercado externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="697" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFF0918C-6DE5-4A9E-B5C2-F9B8B12C6E11}"/>
+  <xr:revisionPtr revIDLastSave="708" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A358CB6D-CCB2-4126-B499-ACBBC8025FB6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="703" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1804,14 +1804,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3584,7 +3584,9 @@
       <c r="H35" s="99">
         <v>50078562.629999995</v>
       </c>
-      <c r="I35" s="100"/>
+      <c r="I35" s="100">
+        <v>67136919.599999964</v>
+      </c>
       <c r="J35" s="100"/>
       <c r="K35" s="100"/>
       <c r="L35" s="100"/>
@@ -4647,7 +4649,9 @@
       <c r="H59" s="91">
         <v>13469.828960000001</v>
       </c>
-      <c r="I59" s="91"/>
+      <c r="I59" s="91">
+        <v>17681.99694999999</v>
+      </c>
       <c r="J59" s="91"/>
       <c r="K59" s="91"/>
       <c r="L59" s="95"/>
@@ -5728,7 +5732,9 @@
       <c r="H83" s="18">
         <v>3717.8321104680153</v>
       </c>
-      <c r="I83" s="18"/>
+      <c r="I83" s="18">
+        <v>3796.9082219528377</v>
+      </c>
       <c r="J83" s="18"/>
       <c r="K83" s="18"/>
       <c r="L83" s="18"/>
@@ -5896,23 +5902,23 @@
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:13" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="128" t="s">
+      <c r="C13" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="129"/>
-      <c r="E13" s="128" t="s">
+      <c r="E13" s="133" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="129"/>
-      <c r="G13" s="128" t="s">
+      <c r="G13" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="129"/>
-      <c r="I13" s="128" t="s">
+      <c r="I13" s="133" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="129"/>
-      <c r="K13" s="128" t="s">
+      <c r="K13" s="133" t="s">
         <v>32</v>
       </c>
       <c r="L13" s="129"/>
@@ -6718,23 +6724,23 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="128" t="s">
+      <c r="C37" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="129"/>
-      <c r="E37" s="128" t="s">
+      <c r="E37" s="133" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="129"/>
-      <c r="G37" s="128" t="s">
+      <c r="G37" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H37" s="129"/>
-      <c r="I37" s="128" t="s">
+      <c r="I37" s="133" t="s">
         <v>31</v>
       </c>
       <c r="J37" s="129"/>
-      <c r="K37" s="128" t="s">
+      <c r="K37" s="133" t="s">
         <v>32</v>
       </c>
       <c r="L37" s="129"/>
@@ -7577,23 +7583,23 @@
       <c r="B67" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C67" s="128" t="s">
+      <c r="C67" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D67" s="129"/>
-      <c r="E67" s="128" t="s">
+      <c r="E67" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F67" s="130"/>
-      <c r="G67" s="128" t="s">
+      <c r="F67" s="128"/>
+      <c r="G67" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H67" s="129"/>
-      <c r="I67" s="130" t="s">
+      <c r="I67" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J67" s="129"/>
-      <c r="K67" s="130" t="s">
+      <c r="K67" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L67" s="129"/>
@@ -7734,23 +7740,23 @@
       <c r="B75" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C75" s="128" t="s">
+      <c r="C75" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="129"/>
-      <c r="E75" s="128" t="s">
+      <c r="E75" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F75" s="130"/>
-      <c r="G75" s="128" t="s">
+      <c r="F75" s="128"/>
+      <c r="G75" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H75" s="129"/>
-      <c r="I75" s="130" t="s">
+      <c r="I75" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J75" s="129"/>
-      <c r="K75" s="130" t="s">
+      <c r="K75" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L75" s="129"/>
@@ -7951,23 +7957,23 @@
       <c r="B83" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C83" s="128" t="s">
+      <c r="C83" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D83" s="129"/>
-      <c r="E83" s="128" t="s">
+      <c r="E83" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F83" s="130"/>
-      <c r="G83" s="128" t="s">
+      <c r="F83" s="128"/>
+      <c r="G83" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H83" s="129"/>
-      <c r="I83" s="130" t="s">
+      <c r="I83" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J83" s="129"/>
-      <c r="K83" s="130" t="s">
+      <c r="K83" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L83" s="129"/>
@@ -8168,23 +8174,23 @@
       <c r="B91" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C91" s="128" t="s">
+      <c r="C91" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="129"/>
-      <c r="E91" s="128" t="s">
+      <c r="E91" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F91" s="130"/>
-      <c r="G91" s="128" t="s">
+      <c r="F91" s="128"/>
+      <c r="G91" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H91" s="129"/>
-      <c r="I91" s="130" t="s">
+      <c r="I91" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J91" s="129"/>
-      <c r="K91" s="130" t="s">
+      <c r="K91" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L91" s="129"/>
@@ -8385,23 +8391,23 @@
       <c r="B99" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C99" s="128" t="s">
+      <c r="C99" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="129"/>
-      <c r="E99" s="128" t="s">
+      <c r="E99" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F99" s="130"/>
-      <c r="G99" s="128" t="s">
+      <c r="F99" s="128"/>
+      <c r="G99" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H99" s="129"/>
-      <c r="I99" s="130" t="s">
+      <c r="I99" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J99" s="129"/>
-      <c r="K99" s="130" t="s">
+      <c r="K99" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L99" s="129"/>
@@ -8613,23 +8619,23 @@
       <c r="B108" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C108" s="128" t="s">
+      <c r="C108" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="129"/>
-      <c r="E108" s="128" t="s">
+      <c r="E108" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F108" s="130"/>
-      <c r="G108" s="128" t="s">
+      <c r="F108" s="128"/>
+      <c r="G108" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H108" s="129"/>
-      <c r="I108" s="130" t="s">
+      <c r="I108" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J108" s="129"/>
-      <c r="K108" s="130" t="s">
+      <c r="K108" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L108" s="129"/>
@@ -8843,23 +8849,23 @@
       <c r="B117" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C117" s="128" t="s">
+      <c r="C117" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D117" s="129"/>
-      <c r="E117" s="128" t="s">
+      <c r="E117" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F117" s="130"/>
-      <c r="G117" s="128" t="s">
+      <c r="F117" s="128"/>
+      <c r="G117" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H117" s="129"/>
-      <c r="I117" s="130" t="s">
+      <c r="I117" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J117" s="129"/>
-      <c r="K117" s="130" t="s">
+      <c r="K117" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L117" s="129"/>
@@ -9073,23 +9079,23 @@
       <c r="B126" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C126" s="128" t="s">
+      <c r="C126" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="129"/>
-      <c r="E126" s="128" t="s">
+      <c r="E126" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F126" s="130"/>
-      <c r="G126" s="128" t="s">
+      <c r="F126" s="128"/>
+      <c r="G126" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H126" s="129"/>
-      <c r="I126" s="130" t="s">
+      <c r="I126" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J126" s="129"/>
-      <c r="K126" s="130" t="s">
+      <c r="K126" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L126" s="129"/>
@@ -9303,23 +9309,23 @@
       <c r="B135" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C135" s="128" t="s">
+      <c r="C135" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="129"/>
-      <c r="E135" s="128" t="s">
+      <c r="E135" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F135" s="130"/>
-      <c r="G135" s="128" t="s">
+      <c r="F135" s="128"/>
+      <c r="G135" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H135" s="129"/>
-      <c r="I135" s="130" t="s">
+      <c r="I135" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J135" s="129"/>
-      <c r="K135" s="130" t="s">
+      <c r="K135" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L135" s="129"/>
@@ -9533,23 +9539,23 @@
       <c r="B145" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C145" s="128" t="s">
+      <c r="C145" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="129"/>
-      <c r="E145" s="128" t="s">
+      <c r="E145" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F145" s="130"/>
-      <c r="G145" s="128" t="s">
+      <c r="F145" s="128"/>
+      <c r="G145" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H145" s="129"/>
-      <c r="I145" s="130" t="s">
+      <c r="I145" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J145" s="129"/>
-      <c r="K145" s="130" t="s">
+      <c r="K145" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L145" s="129"/>
@@ -9763,23 +9769,23 @@
       <c r="B154" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C154" s="128" t="s">
+      <c r="C154" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D154" s="129"/>
-      <c r="E154" s="128" t="s">
+      <c r="E154" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F154" s="130"/>
-      <c r="G154" s="128" t="s">
+      <c r="F154" s="128"/>
+      <c r="G154" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H154" s="129"/>
-      <c r="I154" s="130" t="s">
+      <c r="I154" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J154" s="129"/>
-      <c r="K154" s="130" t="s">
+      <c r="K154" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L154" s="129"/>
@@ -9993,23 +9999,23 @@
       <c r="B163" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C163" s="128" t="s">
+      <c r="C163" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D163" s="129"/>
-      <c r="E163" s="128" t="s">
+      <c r="E163" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F163" s="130"/>
-      <c r="G163" s="128" t="s">
+      <c r="F163" s="128"/>
+      <c r="G163" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H163" s="129"/>
-      <c r="I163" s="130" t="s">
+      <c r="I163" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J163" s="129"/>
-      <c r="K163" s="130" t="s">
+      <c r="K163" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L163" s="129"/>
@@ -10213,23 +10219,23 @@
       <c r="B172" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C172" s="128" t="s">
+      <c r="C172" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D172" s="129"/>
-      <c r="E172" s="128" t="s">
+      <c r="E172" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F172" s="130"/>
-      <c r="G172" s="128" t="s">
+      <c r="F172" s="128"/>
+      <c r="G172" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H172" s="129"/>
-      <c r="I172" s="130" t="s">
+      <c r="I172" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J172" s="129"/>
-      <c r="K172" s="130" t="s">
+      <c r="K172" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L172" s="129"/>
@@ -10433,23 +10439,23 @@
       <c r="B181" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C181" s="128" t="s">
+      <c r="C181" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D181" s="129"/>
-      <c r="E181" s="128" t="s">
+      <c r="E181" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F181" s="130"/>
-      <c r="G181" s="128" t="s">
+      <c r="F181" s="128"/>
+      <c r="G181" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H181" s="129"/>
-      <c r="I181" s="130" t="s">
+      <c r="I181" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J181" s="129"/>
-      <c r="K181" s="130" t="s">
+      <c r="K181" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L181" s="129"/>
@@ -10654,23 +10660,23 @@
       <c r="B190" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C190" s="128" t="s">
+      <c r="C190" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D190" s="129"/>
-      <c r="E190" s="128" t="s">
+      <c r="E190" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F190" s="130"/>
-      <c r="G190" s="128" t="s">
+      <c r="F190" s="128"/>
+      <c r="G190" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H190" s="129"/>
-      <c r="I190" s="130" t="s">
+      <c r="I190" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J190" s="129"/>
-      <c r="K190" s="130" t="s">
+      <c r="K190" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L190" s="129"/>
@@ -10875,23 +10881,23 @@
       <c r="B199" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C199" s="128" t="s">
+      <c r="C199" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D199" s="129"/>
-      <c r="E199" s="128" t="s">
+      <c r="E199" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F199" s="130"/>
-      <c r="G199" s="128" t="s">
+      <c r="F199" s="128"/>
+      <c r="G199" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H199" s="129"/>
-      <c r="I199" s="130" t="s">
+      <c r="I199" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J199" s="129"/>
-      <c r="K199" s="130" t="s">
+      <c r="K199" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L199" s="129"/>
@@ -11096,23 +11102,23 @@
       <c r="B208" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C208" s="128" t="s">
+      <c r="C208" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D208" s="129"/>
-      <c r="E208" s="128" t="s">
+      <c r="E208" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F208" s="130"/>
-      <c r="G208" s="128" t="s">
+      <c r="F208" s="128"/>
+      <c r="G208" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H208" s="129"/>
-      <c r="I208" s="130" t="s">
+      <c r="I208" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J208" s="129"/>
-      <c r="K208" s="130" t="s">
+      <c r="K208" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L208" s="129"/>
@@ -11317,23 +11323,23 @@
       <c r="B217" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C217" s="128" t="s">
+      <c r="C217" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D217" s="129"/>
-      <c r="E217" s="128" t="s">
+      <c r="E217" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F217" s="130"/>
-      <c r="G217" s="128" t="s">
+      <c r="F217" s="128"/>
+      <c r="G217" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H217" s="129"/>
-      <c r="I217" s="130" t="s">
+      <c r="I217" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J217" s="129"/>
-      <c r="K217" s="130" t="s">
+      <c r="K217" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L217" s="129"/>
@@ -11538,23 +11544,23 @@
       <c r="B226" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C226" s="128" t="s">
+      <c r="C226" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D226" s="129"/>
-      <c r="E226" s="128" t="s">
+      <c r="E226" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F226" s="130"/>
-      <c r="G226" s="128" t="s">
+      <c r="F226" s="128"/>
+      <c r="G226" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H226" s="129"/>
-      <c r="I226" s="130" t="s">
+      <c r="I226" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J226" s="129"/>
-      <c r="K226" s="130" t="s">
+      <c r="K226" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L226" s="129"/>
@@ -11742,7 +11748,7 @@
     </row>
     <row r="233" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="234" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C234" s="133" t="s">
+      <c r="C234" s="130" t="s">
         <v>73</v>
       </c>
       <c r="D234" s="131"/>
@@ -11759,23 +11765,23 @@
       <c r="B235" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C235" s="128" t="s">
+      <c r="C235" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D235" s="129"/>
-      <c r="E235" s="128" t="s">
+      <c r="E235" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F235" s="130"/>
-      <c r="G235" s="128" t="s">
+      <c r="F235" s="128"/>
+      <c r="G235" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H235" s="129"/>
-      <c r="I235" s="130" t="s">
+      <c r="I235" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J235" s="129"/>
-      <c r="K235" s="130" t="s">
+      <c r="K235" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L235" s="129"/>
@@ -11963,24 +11969,95 @@
     </row>
   </sheetData>
   <mergeCells count="131">
-    <mergeCell ref="I208:J208"/>
-    <mergeCell ref="K208:L208"/>
-    <mergeCell ref="C216:L216"/>
-    <mergeCell ref="C234:L234"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="E217:F217"/>
-    <mergeCell ref="G217:H217"/>
-    <mergeCell ref="I217:J217"/>
-    <mergeCell ref="C235:D235"/>
-    <mergeCell ref="E235:F235"/>
-    <mergeCell ref="G235:H235"/>
-    <mergeCell ref="I235:J235"/>
-    <mergeCell ref="K235:L235"/>
-    <mergeCell ref="C226:D226"/>
-    <mergeCell ref="E226:F226"/>
-    <mergeCell ref="G226:H226"/>
-    <mergeCell ref="I226:J226"/>
-    <mergeCell ref="K226:L226"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C107:L107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="C134:L134"/>
+    <mergeCell ref="C125:L125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="C116:L116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="K117:L117"/>
+    <mergeCell ref="C144:L144"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="C153:L153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="K154:L154"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="C171:L171"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="I172:J172"/>
+    <mergeCell ref="K172:L172"/>
     <mergeCell ref="C180:L180"/>
     <mergeCell ref="C181:D181"/>
     <mergeCell ref="E181:F181"/>
@@ -12005,95 +12082,24 @@
     <mergeCell ref="C208:D208"/>
     <mergeCell ref="E208:F208"/>
     <mergeCell ref="G208:H208"/>
-    <mergeCell ref="C162:L162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="K163:L163"/>
-    <mergeCell ref="C171:L171"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="I172:J172"/>
-    <mergeCell ref="K172:L172"/>
-    <mergeCell ref="C144:L144"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="E145:F145"/>
-    <mergeCell ref="G145:H145"/>
-    <mergeCell ref="I145:J145"/>
-    <mergeCell ref="K145:L145"/>
-    <mergeCell ref="C153:L153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="I154:J154"/>
-    <mergeCell ref="K154:L154"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="C134:L134"/>
-    <mergeCell ref="C125:L125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="G126:H126"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="K126:L126"/>
-    <mergeCell ref="C116:L116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="G117:H117"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="K117:L117"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C107:L107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="I208:J208"/>
+    <mergeCell ref="K208:L208"/>
+    <mergeCell ref="C216:L216"/>
+    <mergeCell ref="C234:L234"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="I217:J217"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="I235:J235"/>
+    <mergeCell ref="K235:L235"/>
+    <mergeCell ref="C226:D226"/>
+    <mergeCell ref="E226:F226"/>
+    <mergeCell ref="G226:H226"/>
+    <mergeCell ref="I226:J226"/>
+    <mergeCell ref="K226:L226"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12102,7 +12108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B9:I247"/>
+  <dimension ref="B9:I248"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -15414,21 +15420,35 @@
       </c>
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B246" s="107">
+      <c r="B246" s="93">
         <v>46174</v>
       </c>
-      <c r="C246" s="105">
+      <c r="C246" s="87">
         <v>50078562.629999995</v>
       </c>
-      <c r="D246" s="21">
+      <c r="D246" s="83">
         <v>13469.828960000001</v>
       </c>
-      <c r="E246" s="20">
+      <c r="E246" s="22">
         <v>3717.8321104680153</v>
       </c>
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B247" s="55" t="s">
+      <c r="B247" s="107">
+        <v>46204</v>
+      </c>
+      <c r="C247" s="105">
+        <v>67136919.599999964</v>
+      </c>
+      <c r="D247" s="21">
+        <v>17681.99694999999</v>
+      </c>
+      <c r="E247" s="20">
+        <v>3796.9082219528377</v>
+      </c>
+    </row>
+    <row r="248" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B248" s="55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -15446,10 +15466,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -15690,35 +15726,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC8F936-4AF3-4FF9-8B1E-0736929643E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15737,21 +15768,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data_raw/exportacion_leche_polvo_entera.xlsx
+++ b/data_raw/exportacion_leche_polvo_entera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/2- Mercado externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="708" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A358CB6D-CCB2-4126-B499-ACBBC8025FB6}"/>
+  <xr:revisionPtr revIDLastSave="721" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4723A0B2-0C2D-4BA3-82E2-08AB10AA6CE1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="703" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1804,14 +1804,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3587,7 +3587,9 @@
       <c r="I35" s="100">
         <v>67136919.599999964</v>
       </c>
-      <c r="J35" s="100"/>
+      <c r="J35" s="100">
+        <v>41213979.369999953</v>
+      </c>
       <c r="K35" s="100"/>
       <c r="L35" s="100"/>
       <c r="M35" s="99"/>
@@ -4652,7 +4654,9 @@
       <c r="I59" s="91">
         <v>17681.99694999999</v>
       </c>
-      <c r="J59" s="91"/>
+      <c r="J59" s="91">
+        <v>11081.581000000002</v>
+      </c>
       <c r="K59" s="91"/>
       <c r="L59" s="95"/>
       <c r="M59" s="95"/>
@@ -5735,7 +5739,9 @@
       <c r="I83" s="18">
         <v>3796.9082219528377</v>
       </c>
-      <c r="J83" s="18"/>
+      <c r="J83" s="18">
+        <v>3719.1425456349543</v>
+      </c>
       <c r="K83" s="18"/>
       <c r="L83" s="18"/>
       <c r="M83" s="18"/>
@@ -5902,23 +5908,23 @@
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:13" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="133" t="s">
+      <c r="C13" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="129"/>
-      <c r="E13" s="133" t="s">
+      <c r="E13" s="128" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="129"/>
-      <c r="G13" s="133" t="s">
+      <c r="G13" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="129"/>
-      <c r="I13" s="133" t="s">
+      <c r="I13" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="129"/>
-      <c r="K13" s="133" t="s">
+      <c r="K13" s="128" t="s">
         <v>32</v>
       </c>
       <c r="L13" s="129"/>
@@ -6724,23 +6730,23 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="133" t="s">
+      <c r="C37" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="129"/>
-      <c r="E37" s="133" t="s">
+      <c r="E37" s="128" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="129"/>
-      <c r="G37" s="133" t="s">
+      <c r="G37" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H37" s="129"/>
-      <c r="I37" s="133" t="s">
+      <c r="I37" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J37" s="129"/>
-      <c r="K37" s="133" t="s">
+      <c r="K37" s="128" t="s">
         <v>32</v>
       </c>
       <c r="L37" s="129"/>
@@ -7583,23 +7589,23 @@
       <c r="B67" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C67" s="133" t="s">
+      <c r="C67" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D67" s="129"/>
-      <c r="E67" s="133" t="s">
+      <c r="E67" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F67" s="128"/>
-      <c r="G67" s="133" t="s">
+      <c r="F67" s="130"/>
+      <c r="G67" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H67" s="129"/>
-      <c r="I67" s="128" t="s">
+      <c r="I67" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J67" s="129"/>
-      <c r="K67" s="128" t="s">
+      <c r="K67" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L67" s="129"/>
@@ -7740,23 +7746,23 @@
       <c r="B75" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C75" s="133" t="s">
+      <c r="C75" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="129"/>
-      <c r="E75" s="133" t="s">
+      <c r="E75" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F75" s="128"/>
-      <c r="G75" s="133" t="s">
+      <c r="F75" s="130"/>
+      <c r="G75" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H75" s="129"/>
-      <c r="I75" s="128" t="s">
+      <c r="I75" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J75" s="129"/>
-      <c r="K75" s="128" t="s">
+      <c r="K75" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L75" s="129"/>
@@ -7957,23 +7963,23 @@
       <c r="B83" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C83" s="133" t="s">
+      <c r="C83" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D83" s="129"/>
-      <c r="E83" s="133" t="s">
+      <c r="E83" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F83" s="128"/>
-      <c r="G83" s="133" t="s">
+      <c r="F83" s="130"/>
+      <c r="G83" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H83" s="129"/>
-      <c r="I83" s="128" t="s">
+      <c r="I83" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J83" s="129"/>
-      <c r="K83" s="128" t="s">
+      <c r="K83" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L83" s="129"/>
@@ -8174,23 +8180,23 @@
       <c r="B91" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C91" s="133" t="s">
+      <c r="C91" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="129"/>
-      <c r="E91" s="133" t="s">
+      <c r="E91" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F91" s="128"/>
-      <c r="G91" s="133" t="s">
+      <c r="F91" s="130"/>
+      <c r="G91" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H91" s="129"/>
-      <c r="I91" s="128" t="s">
+      <c r="I91" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J91" s="129"/>
-      <c r="K91" s="128" t="s">
+      <c r="K91" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L91" s="129"/>
@@ -8391,23 +8397,23 @@
       <c r="B99" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C99" s="133" t="s">
+      <c r="C99" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="129"/>
-      <c r="E99" s="133" t="s">
+      <c r="E99" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F99" s="128"/>
-      <c r="G99" s="133" t="s">
+      <c r="F99" s="130"/>
+      <c r="G99" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H99" s="129"/>
-      <c r="I99" s="128" t="s">
+      <c r="I99" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J99" s="129"/>
-      <c r="K99" s="128" t="s">
+      <c r="K99" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L99" s="129"/>
@@ -8619,23 +8625,23 @@
       <c r="B108" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C108" s="133" t="s">
+      <c r="C108" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="129"/>
-      <c r="E108" s="133" t="s">
+      <c r="E108" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F108" s="128"/>
-      <c r="G108" s="133" t="s">
+      <c r="F108" s="130"/>
+      <c r="G108" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H108" s="129"/>
-      <c r="I108" s="128" t="s">
+      <c r="I108" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J108" s="129"/>
-      <c r="K108" s="128" t="s">
+      <c r="K108" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L108" s="129"/>
@@ -8849,23 +8855,23 @@
       <c r="B117" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C117" s="133" t="s">
+      <c r="C117" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D117" s="129"/>
-      <c r="E117" s="133" t="s">
+      <c r="E117" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F117" s="128"/>
-      <c r="G117" s="133" t="s">
+      <c r="F117" s="130"/>
+      <c r="G117" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H117" s="129"/>
-      <c r="I117" s="128" t="s">
+      <c r="I117" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J117" s="129"/>
-      <c r="K117" s="128" t="s">
+      <c r="K117" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L117" s="129"/>
@@ -9079,23 +9085,23 @@
       <c r="B126" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C126" s="133" t="s">
+      <c r="C126" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="129"/>
-      <c r="E126" s="133" t="s">
+      <c r="E126" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F126" s="128"/>
-      <c r="G126" s="133" t="s">
+      <c r="F126" s="130"/>
+      <c r="G126" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H126" s="129"/>
-      <c r="I126" s="128" t="s">
+      <c r="I126" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J126" s="129"/>
-      <c r="K126" s="128" t="s">
+      <c r="K126" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L126" s="129"/>
@@ -9309,23 +9315,23 @@
       <c r="B135" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C135" s="133" t="s">
+      <c r="C135" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="129"/>
-      <c r="E135" s="133" t="s">
+      <c r="E135" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F135" s="128"/>
-      <c r="G135" s="133" t="s">
+      <c r="F135" s="130"/>
+      <c r="G135" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H135" s="129"/>
-      <c r="I135" s="128" t="s">
+      <c r="I135" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J135" s="129"/>
-      <c r="K135" s="128" t="s">
+      <c r="K135" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L135" s="129"/>
@@ -9539,23 +9545,23 @@
       <c r="B145" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C145" s="133" t="s">
+      <c r="C145" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="129"/>
-      <c r="E145" s="133" t="s">
+      <c r="E145" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F145" s="128"/>
-      <c r="G145" s="133" t="s">
+      <c r="F145" s="130"/>
+      <c r="G145" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H145" s="129"/>
-      <c r="I145" s="128" t="s">
+      <c r="I145" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J145" s="129"/>
-      <c r="K145" s="128" t="s">
+      <c r="K145" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L145" s="129"/>
@@ -9769,23 +9775,23 @@
       <c r="B154" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C154" s="133" t="s">
+      <c r="C154" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D154" s="129"/>
-      <c r="E154" s="133" t="s">
+      <c r="E154" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F154" s="128"/>
-      <c r="G154" s="133" t="s">
+      <c r="F154" s="130"/>
+      <c r="G154" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H154" s="129"/>
-      <c r="I154" s="128" t="s">
+      <c r="I154" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J154" s="129"/>
-      <c r="K154" s="128" t="s">
+      <c r="K154" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L154" s="129"/>
@@ -9999,23 +10005,23 @@
       <c r="B163" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C163" s="133" t="s">
+      <c r="C163" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D163" s="129"/>
-      <c r="E163" s="133" t="s">
+      <c r="E163" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F163" s="128"/>
-      <c r="G163" s="133" t="s">
+      <c r="F163" s="130"/>
+      <c r="G163" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H163" s="129"/>
-      <c r="I163" s="128" t="s">
+      <c r="I163" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J163" s="129"/>
-      <c r="K163" s="128" t="s">
+      <c r="K163" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L163" s="129"/>
@@ -10219,23 +10225,23 @@
       <c r="B172" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C172" s="133" t="s">
+      <c r="C172" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D172" s="129"/>
-      <c r="E172" s="133" t="s">
+      <c r="E172" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F172" s="128"/>
-      <c r="G172" s="133" t="s">
+      <c r="F172" s="130"/>
+      <c r="G172" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H172" s="129"/>
-      <c r="I172" s="128" t="s">
+      <c r="I172" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J172" s="129"/>
-      <c r="K172" s="128" t="s">
+      <c r="K172" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L172" s="129"/>
@@ -10439,23 +10445,23 @@
       <c r="B181" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C181" s="133" t="s">
+      <c r="C181" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D181" s="129"/>
-      <c r="E181" s="133" t="s">
+      <c r="E181" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F181" s="128"/>
-      <c r="G181" s="133" t="s">
+      <c r="F181" s="130"/>
+      <c r="G181" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H181" s="129"/>
-      <c r="I181" s="128" t="s">
+      <c r="I181" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J181" s="129"/>
-      <c r="K181" s="128" t="s">
+      <c r="K181" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L181" s="129"/>
@@ -10660,23 +10666,23 @@
       <c r="B190" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C190" s="133" t="s">
+      <c r="C190" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D190" s="129"/>
-      <c r="E190" s="133" t="s">
+      <c r="E190" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F190" s="128"/>
-      <c r="G190" s="133" t="s">
+      <c r="F190" s="130"/>
+      <c r="G190" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H190" s="129"/>
-      <c r="I190" s="128" t="s">
+      <c r="I190" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J190" s="129"/>
-      <c r="K190" s="128" t="s">
+      <c r="K190" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L190" s="129"/>
@@ -10881,23 +10887,23 @@
       <c r="B199" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C199" s="133" t="s">
+      <c r="C199" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D199" s="129"/>
-      <c r="E199" s="133" t="s">
+      <c r="E199" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F199" s="128"/>
-      <c r="G199" s="133" t="s">
+      <c r="F199" s="130"/>
+      <c r="G199" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H199" s="129"/>
-      <c r="I199" s="128" t="s">
+      <c r="I199" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J199" s="129"/>
-      <c r="K199" s="128" t="s">
+      <c r="K199" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L199" s="129"/>
@@ -11102,23 +11108,23 @@
       <c r="B208" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C208" s="133" t="s">
+      <c r="C208" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D208" s="129"/>
-      <c r="E208" s="133" t="s">
+      <c r="E208" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F208" s="128"/>
-      <c r="G208" s="133" t="s">
+      <c r="F208" s="130"/>
+      <c r="G208" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H208" s="129"/>
-      <c r="I208" s="128" t="s">
+      <c r="I208" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J208" s="129"/>
-      <c r="K208" s="128" t="s">
+      <c r="K208" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L208" s="129"/>
@@ -11323,23 +11329,23 @@
       <c r="B217" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C217" s="133" t="s">
+      <c r="C217" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D217" s="129"/>
-      <c r="E217" s="133" t="s">
+      <c r="E217" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F217" s="128"/>
-      <c r="G217" s="133" t="s">
+      <c r="F217" s="130"/>
+      <c r="G217" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H217" s="129"/>
-      <c r="I217" s="128" t="s">
+      <c r="I217" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J217" s="129"/>
-      <c r="K217" s="128" t="s">
+      <c r="K217" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L217" s="129"/>
@@ -11544,23 +11550,23 @@
       <c r="B226" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C226" s="133" t="s">
+      <c r="C226" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D226" s="129"/>
-      <c r="E226" s="133" t="s">
+      <c r="E226" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F226" s="128"/>
-      <c r="G226" s="133" t="s">
+      <c r="F226" s="130"/>
+      <c r="G226" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H226" s="129"/>
-      <c r="I226" s="128" t="s">
+      <c r="I226" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J226" s="129"/>
-      <c r="K226" s="128" t="s">
+      <c r="K226" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L226" s="129"/>
@@ -11748,7 +11754,7 @@
     </row>
     <row r="233" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="234" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C234" s="130" t="s">
+      <c r="C234" s="133" t="s">
         <v>73</v>
       </c>
       <c r="D234" s="131"/>
@@ -11765,23 +11771,23 @@
       <c r="B235" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C235" s="133" t="s">
+      <c r="C235" s="128" t="s">
         <v>28</v>
       </c>
       <c r="D235" s="129"/>
-      <c r="E235" s="133" t="s">
+      <c r="E235" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="F235" s="128"/>
-      <c r="G235" s="133" t="s">
+      <c r="F235" s="130"/>
+      <c r="G235" s="128" t="s">
         <v>30</v>
       </c>
       <c r="H235" s="129"/>
-      <c r="I235" s="128" t="s">
+      <c r="I235" s="130" t="s">
         <v>31</v>
       </c>
       <c r="J235" s="129"/>
-      <c r="K235" s="128" t="s">
+      <c r="K235" s="130" t="s">
         <v>17</v>
       </c>
       <c r="L235" s="129"/>
@@ -11969,95 +11975,24 @@
     </row>
   </sheetData>
   <mergeCells count="131">
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C107:L107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="C134:L134"/>
-    <mergeCell ref="C125:L125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="G126:H126"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="K126:L126"/>
-    <mergeCell ref="C116:L116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="G117:H117"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="K117:L117"/>
-    <mergeCell ref="C144:L144"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="E145:F145"/>
-    <mergeCell ref="G145:H145"/>
-    <mergeCell ref="I145:J145"/>
-    <mergeCell ref="K145:L145"/>
-    <mergeCell ref="C153:L153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="I154:J154"/>
-    <mergeCell ref="K154:L154"/>
-    <mergeCell ref="C162:L162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="K163:L163"/>
-    <mergeCell ref="C171:L171"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="I172:J172"/>
-    <mergeCell ref="K172:L172"/>
+    <mergeCell ref="I208:J208"/>
+    <mergeCell ref="K208:L208"/>
+    <mergeCell ref="C216:L216"/>
+    <mergeCell ref="C234:L234"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="I217:J217"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="I235:J235"/>
+    <mergeCell ref="K235:L235"/>
+    <mergeCell ref="C226:D226"/>
+    <mergeCell ref="E226:F226"/>
+    <mergeCell ref="G226:H226"/>
+    <mergeCell ref="I226:J226"/>
+    <mergeCell ref="K226:L226"/>
     <mergeCell ref="C180:L180"/>
     <mergeCell ref="C181:D181"/>
     <mergeCell ref="E181:F181"/>
@@ -12082,24 +12017,95 @@
     <mergeCell ref="C208:D208"/>
     <mergeCell ref="E208:F208"/>
     <mergeCell ref="G208:H208"/>
-    <mergeCell ref="I208:J208"/>
-    <mergeCell ref="K208:L208"/>
-    <mergeCell ref="C216:L216"/>
-    <mergeCell ref="C234:L234"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="E217:F217"/>
-    <mergeCell ref="G217:H217"/>
-    <mergeCell ref="I217:J217"/>
-    <mergeCell ref="C235:D235"/>
-    <mergeCell ref="E235:F235"/>
-    <mergeCell ref="G235:H235"/>
-    <mergeCell ref="I235:J235"/>
-    <mergeCell ref="K235:L235"/>
-    <mergeCell ref="C226:D226"/>
-    <mergeCell ref="E226:F226"/>
-    <mergeCell ref="G226:H226"/>
-    <mergeCell ref="I226:J226"/>
-    <mergeCell ref="K226:L226"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="C171:L171"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="I172:J172"/>
+    <mergeCell ref="K172:L172"/>
+    <mergeCell ref="C144:L144"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="C153:L153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="K154:L154"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="C134:L134"/>
+    <mergeCell ref="C125:L125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="C116:L116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="K117:L117"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C107:L107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12108,7 +12114,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B9:I248"/>
+  <dimension ref="B9:I249"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -15434,21 +15440,35 @@
       </c>
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B247" s="107">
+      <c r="B247" s="93">
         <v>46204</v>
       </c>
-      <c r="C247" s="105">
+      <c r="C247" s="87">
         <v>67136919.599999964</v>
       </c>
-      <c r="D247" s="21">
+      <c r="D247" s="83">
         <v>17681.99694999999</v>
       </c>
-      <c r="E247" s="20">
+      <c r="E247" s="22">
         <v>3796.9082219528377</v>
       </c>
     </row>
     <row r="248" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B248" s="55" t="s">
+      <c r="B248" s="107">
+        <v>46235</v>
+      </c>
+      <c r="C248" s="105">
+        <v>41213979.369999953</v>
+      </c>
+      <c r="D248" s="21">
+        <v>11081.581000000002</v>
+      </c>
+      <c r="E248" s="20">
+        <v>3719.1425456349543</v>
+      </c>
+    </row>
+    <row r="249" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B249" s="55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -15466,26 +15486,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -15726,30 +15730,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC8F936-4AF3-4FF9-8B1E-0736929643E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15768,10 +15777,21 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>